--- a/Document/정책문서.xlsx
+++ b/Document/정책문서.xlsx
@@ -8,17 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git_fork\ProjectShoot\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01C63934-31CC-4D47-8F68-326F2CD450AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE523EAD-D810-4A5F-8C10-1CFCF9EBCD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="711" firstSheet="1" activeTab="5" xr2:uid="{F9E8F865-F741-4425-897D-555A2E4B3EBE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="711" firstSheet="1" activeTab="3" xr2:uid="{F9E8F865-F741-4425-897D-555A2E4B3EBE}"/>
   </bookViews>
   <sheets>
     <sheet name="깃포크 공부" sheetId="11" state="hidden" r:id="rId1"/>
     <sheet name="player" sheetId="3" r:id="rId2"/>
     <sheet name="enemy" sheetId="6" r:id="rId3"/>
-    <sheet name="생애주기" sheetId="13" r:id="rId4"/>
-    <sheet name="카메라 " sheetId="15" r:id="rId5"/>
-    <sheet name="개발요청" sheetId="12" r:id="rId6"/>
+    <sheet name="Formation" sheetId="16" r:id="rId4"/>
+    <sheet name="Move_Pattern" sheetId="17" r:id="rId5"/>
+    <sheet name="생애주기" sheetId="13" r:id="rId6"/>
+    <sheet name="카메라 " sheetId="15" r:id="rId7"/>
+    <sheet name="개발요청" sheetId="12" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,16 +40,204 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>user</author>
+  </authors>
+  <commentList>
+    <comment ref="E38" authorId="0" shapeId="0" xr:uid="{6849FD8E-1256-4229-AD4B-FBC70E2BDB53}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>user:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>최대</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>스폰</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>일시</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>진행</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>멈춤
+시간</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>간의</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>간격은</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>유지되어야함</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="275">
-  <si>
-    <t xml:space="preserve">더 좋은 아이디어가 있다면 적극 환영합니다. </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">이 문서에서는 플레이어 기체를 ufc 로 표기합니다 (임시조치)  </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="332">
   <si>
     <t>설명</t>
   </si>
@@ -102,10 +292,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">(일단 고정, 늘어나지 않을 예정) </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>적과 충돌 시, 미사일 피격시 감소</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -266,10 +452,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>개발 진척에 따라 만듭니다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>적이 잡힌경우의 연출에 대해서 설명합니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -303,10 +485,6 @@
   </si>
   <si>
     <t xml:space="preserve">충돌 대미지  </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">이거 별도로 설정이 필요할 것같습니다. </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -968,67 +1146,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>군집일지 단일체일지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">군입인 경우 소환 좌표나 분포를 어떻게 표현할지 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">스테이지에서 스폰이 되는건데 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">몬스터의 스폰조건 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">적에 따라 상이 (특정 시간 경과, n초마다 등장, 특정 시간 경과 후 n초마다 등장) </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">더미 적들 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">이름 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>석삼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>너구리</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">보스 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>적 더미 ( 2번 까지 )</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>한이</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>두식</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>오진</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>육개장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이동 속도</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1152,12 +1274,343 @@
     <t xml:space="preserve">유진님 웹백엔드 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t xml:space="preserve">1개 (일단 고정, 늘어나지 않을 예정) </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정의</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">몬스터가 배치되는 형태 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>포매이션 형태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Formation(적 진형)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shape_V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Line_H</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Line_V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shape_A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">정책 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>본 문서에서는 이하 '진형'으로 표현</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">2종 이하의 적으로 구성 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">기획 의도 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">대장기 와 호위기로 구성 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">적 유닛들이 단독이 아닌 일정한 형태를 지어 등장, 유저에게 시작적 즐거움과 전략의 즐거움을 제공 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄴ 호위기: 진형에서 대장을 제외한 모든 유닛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>설명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>별도의 진형 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">진형 당 최대 배치 유닛 수는 7기 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>ㄴ ( 호위호위호위</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>대장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">호위호위호위) </t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가로 일렬 대형 (horizontal)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>세로 일렬 대형 (vertical)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시옷모양 대형. 편의상 A로 표기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v모양 대형. (예시: 앞에 탱커 뒤에 딜러)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>진형 종류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SO(스크립터블 오브젝트 구조) </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스폰 타임라인 데이터에 같이 들어감</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>생성되는 시간 (초)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">적 id </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>개체 수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>진형</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>진형 간격 x</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>진형 간격 y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>행동 패턴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Spawn_Id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Time_Stamp </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpwanZone_Id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Count</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Formation_Id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Spacing x </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Spacing y </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Move_Pattern_ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하나,두식이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shape_v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스폰 구역</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스폰 위치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Is_Random</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스폰 Id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">스폰 고유 번호 </t>
+  </si>
+  <si>
+    <t>Spawn_ID (int)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Time_Stamp (float)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">게임 시작 후 스폰될 타이밍 (초 단위) </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Main_Enemy , Sub_Enemy </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대장칸, 부하칸에 기획자가 드래그</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Spawn_Zone (Link / Object)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스폰 영역 박스 오브젝트를 기획자가 링크</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Is_Random (Bool / 체크박스)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>체크하면 영역 내 랜덤 배치, 체크를 해제하면 영역의 정중앙에 배치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Count (int)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">소환할 마릿수 (최대 7마리) </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Formation_ID (Enum)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">진형 종류 중 하나 선택 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Main_Enemy / Sub_Enemy (EnemyData_SO 링크)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>링크</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zone 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zone 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zone 3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Spacing (float): 기체 간 격차 간격 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄴ 대장기: 일반적으로 진형에서 가장 강한 유닛. 홀수의 경우 진형의 중앙에 위치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">배치 순서의 경우 다음과 같음 (노랑: 대장기 파랑:호위기) </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="177" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1274,8 +1727,54 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0066FF"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1302,18 +1801,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5B0C7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1330,8 +1817,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="23">
+  <borders count="35">
     <border>
       <left/>
       <right/>
@@ -1609,16 +2102,174 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1673,20 +2324,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1724,10 +2366,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1739,7 +2381,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1748,10 +2390,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="1" applyFont="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -1766,8 +2408,11 @@
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1790,6 +2435,102 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="20% - 강조색3" xfId="1" builtinId="38"/>
@@ -1799,6 +2540,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF0066FF"/>
       <color rgb="FFFF66CC"/>
       <color rgb="FFB2B5BA"/>
       <color rgb="FFFF99CC"/>
@@ -1928,16 +2670,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>752475</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>19048</xdr:rowOff>
+      <xdr:rowOff>28573</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>447675</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>733425</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>219074</xdr:rowOff>
+      <xdr:rowOff>228599</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1961,7 +2703,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm rot="10800000">
-          <a:off x="0" y="19048"/>
+          <a:off x="1543050" y="28573"/>
           <a:ext cx="1238250" cy="876301"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3905,15 +4647,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>590551</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>400051</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -3928,7 +4670,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4819650" y="9963150"/>
+          <a:off x="5581650" y="6838950"/>
           <a:ext cx="3762376" cy="5324475"/>
           <a:chOff x="857250" y="9715500"/>
           <a:chExt cx="3762376" cy="5324475"/>
@@ -4310,6 +5052,399 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>318052</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>28161</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>24847</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>16565</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="직사각형 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A543E9E-B357-68C8-51B1-61CF818DCD6C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14986552" y="4666422"/>
+          <a:ext cx="1081708" cy="402534"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            <a:t>생성영역</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100"/>
+            <a:t>4</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>670892</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>173935</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>364436</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>140804</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="타원 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89C76D5C-08FB-8D6B-B8EF-9FC7DE93C678}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2178327" y="3776870"/>
+          <a:ext cx="381000" cy="380999"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent4">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100"/>
+            <a:t>1</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>82827</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>173935</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>463827</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>140804</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="타원 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD753711-D943-F2F7-0480-3ADDADFF2280}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1590262" y="3776870"/>
+          <a:ext cx="381000" cy="380999"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100"/>
+            <a:t>2</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>621197</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>173935</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>314740</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>140804</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="타원 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5EE6612B-E8F8-86A4-4C87-CAAF29B50274}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2816088" y="3776870"/>
+          <a:ext cx="381000" cy="380999"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100"/>
+            <a:t>3</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>99393</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>173935</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>480393</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>140804</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="타원 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AFE6CB83-5768-697B-6544-0C62D362FB1A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="919371" y="3776870"/>
+          <a:ext cx="381000" cy="380999"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100"/>
+            <a:t>4</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>563220</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>173934</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>256764</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>140803</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="타원 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9ACB82F-5785-4549-AE72-CF121D3EEE9B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3445568" y="3776869"/>
+          <a:ext cx="381000" cy="380999"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100"/>
+            <a:t>5</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -5120,7 +6255,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -6010,8 +7145,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="38.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
-        <v>79</v>
+      <c r="A1" s="21" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
@@ -6019,26 +7154,26 @@
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="O3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="P3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="H4" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="P4" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="P5" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -6046,7 +7181,7 @@
         <v>2</v>
       </c>
       <c r="G28" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -6061,509 +7196,493 @@
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.625" customWidth="1"/>
+    <col min="1" max="1" width="3.75" customWidth="1"/>
+    <col min="2" max="2" width="5.375" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="44.125" customWidth="1"/>
     <col min="5" max="5" width="13.75" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="2.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="64.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="64.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="26.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="26.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
+    <row r="1" spans="1:7" ht="26.25" x14ac:dyDescent="0.3">
+      <c r="A1" s="47" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B3" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="10" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="26.25" x14ac:dyDescent="0.3">
-      <c r="A3" s="9" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B6" s="8" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B7" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="10" t="s">
+      <c r="G4" s="11"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="11">
+        <f t="shared" ref="B5:B12" si="0">ROW()-ROW($B$4)</f>
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="11">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="11">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="11">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
         <v>11</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="H7" s="11"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B8" s="11">
-        <f t="shared" ref="B8:B15" si="0">ROW()-ROW($B$7)</f>
-        <v>1</v>
-      </c>
-      <c r="C8" s="22" t="s">
-        <v>10</v>
       </c>
       <c r="D8" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E8" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B9" s="11">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>15</v>
+        <v>5</v>
+      </c>
+      <c r="C9" t="s">
+        <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="G9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+      <c r="F9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B10" s="11">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+      <c r="E10" s="13"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B11" s="11">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>13</v>
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="E11" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" t="s">
         <v>43</v>
       </c>
-      <c r="G11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B12" s="11">
         <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="E12" s="13"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B13" s="11"/>
+      <c r="E13" s="13"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B14" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="13"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B15" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="E15" s="13"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B16" s="11">
+        <f>ROW()-ROW($B$15)</f>
+        <v>1</v>
+      </c>
+      <c r="C16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B17" s="11">
+        <f>ROW()-ROW($B$15)</f>
+        <v>2</v>
+      </c>
+      <c r="C17" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" s="13"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E18" s="13"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B19" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" s="13"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B20" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B21" s="11">
+        <f>ROW()-ROW($B$20)</f>
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B22" s="11">
+        <f t="shared" ref="B22:B26" si="1">ROW()-ROW($B$20)</f>
+        <v>2</v>
+      </c>
+      <c r="C22" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" t="s">
+        <v>2</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F22" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B23" s="11">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="G12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B13" s="11">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="C13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="E23" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="13"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B14" s="11">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="C14" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="G14" t="s">
-        <v>47</v>
-      </c>
-      <c r="H14" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B15" s="11">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="E15" s="13"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B16" s="11"/>
-      <c r="E16" s="13"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B17" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E17" s="13"/>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B18" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E18" s="13"/>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B19" s="11">
-        <f>ROW()-ROW($B$18)</f>
-        <v>1</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="F23" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B24" s="11">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="C24" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F24" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B25" s="11">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="C25" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" t="s">
         <v>37</v>
       </c>
-      <c r="D19" t="s">
-        <v>41</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B20" s="11">
-        <f>ROW()-ROW($B$18)</f>
-        <v>2</v>
-      </c>
-      <c r="C20" t="s">
-        <v>77</v>
-      </c>
-      <c r="E20" s="13"/>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="E21" s="13"/>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B22" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E22" s="13"/>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B23" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B24" s="11">
-        <f>ROW()-ROW($B$23)</f>
-        <v>1</v>
-      </c>
-      <c r="C24" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" t="s">
-        <v>5</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="G24" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B25" s="11">
-        <f t="shared" ref="B25:B29" si="1">ROW()-ROW($B$23)</f>
-        <v>2</v>
-      </c>
-      <c r="C25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D25" t="s">
-        <v>4</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="G25" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="E25" s="13"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B26" s="11">
         <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="C26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" t="s">
+        <v>42</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F26" t="s">
+        <v>44</v>
+      </c>
+      <c r="G26" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B28" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B29" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="G29" s="11"/>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B30" s="11">
+        <f t="shared" ref="B30:B38" si="2">ROW()-ROW($B$29)</f>
+        <v>1</v>
+      </c>
+      <c r="C30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30" t="s">
         <v>3</v>
       </c>
-      <c r="C26" t="s">
-        <v>13</v>
-      </c>
-      <c r="D26" t="s">
-        <v>7</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="G26" t="s">
+      <c r="F30" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B31" s="11">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="C31" t="s">
+        <v>22</v>
+      </c>
+      <c r="D31" t="s">
+        <v>2</v>
+      </c>
+      <c r="F31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B32" s="11">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="C32" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B27" s="11">
-        <f t="shared" si="1"/>
+      <c r="D32" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B33" s="11">
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="C27" t="s">
-        <v>21</v>
-      </c>
-      <c r="D27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="G27" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B28" s="11">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="C28" t="s">
-        <v>38</v>
-      </c>
-      <c r="D28" t="s">
-        <v>40</v>
-      </c>
-      <c r="E28" s="13"/>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B29" s="11">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="C29" t="s">
-        <v>44</v>
-      </c>
-      <c r="D29" t="s">
-        <v>45</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="G29" t="s">
-        <v>47</v>
-      </c>
-      <c r="H29" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B31" s="8" t="s">
+      <c r="C33" t="s">
+        <v>18</v>
+      </c>
+      <c r="D33" t="s">
+        <v>19</v>
+      </c>
+      <c r="F33" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B32" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="H32" s="11"/>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B33" s="11">
-        <f t="shared" ref="B33:B41" si="2">ROW()-ROW($B$32)</f>
-        <v>1</v>
-      </c>
-      <c r="C33" t="s">
-        <v>24</v>
-      </c>
-      <c r="D33" t="s">
-        <v>5</v>
-      </c>
-      <c r="G33" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B34" s="11">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C34" t="s">
+        <v>24</v>
+      </c>
+      <c r="D34" t="s">
         <v>25</v>
       </c>
-      <c r="D34" t="s">
-        <v>4</v>
-      </c>
-      <c r="G34" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B35" s="11">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C35" t="s">
         <v>26</v>
       </c>
-      <c r="D35" t="s">
-        <v>7</v>
-      </c>
-      <c r="G35" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B36" s="11">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C36" t="s">
-        <v>21</v>
-      </c>
-      <c r="D36" t="s">
-        <v>22</v>
-      </c>
-      <c r="G36" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B37" s="11">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C37" t="s">
-        <v>27</v>
-      </c>
-      <c r="D37" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E37" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F37" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B38" s="11">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C38" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B39" s="11">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-      <c r="C39" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B40" s="11">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="C40" t="s">
-        <v>31</v>
-      </c>
-      <c r="E40" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G40" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B41" s="11">
-        <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-      <c r="C41" t="s">
-        <v>35</v>
-      </c>
-      <c r="D41" t="s">
-        <v>36</v>
+        <v>32</v>
+      </c>
+      <c r="D38" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -6578,34 +7697,34 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="B1:U50"/>
+  <dimension ref="A1:U35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.625" customWidth="1"/>
     <col min="2" max="2" width="6.75" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="3" max="3" width="16.5" customWidth="1"/>
     <col min="4" max="4" width="39.125" customWidth="1"/>
     <col min="5" max="5" width="15.375" customWidth="1"/>
     <col min="16" max="16" width="4.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="26.25" x14ac:dyDescent="0.3">
-      <c r="D1" s="9" t="s">
-        <v>49</v>
+    <row r="1" spans="1:21" ht="26.25" x14ac:dyDescent="0.3">
+      <c r="A1" s="47" t="s">
+        <v>46</v>
       </c>
       <c r="E1" s="12"/>
     </row>
-    <row r="2" spans="2:21" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:21" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D2" s="9"/>
       <c r="E2" s="12"/>
       <c r="K2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="Q2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="2:21" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D3" s="9"/>
       <c r="E3" s="12"/>
       <c r="K3" s="15">
@@ -6623,93 +7742,91 @@
       <c r="T3" s="1"/>
       <c r="U3" s="2"/>
     </row>
-    <row r="4" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="K4" s="3"/>
       <c r="O4" s="4"/>
       <c r="Q4" s="3"/>
       <c r="U4" s="4"/>
     </row>
-    <row r="5" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="K5" s="3"/>
       <c r="O5" s="4"/>
       <c r="Q5" s="3"/>
       <c r="U5" s="4"/>
     </row>
-    <row r="6" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="K6" s="3"/>
       <c r="O6" s="4"/>
       <c r="Q6" s="3"/>
       <c r="U6" s="4"/>
     </row>
-    <row r="7" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B7" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>52</v>
+        <v>7</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>49</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="K7" s="3"/>
       <c r="O7" s="4"/>
       <c r="Q7" s="3"/>
       <c r="U7" s="4"/>
     </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B8" s="11">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K8" s="3"/>
       <c r="O8" s="4"/>
       <c r="Q8" s="3"/>
       <c r="U8" s="4"/>
     </row>
-    <row r="9" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B9" s="11">
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>58</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="E9" s="17"/>
       <c r="K9" s="3"/>
       <c r="O9" s="4"/>
       <c r="Q9" s="3"/>
       <c r="U9" s="4"/>
     </row>
-    <row r="10" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="K10" s="3"/>
       <c r="O10" s="4"/>
       <c r="Q10" s="3"/>
       <c r="U10" s="4"/>
     </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="K11" s="3"/>
       <c r="O11" s="4"/>
       <c r="Q11" s="3"/>
       <c r="U11" s="4"/>
     </row>
-    <row r="12" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B12" s="8" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E12" s="11"/>
       <c r="K12" s="3"/>
@@ -6717,79 +7834,79 @@
       <c r="Q12" s="3"/>
       <c r="U12" s="4"/>
     </row>
-    <row r="13" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B13" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>11</v>
-      </c>
       <c r="D13" s="10" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K13" s="3"/>
       <c r="O13" s="4"/>
       <c r="Q13" s="3"/>
       <c r="U13" s="4"/>
     </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B14" s="11">
         <f t="shared" ref="B14:B19" si="0">ROW()-ROW($B$13)</f>
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F14" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K14" s="3"/>
       <c r="O14" s="4"/>
       <c r="Q14" s="3"/>
       <c r="U14" s="4"/>
     </row>
-    <row r="15" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B15" s="11">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="K15" s="3"/>
       <c r="O15" s="4"/>
       <c r="Q15" s="3"/>
       <c r="U15" s="4"/>
     </row>
-    <row r="16" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B16" s="11">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D16" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E16" s="13"/>
       <c r="F16" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="K16" s="3"/>
       <c r="O16" s="4"/>
@@ -6802,10 +7919,10 @@
         <v>4</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="K17" s="3"/>
       <c r="O17" s="4"/>
@@ -6818,10 +7935,10 @@
         <v>5</v>
       </c>
       <c r="C18" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D18" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="K18" s="3"/>
       <c r="O18" s="4"/>
@@ -6829,20 +7946,19 @@
       <c r="U18" s="4"/>
     </row>
     <row r="19" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B19" s="18">
+      <c r="B19" s="57">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C19" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="D19" s="19"/>
-      <c r="E19" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="F19" s="19" t="s">
-        <v>68</v>
-      </c>
+      <c r="C19" s="58" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" s="58"/>
+      <c r="E19" s="57" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" s="58"/>
+      <c r="G19" s="58"/>
       <c r="K19" s="3"/>
       <c r="O19" s="4"/>
       <c r="Q19" s="3"/>
@@ -6856,7 +7972,7 @@
     </row>
     <row r="21" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B21" s="8" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="K21" s="3"/>
       <c r="O21" s="4"/>
@@ -6865,19 +7981,19 @@
     </row>
     <row r="22" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B22" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="10" t="s">
-        <v>11</v>
-      </c>
       <c r="D22" s="10" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K22" s="3"/>
       <c r="O22" s="4"/>
@@ -6890,13 +8006,13 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D23" t="s">
+        <v>60</v>
+      </c>
+      <c r="F23" t="s">
         <v>64</v>
-      </c>
-      <c r="F23" t="s">
-        <v>69</v>
       </c>
       <c r="K23" s="3"/>
       <c r="O23" s="4"/>
@@ -6909,10 +8025,10 @@
         <v>2</v>
       </c>
       <c r="C24" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" t="s">
         <v>65</v>
-      </c>
-      <c r="F24" t="s">
-        <v>70</v>
       </c>
       <c r="K24" s="3"/>
       <c r="O24" s="4"/>
@@ -6925,7 +8041,7 @@
         <v>3</v>
       </c>
       <c r="C25" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="K25" s="3"/>
       <c r="O25" s="4"/>
@@ -6938,7 +8054,7 @@
         <v>4</v>
       </c>
       <c r="C26" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="K26" s="3"/>
       <c r="O26" s="4"/>
@@ -6951,7 +8067,7 @@
         <v>5</v>
       </c>
       <c r="C27" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="K27" s="5"/>
       <c r="L27" s="6"/>
@@ -6964,145 +8080,46 @@
       <c r="T27" s="6"/>
       <c r="U27" s="7"/>
     </row>
-    <row r="29" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B29" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="30" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B30" t="s">
-        <v>235</v>
+    <row r="30" spans="2:21" ht="26.25" x14ac:dyDescent="0.3">
+      <c r="B30" s="39" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="31" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B31" s="14" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B32" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B33" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B35" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B37" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C37" s="14" t="s">
-        <v>240</v>
-      </c>
-      <c r="D37" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="E37" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="F37" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="G37" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="H37" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="I37" s="14" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B38" s="11">
+      <c r="B32" s="11">
         <v>1</v>
       </c>
-      <c r="C38" t="s">
-        <v>245</v>
-      </c>
-      <c r="D38">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B39" s="11">
+      <c r="C32" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B33" s="11">
         <v>2</v>
       </c>
-      <c r="C39" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B40" s="11">
+      <c r="C33" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B34" s="11">
         <v>3</v>
       </c>
-      <c r="C40" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B41" s="11">
+      <c r="C34" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B35" s="11">
         <v>4</v>
       </c>
-      <c r="C41" t="s">
-        <v>242</v>
-      </c>
-      <c r="D41" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C42" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C43" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="45" spans="2:9" ht="26.25" x14ac:dyDescent="0.3">
-      <c r="B45" s="42" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B46" s="14" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B47" s="11">
-        <v>1</v>
-      </c>
-      <c r="C47" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="48" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B48" s="11">
-        <v>2</v>
-      </c>
-      <c r="C48" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B49" s="11">
-        <v>3</v>
-      </c>
-      <c r="C49" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B50" s="11">
-        <v>4</v>
-      </c>
-      <c r="C50" t="s">
-        <v>272</v>
+      <c r="C35" t="s">
+        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -7113,6 +8130,525 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90669897-7B19-41C3-ACE9-893F9F9C4143}">
+  <dimension ref="A1:P51"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="2.875" customWidth="1"/>
+    <col min="2" max="2" width="4.125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="3.75" customWidth="1"/>
+    <col min="7" max="7" width="9" customWidth="1"/>
+    <col min="9" max="9" width="9" customWidth="1"/>
+    <col min="11" max="11" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="26.25" x14ac:dyDescent="0.3">
+      <c r="A1" s="47" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="47"/>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="47"/>
+      <c r="B3" s="8" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="47"/>
+      <c r="C4" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="47"/>
+      <c r="C5" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="47"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B7" s="8" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C8" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B10" s="8" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C11" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C13" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D14" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D15" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C17" s="56" t="s">
+        <v>331</v>
+      </c>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
+      <c r="F17" s="56"/>
+      <c r="G17" s="56"/>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C22" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C23" s="18"/>
+      <c r="D23" s="18" t="s">
+        <v>276</v>
+      </c>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B25" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C26" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="55" t="s">
+        <v>259</v>
+      </c>
+      <c r="E26" s="55"/>
+      <c r="F26" s="55" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C27" s="11">
+        <f>ROW()-ROW($C$26)</f>
+        <v>1</v>
+      </c>
+      <c r="D27" t="s">
+        <v>265</v>
+      </c>
+      <c r="F27" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C28" s="11">
+        <f t="shared" ref="C28:C31" si="0">ROW()-ROW($C$26)</f>
+        <v>2</v>
+      </c>
+      <c r="D28" t="s">
+        <v>262</v>
+      </c>
+      <c r="F28" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C29" s="11">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="D29" t="s">
+        <v>263</v>
+      </c>
+      <c r="F29" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C30" s="11">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="D30" t="s">
+        <v>264</v>
+      </c>
+      <c r="F30" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C31" s="11">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="D31" t="s">
+        <v>261</v>
+      </c>
+      <c r="F31" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B33" s="8" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C34" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="36" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D36" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="E36" s="60" t="s">
+        <v>284</v>
+      </c>
+      <c r="F36" s="61"/>
+      <c r="G36" s="60" t="s">
+        <v>285</v>
+      </c>
+      <c r="H36" s="61"/>
+      <c r="I36" s="59" t="s">
+        <v>301</v>
+      </c>
+      <c r="J36" s="62"/>
+      <c r="K36" s="60" t="s">
+        <v>304</v>
+      </c>
+      <c r="L36" s="63" t="s">
+        <v>287</v>
+      </c>
+      <c r="M36" s="64" t="s">
+        <v>286</v>
+      </c>
+      <c r="N36" s="64" t="s">
+        <v>288</v>
+      </c>
+      <c r="O36" s="65" t="s">
+        <v>289</v>
+      </c>
+      <c r="P36" s="20" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D37" s="19" t="s">
+        <v>302</v>
+      </c>
+      <c r="E37" s="60" t="s">
+        <v>303</v>
+      </c>
+      <c r="F37" s="61"/>
+      <c r="G37" s="60" t="s">
+        <v>325</v>
+      </c>
+      <c r="H37" s="61"/>
+      <c r="I37" s="60" t="s">
+        <v>325</v>
+      </c>
+      <c r="J37" s="62"/>
+      <c r="K37" s="60" t="s">
+        <v>305</v>
+      </c>
+      <c r="L37" s="66" t="s">
+        <v>308</v>
+      </c>
+      <c r="M37" s="67" t="s">
+        <v>302</v>
+      </c>
+      <c r="N37" s="67" t="s">
+        <v>303</v>
+      </c>
+      <c r="O37" s="68" t="s">
+        <v>303</v>
+      </c>
+      <c r="P37" s="20"/>
+    </row>
+    <row r="38" spans="2:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D38" s="19" t="s">
+        <v>291</v>
+      </c>
+      <c r="E38" s="60" t="s">
+        <v>292</v>
+      </c>
+      <c r="F38" s="61"/>
+      <c r="G38" s="86" t="s">
+        <v>314</v>
+      </c>
+      <c r="H38" s="61"/>
+      <c r="I38" s="59" t="s">
+        <v>293</v>
+      </c>
+      <c r="J38" s="62"/>
+      <c r="K38" s="60" t="s">
+        <v>307</v>
+      </c>
+      <c r="L38" s="69" t="s">
+        <v>295</v>
+      </c>
+      <c r="M38" s="70" t="s">
+        <v>294</v>
+      </c>
+      <c r="N38" s="70" t="s">
+        <v>296</v>
+      </c>
+      <c r="O38" s="71" t="s">
+        <v>297</v>
+      </c>
+      <c r="P38" s="20" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D39" s="72">
+        <f>ROW()-ROW($D$38)</f>
+        <v>1</v>
+      </c>
+      <c r="E39" s="73">
+        <v>3</v>
+      </c>
+      <c r="F39" s="74"/>
+      <c r="G39" s="75" t="s">
+        <v>299</v>
+      </c>
+      <c r="H39" s="74"/>
+      <c r="I39" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="J39" s="74"/>
+      <c r="K39" s="76"/>
+      <c r="L39" s="77" t="s">
+        <v>300</v>
+      </c>
+      <c r="M39" s="77">
+        <v>5</v>
+      </c>
+      <c r="N39" s="77">
+        <v>30</v>
+      </c>
+      <c r="O39" s="77">
+        <v>30</v>
+      </c>
+      <c r="P39" s="78"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D40" s="72">
+        <f t="shared" ref="D40:D42" si="1">ROW()-ROW($D$38)</f>
+        <v>2</v>
+      </c>
+      <c r="E40" s="73" t="s">
+        <v>306</v>
+      </c>
+      <c r="F40" s="74"/>
+      <c r="G40" s="75" t="s">
+        <v>306</v>
+      </c>
+      <c r="H40" s="74"/>
+      <c r="I40" s="74" t="s">
+        <v>327</v>
+      </c>
+      <c r="J40" s="74"/>
+      <c r="K40" s="77"/>
+      <c r="L40" s="77"/>
+      <c r="M40" s="77"/>
+      <c r="N40" s="77"/>
+      <c r="O40" s="77"/>
+      <c r="P40" s="79"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D41" s="72">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="E41" s="73" t="s">
+        <v>306</v>
+      </c>
+      <c r="F41" s="74"/>
+      <c r="G41" s="75" t="s">
+        <v>306</v>
+      </c>
+      <c r="H41" s="74"/>
+      <c r="I41" s="74" t="s">
+        <v>328</v>
+      </c>
+      <c r="J41" s="74"/>
+      <c r="K41" s="77"/>
+      <c r="L41" s="77"/>
+      <c r="M41" s="77"/>
+      <c r="N41" s="77"/>
+      <c r="O41" s="77"/>
+      <c r="P41" s="79"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D42" s="80">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="E42" s="85" t="s">
+        <v>306</v>
+      </c>
+      <c r="F42" s="82"/>
+      <c r="G42" s="81" t="s">
+        <v>306</v>
+      </c>
+      <c r="H42" s="82"/>
+      <c r="I42" s="82" t="s">
+        <v>306</v>
+      </c>
+      <c r="J42" s="82"/>
+      <c r="K42" s="83"/>
+      <c r="L42" s="83"/>
+      <c r="M42" s="83"/>
+      <c r="N42" s="83"/>
+      <c r="O42" s="83"/>
+      <c r="P42" s="84"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D44" t="s">
+        <v>311</v>
+      </c>
+      <c r="G44" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D45" t="s">
+        <v>312</v>
+      </c>
+      <c r="G45" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D46" t="s">
+        <v>324</v>
+      </c>
+      <c r="G46" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D47" t="s">
+        <v>316</v>
+      </c>
+      <c r="G47" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D48" t="s">
+        <v>318</v>
+      </c>
+      <c r="G48" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="49" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D49" t="s">
+        <v>320</v>
+      </c>
+      <c r="G49" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="50" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D50" t="s">
+        <v>322</v>
+      </c>
+      <c r="G50" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="51" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D51" t="s">
+        <v>329</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96B3948A-F2EB-4210-816C-FE29D536AFF8}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3FA637D-A4E4-43F5-99C7-0DE64168A271}">
   <dimension ref="A1:L46"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -7132,411 +8668,411 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="31.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="31" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="32" t="s">
+        <v>143</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B5" s="51" t="s">
+        <v>129</v>
+      </c>
+      <c r="C5" s="51"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48" t="s">
+        <v>126</v>
+      </c>
+      <c r="F5" s="50"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="48" t="s">
+        <v>136</v>
+      </c>
+      <c r="I5" s="49"/>
+      <c r="J5" s="48" t="s">
+        <v>141</v>
+      </c>
+      <c r="K5" s="49"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B6" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="F6" s="30" t="s">
+        <v>132</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="I6" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="J6" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="K6" s="24" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="35" t="s">
-        <v>148</v>
-      </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B5" s="53" t="s">
-        <v>134</v>
-      </c>
-      <c r="C5" s="53"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50" t="s">
-        <v>131</v>
-      </c>
-      <c r="F5" s="52"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="50" t="s">
+      <c r="D7" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B9" s="48" t="s">
+        <v>151</v>
+      </c>
+      <c r="C9" s="49"/>
+      <c r="D9" s="48" t="s">
+        <v>153</v>
+      </c>
+      <c r="E9" s="50"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="48" t="s">
+        <v>136</v>
+      </c>
+      <c r="H9" s="49"/>
+      <c r="I9" s="48" t="s">
         <v>141</v>
       </c>
-      <c r="I5" s="51"/>
-      <c r="J5" s="50" t="s">
-        <v>146</v>
-      </c>
-      <c r="K5" s="51"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B6" s="28" t="s">
+      <c r="J9" s="49"/>
+      <c r="K9" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="L9" s="49"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B10" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>150</v>
+      </c>
+      <c r="D10" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="E10" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="F10" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="C6" s="29" t="s">
-        <v>135</v>
-      </c>
-      <c r="D6" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="E6" s="32" t="s">
+      <c r="G10" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="H10" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="I10" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="J10" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="K10" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="L10" s="19" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="52" t="s">
+        <v>155</v>
+      </c>
+      <c r="D14" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="F14" s="51" t="s">
+        <v>165</v>
+      </c>
+      <c r="G14" s="51"/>
+      <c r="H14" s="51"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="53"/>
+      <c r="D15" s="34" t="s">
+        <v>157</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="53"/>
+      <c r="D16" s="35" t="s">
+        <v>158</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="53"/>
+      <c r="D17" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="53"/>
+      <c r="D18" s="13" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="53"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="53"/>
+      <c r="E20" s="36" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="53"/>
+      <c r="E21" s="13" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="53"/>
+      <c r="E22" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="53"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="53"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="53"/>
+      <c r="E25" s="11" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="53"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="53"/>
+      <c r="E27" s="13" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="53"/>
+      <c r="E28" s="13" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="53"/>
+      <c r="E29" s="11" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="53"/>
+      <c r="E30" s="13" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="54"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B33" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="C33" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="F6" s="33" t="s">
-        <v>137</v>
-      </c>
-      <c r="G6" s="27" t="s">
-        <v>138</v>
-      </c>
-      <c r="H6" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="I6" s="23" t="s">
-        <v>145</v>
-      </c>
-      <c r="J6" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="K6" s="27" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="I7" s="11" t="s">
+      <c r="D33" s="48" t="s">
+        <v>189</v>
+      </c>
+      <c r="E33" s="49"/>
+      <c r="F33" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="G33" s="49"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B34" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="J7" s="11" t="s">
+      <c r="C34" s="29" t="s">
+        <v>185</v>
+      </c>
+      <c r="D34" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="E34" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="F34" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="G34" s="19" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="C35" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="K7" s="11" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="50" t="s">
-        <v>156</v>
-      </c>
-      <c r="C9" s="51"/>
-      <c r="D9" s="50" t="s">
-        <v>158</v>
-      </c>
-      <c r="E9" s="52"/>
-      <c r="F9" s="51"/>
-      <c r="G9" s="50" t="s">
-        <v>141</v>
-      </c>
-      <c r="H9" s="51"/>
-      <c r="I9" s="50" t="s">
-        <v>146</v>
-      </c>
-      <c r="J9" s="51"/>
-      <c r="K9" s="50" t="s">
-        <v>183</v>
-      </c>
-      <c r="L9" s="51"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B10" s="28" t="s">
-        <v>157</v>
-      </c>
-      <c r="C10" s="29" t="s">
-        <v>155</v>
-      </c>
-      <c r="D10" s="32" t="s">
-        <v>172</v>
-      </c>
-      <c r="E10" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="F10" s="27" t="s">
-        <v>138</v>
-      </c>
-      <c r="G10" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="H10" s="23" t="s">
-        <v>178</v>
-      </c>
-      <c r="I10" s="28" t="s">
-        <v>181</v>
-      </c>
-      <c r="J10" s="27" t="s">
-        <v>180</v>
-      </c>
-      <c r="K10" s="21" t="s">
-        <v>184</v>
-      </c>
-      <c r="L10" s="21" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>238</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="K11" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="L11" s="11" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="54" t="s">
-        <v>160</v>
-      </c>
-      <c r="D14" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="E14" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="F14" s="53" t="s">
-        <v>170</v>
-      </c>
-      <c r="G14" s="53"/>
-      <c r="H14" s="53"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="55"/>
-      <c r="D15" s="37" t="s">
-        <v>162</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="55"/>
-      <c r="D16" s="38" t="s">
-        <v>163</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="55"/>
-      <c r="D17" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>169</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="55"/>
-      <c r="D18" s="13" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="55"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="55"/>
-      <c r="E20" s="39" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="55"/>
-      <c r="E21" s="13" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="55"/>
-      <c r="E22" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="55"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="55"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="55"/>
-      <c r="E25" s="11" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="55"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="55"/>
-      <c r="E27" s="13" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="55"/>
-      <c r="E28" s="13" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="55"/>
-      <c r="E29" s="11" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="55"/>
-      <c r="E30" s="13" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="56"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B33" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="C33" s="30" t="s">
-        <v>158</v>
-      </c>
-      <c r="D33" s="50" t="s">
-        <v>194</v>
-      </c>
-      <c r="E33" s="51"/>
-      <c r="F33" s="50" t="s">
-        <v>183</v>
-      </c>
-      <c r="G33" s="51"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B34" s="29" t="s">
-        <v>155</v>
-      </c>
-      <c r="C34" s="32" t="s">
-        <v>190</v>
-      </c>
-      <c r="D34" s="21" t="s">
-        <v>192</v>
-      </c>
-      <c r="E34" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="F34" s="21" t="s">
-        <v>197</v>
-      </c>
-      <c r="G34" s="21" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="21" t="s">
+      <c r="D35" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="B35" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="C35" s="11" t="s">
+      <c r="E35" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="D35" s="11" t="s">
+      <c r="F35" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="E35" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="F35" s="11" t="s">
-        <v>198</v>
-      </c>
       <c r="G35" s="11" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B38" s="21" t="s">
+      <c r="B38" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="C38" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="D38" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="E38" s="19" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="B39" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="C38" s="21" t="s">
+      <c r="C39" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="E39" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="D38" s="21" t="s">
-        <v>219</v>
-      </c>
-      <c r="E38" s="21" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="21" t="s">
-        <v>211</v>
-      </c>
-      <c r="B39" s="11" t="s">
+    </row>
+    <row r="40" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="E40" s="38" t="s">
         <v>223</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="D39" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="E40" s="41" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
@@ -7597,7 +9133,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{511B7746-4A5E-454B-8602-7B4B353E7BEF}">
   <dimension ref="A1:Y20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -7608,171 +9144,171 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="26.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="42" t="s">
-        <v>205</v>
+      <c r="A1" s="39" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>206</v>
-      </c>
-      <c r="N3" s="43" t="s">
-        <v>264</v>
-      </c>
-      <c r="O3" s="43"/>
-      <c r="P3" s="43"/>
-      <c r="Q3" s="43"/>
-      <c r="R3" s="43"/>
-      <c r="S3" s="43"/>
-      <c r="T3" s="43"/>
-      <c r="U3" s="43"/>
-      <c r="V3" s="43"/>
-      <c r="W3" s="43"/>
+        <v>201</v>
+      </c>
+      <c r="N3" s="40" t="s">
+        <v>245</v>
+      </c>
+      <c r="O3" s="40"/>
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="40"/>
+      <c r="S3" s="40"/>
+      <c r="T3" s="40"/>
+      <c r="U3" s="40"/>
+      <c r="V3" s="40"/>
+      <c r="W3" s="40"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C4" t="s">
-        <v>252</v>
-      </c>
-      <c r="N4" s="44" t="s">
-        <v>265</v>
-      </c>
-      <c r="O4" s="43"/>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="43"/>
-      <c r="R4" s="43"/>
-      <c r="S4" s="43"/>
-      <c r="T4" s="43"/>
-      <c r="U4" s="43"/>
-      <c r="V4" s="43"/>
-      <c r="W4" s="43"/>
+        <v>233</v>
+      </c>
+      <c r="N4" s="41" t="s">
+        <v>246</v>
+      </c>
+      <c r="O4" s="40"/>
+      <c r="P4" s="40"/>
+      <c r="Q4" s="40"/>
+      <c r="R4" s="40"/>
+      <c r="S4" s="40"/>
+      <c r="T4" s="40"/>
+      <c r="U4" s="40"/>
+      <c r="V4" s="40"/>
+      <c r="W4" s="40"/>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C5" t="s">
-        <v>254</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6" spans="1:25" ht="21.75" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C6" t="s">
-        <v>269</v>
-      </c>
-      <c r="N6" s="45" t="s">
-        <v>256</v>
-      </c>
-      <c r="O6" s="46"/>
-      <c r="P6" s="46"/>
-      <c r="Q6" s="46"/>
-      <c r="R6" s="46"/>
-      <c r="S6" s="46"/>
-      <c r="T6" s="46"/>
-      <c r="U6" s="46"/>
-      <c r="V6" s="46"/>
-      <c r="W6" s="46"/>
-      <c r="X6" s="46"/>
-      <c r="Y6" s="46"/>
+        <v>250</v>
+      </c>
+      <c r="N6" s="42" t="s">
+        <v>237</v>
+      </c>
+      <c r="O6" s="43"/>
+      <c r="P6" s="43"/>
+      <c r="Q6" s="43"/>
+      <c r="R6" s="43"/>
+      <c r="S6" s="43"/>
+      <c r="T6" s="43"/>
+      <c r="U6" s="43"/>
+      <c r="V6" s="43"/>
+      <c r="W6" s="43"/>
+      <c r="X6" s="43"/>
+      <c r="Y6" s="43"/>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="N7" s="46"/>
-      <c r="O7" s="46"/>
-      <c r="P7" s="46"/>
-      <c r="Q7" s="46"/>
-      <c r="R7" s="46"/>
-      <c r="S7" s="46"/>
-      <c r="T7" s="46"/>
-      <c r="U7" s="46"/>
-      <c r="V7" s="46"/>
-      <c r="W7" s="46"/>
-      <c r="X7" s="46"/>
-      <c r="Y7" s="46"/>
+      <c r="N7" s="43"/>
+      <c r="O7" s="43"/>
+      <c r="P7" s="43"/>
+      <c r="Q7" s="43"/>
+      <c r="R7" s="43"/>
+      <c r="S7" s="43"/>
+      <c r="T7" s="43"/>
+      <c r="U7" s="43"/>
+      <c r="V7" s="43"/>
+      <c r="W7" s="43"/>
+      <c r="X7" s="43"/>
+      <c r="Y7" s="43"/>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>260</v>
-      </c>
-      <c r="N8" s="46" t="s">
-        <v>257</v>
-      </c>
-      <c r="O8" s="46"/>
-      <c r="P8" s="46"/>
-      <c r="Q8" s="46"/>
-      <c r="R8" s="46"/>
-      <c r="S8" s="46"/>
-      <c r="T8" s="46"/>
-      <c r="U8" s="46"/>
-      <c r="V8" s="46"/>
-      <c r="W8" s="46"/>
-      <c r="X8" s="46"/>
-      <c r="Y8" s="46"/>
+        <v>241</v>
+      </c>
+      <c r="N8" s="43" t="s">
+        <v>238</v>
+      </c>
+      <c r="O8" s="43"/>
+      <c r="P8" s="43"/>
+      <c r="Q8" s="43"/>
+      <c r="R8" s="43"/>
+      <c r="S8" s="43"/>
+      <c r="T8" s="43"/>
+      <c r="U8" s="43"/>
+      <c r="V8" s="43"/>
+      <c r="W8" s="43"/>
+      <c r="X8" s="43"/>
+      <c r="Y8" s="43"/>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
-        <v>253</v>
-      </c>
-      <c r="N9" s="47"/>
-      <c r="O9" s="46"/>
-      <c r="P9" s="46"/>
-      <c r="Q9" s="46"/>
-      <c r="R9" s="46"/>
-      <c r="S9" s="46"/>
-      <c r="T9" s="46"/>
-      <c r="U9" s="46"/>
-      <c r="V9" s="46"/>
-      <c r="W9" s="46"/>
-      <c r="X9" s="46"/>
-      <c r="Y9" s="46"/>
+        <v>234</v>
+      </c>
+      <c r="N9" s="44"/>
+      <c r="O9" s="43"/>
+      <c r="P9" s="43"/>
+      <c r="Q9" s="43"/>
+      <c r="R9" s="43"/>
+      <c r="S9" s="43"/>
+      <c r="T9" s="43"/>
+      <c r="U9" s="43"/>
+      <c r="V9" s="43"/>
+      <c r="W9" s="43"/>
+      <c r="X9" s="43"/>
+      <c r="Y9" s="43"/>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="N10" s="48" t="s">
-        <v>267</v>
-      </c>
-      <c r="O10" s="46"/>
-      <c r="P10" s="46"/>
-      <c r="Q10" s="46"/>
-      <c r="R10" s="46"/>
-      <c r="S10" s="46"/>
-      <c r="T10" s="46"/>
-      <c r="U10" s="46"/>
-      <c r="V10" s="46"/>
-      <c r="W10" s="46"/>
-      <c r="X10" s="46"/>
-      <c r="Y10" s="46"/>
+      <c r="N10" s="45" t="s">
+        <v>248</v>
+      </c>
+      <c r="O10" s="43"/>
+      <c r="P10" s="43"/>
+      <c r="Q10" s="43"/>
+      <c r="R10" s="43"/>
+      <c r="S10" s="43"/>
+      <c r="T10" s="43"/>
+      <c r="U10" s="43"/>
+      <c r="V10" s="43"/>
+      <c r="W10" s="43"/>
+      <c r="X10" s="43"/>
+      <c r="Y10" s="43"/>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>258</v>
-      </c>
-      <c r="N11" s="48" t="s">
-        <v>268</v>
-      </c>
-      <c r="O11" s="46"/>
-      <c r="P11" s="46"/>
-      <c r="Q11" s="46"/>
-      <c r="R11" s="46"/>
-      <c r="S11" s="46"/>
-      <c r="T11" s="46"/>
-      <c r="U11" s="46"/>
-      <c r="V11" s="46"/>
-      <c r="W11" s="46"/>
-      <c r="X11" s="46"/>
-      <c r="Y11" s="46"/>
+        <v>239</v>
+      </c>
+      <c r="N11" s="45" t="s">
+        <v>249</v>
+      </c>
+      <c r="O11" s="43"/>
+      <c r="P11" s="43"/>
+      <c r="Q11" s="43"/>
+      <c r="R11" s="43"/>
+      <c r="S11" s="43"/>
+      <c r="T11" s="43"/>
+      <c r="U11" s="43"/>
+      <c r="V11" s="43"/>
+      <c r="W11" s="43"/>
+      <c r="X11" s="43"/>
+      <c r="Y11" s="43"/>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="C12" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.3">
@@ -7780,17 +9316,17 @@
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>261</v>
+        <v>242</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="C15" t="s">
-        <v>262</v>
+        <v>243</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
-        <v>263</v>
+        <v>244</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
@@ -7798,12 +9334,12 @@
         <v>4</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
+        <v>240</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>266</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -7812,7 +9348,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FEA1851-41A0-400A-9D42-CA24EB0A5B33}">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
@@ -7832,49 +9368,49 @@
   <sheetData>
     <row r="2" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B2" s="14" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D2" s="16"/>
       <c r="H2" s="16" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B3" s="25">
+      <c r="B3" s="22">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H3" t="s">
         <v>90</v>
-      </c>
-      <c r="H3" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.3">
       <c r="E4" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="F4" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.3">
       <c r="E5" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.3">
       <c r="E6" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8" spans="2:19" x14ac:dyDescent="0.3">
@@ -7882,13 +9418,13 @@
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
-      </c>
-      <c r="E8" s="40" t="s">
-        <v>212</v>
+        <v>87</v>
+      </c>
+      <c r="E8" s="37" t="s">
+        <v>207</v>
       </c>
       <c r="H8" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.3">
@@ -7896,13 +9432,13 @@
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
-      </c>
-      <c r="F10" s="40" t="s">
-        <v>213</v>
+        <v>91</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>208</v>
       </c>
       <c r="H10" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.3">
@@ -7910,41 +9446,41 @@
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E12" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="H12" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J12" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" spans="2:19" x14ac:dyDescent="0.3">
       <c r="C13" t="s">
-        <v>99</v>
-      </c>
-      <c r="E13" s="40" t="s">
-        <v>214</v>
+        <v>94</v>
+      </c>
+      <c r="E13" s="37" t="s">
+        <v>209</v>
       </c>
       <c r="J13" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B15" s="25">
+      <c r="B15" s="22">
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H15" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="S15" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.3">
@@ -7955,18 +9491,18 @@
         <v>5.25</v>
       </c>
       <c r="C17" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="H17" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="S17" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="2:19" x14ac:dyDescent="0.3">
       <c r="S18" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="2:19" x14ac:dyDescent="0.3">
@@ -7974,31 +9510,31 @@
         <v>5.5</v>
       </c>
       <c r="C19" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E19" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="H19" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="2:19" x14ac:dyDescent="0.3">
       <c r="E20" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="S20" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22" spans="2:19" x14ac:dyDescent="0.3">
       <c r="D22" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="24" spans="2:19" x14ac:dyDescent="0.3">
       <c r="D24" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" spans="2:19" x14ac:dyDescent="0.3">
@@ -8006,60 +9542,60 @@
         <v>6</v>
       </c>
       <c r="C26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="2:19" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D27" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="E27" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="2:19" x14ac:dyDescent="0.3">
       <c r="C29" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D29" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30" spans="2:19" x14ac:dyDescent="0.3">
       <c r="D30" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32" spans="2:19" x14ac:dyDescent="0.3">
       <c r="C32" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D32" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C34" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D34" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C36" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D36" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D37" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.3">
@@ -8067,18 +9603,18 @@
         <v>7</v>
       </c>
       <c r="C39" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B41" s="36">
+      <c r="B41" s="33">
         <v>8</v>
       </c>
       <c r="C41" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D41" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.3">
@@ -8086,20 +9622,20 @@
         <v>9</v>
       </c>
       <c r="C43" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B45" s="49">
+      <c r="B45" s="46">
         <v>10</v>
       </c>
       <c r="C45" t="s">
-        <v>273</v>
+        <v>254</v>
       </c>
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C47" t="s">
-        <v>274</v>
+        <v>255</v>
       </c>
     </row>
   </sheetData>

--- a/Document/정책문서.xlsx
+++ b/Document/정책문서.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git_fork\ProjectShoot\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE523EAD-D810-4A5F-8C10-1CFCF9EBCD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E558F32E-01BF-419A-8E3E-C87A5283094E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="711" firstSheet="1" activeTab="3" xr2:uid="{F9E8F865-F741-4425-897D-555A2E4B3EBE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="711" firstSheet="1" activeTab="5" xr2:uid="{F9E8F865-F741-4425-897D-555A2E4B3EBE}"/>
   </bookViews>
   <sheets>
     <sheet name="깃포크 공부" sheetId="11" state="hidden" r:id="rId1"/>
     <sheet name="player" sheetId="3" r:id="rId2"/>
     <sheet name="enemy" sheetId="6" r:id="rId3"/>
-    <sheet name="Formation" sheetId="16" r:id="rId4"/>
-    <sheet name="Move_Pattern" sheetId="17" r:id="rId5"/>
-    <sheet name="생애주기" sheetId="13" r:id="rId6"/>
-    <sheet name="카메라 " sheetId="15" r:id="rId7"/>
-    <sheet name="개발요청" sheetId="12" r:id="rId8"/>
+    <sheet name="Spawn" sheetId="18" r:id="rId4"/>
+    <sheet name="Formation" sheetId="16" r:id="rId5"/>
+    <sheet name="Move_Pattern" sheetId="17" r:id="rId6"/>
+    <sheet name="생애주기" sheetId="13" r:id="rId7"/>
+    <sheet name="카메라 " sheetId="15" r:id="rId8"/>
+    <sheet name="개발요청" sheetId="12" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,204 +41,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>user</author>
-  </authors>
-  <commentList>
-    <comment ref="E38" authorId="0" shapeId="0" xr:uid="{6849FD8E-1256-4229-AD4B-FBC70E2BDB53}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>user:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>최대</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>스폰</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>일시</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>진행</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>멈춤
-시간</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>간의</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>간격은</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>유지되어야함</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="359">
   <si>
     <t>설명</t>
   </si>
@@ -1448,10 +1253,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SpwanZone_Id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Count</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1480,10 +1281,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>스폰 구역</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1492,22 +1289,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>스폰 위치</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bool</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Is_Random</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Enum</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1539,22 +1324,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Spawn_Zone (Link / Object)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>스폰 영역 박스 오브젝트를 기획자가 링크</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Is_Random (Bool / 체크박스)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>체크하면 영역 내 랜덤 배치, 체크를 해제하면 영역의 정중앙에 배치</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Count (int)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1579,27 +1348,243 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>zone 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zone 2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zone 3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Spacing (float): 기체 간 격차 간격 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ㄴ 대장기: 일반적으로 진형에서 가장 강한 유닛. 홀수의 경우 진형의 중앙에 위치</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">배치 순서의 경우 다음과 같음 (노랑: 대장기 파랑:호위기) </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">공약수가 많아서 나누기 좋아보임 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>640*1080</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Move_Pattern (행동 규칙)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">몬스터가 행동하는 형태 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>행동 종류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Spacing x (float)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Spawn (생성 규칙)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기체 간 가로 격차</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Spacing y (float)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기체 간 세로 격차</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">유닛이 생성되는 규칙 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">스폰은 그룹과 영역이 존재 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그룹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영역</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">생성 규칙을 통해 원활한 플레이 경험 제공 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영역을 관리하기 위한 개념. 시각적 실체는 존재하지 않음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유닛이 생성되는 위치값.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스폰 그룹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpwanGroup_Id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpawnGroup (Link / Object)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>group 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>group 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스폰그룹을 기획자가 링크</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">참조 이미지 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>몬스터가 의도와 목적을 가지고 행동하는 장면을 연출, 유저에게 더 나은 플레이 환경 제공</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">한 화면에서 생성될 수 있는 몬스터의 경우 최대 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">마리 </t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사전 생성된 타임라인에 맞춰서 몬스터가 생성, 이후 행동 패턴에 따라 행동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>적은 지정된 그룹의 하위 영역 중 랜덤한 위치로 스폰됨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>생성 규칙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>언제 생성?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>group 3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  ㄴ 해당 숫자는 개발 여건에 따라 변경 될 수 있음 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게임 씬 안에 최대 적 숫자에 도달한 경우 타임라인 지연</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  ㄴ 적이 죽은 경우 지연된 타임라인이 있는지 확인, 있다면 다시 진행 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">어디서 생성? </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> ㄴ 그룹의 하위 영역이 1개일 경우 해당 영역에서만 몬스터 생성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>행동 형태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">행동의 경우 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이동</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">과 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사격</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 두종류로 나눔 </t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동 종류</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1608,9 +1593,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="0.0"/>
+    <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1738,26 +1723,6 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF0066FF"/>
       <name val="맑은 고딕"/>
@@ -1773,8 +1738,56 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0066FF"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="4"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1823,8 +1836,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="35">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -2260,6 +2279,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -2269,7 +2319,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2414,122 +2464,233 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="33" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="34" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="23" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="24" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="13" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="37" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2540,12 +2701,12 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF79DCFF"/>
       <color rgb="FF0066FF"/>
       <color rgb="FFFF66CC"/>
       <color rgb="FFB2B5BA"/>
       <color rgb="FFFF99CC"/>
       <color rgb="FFC2E494"/>
-      <color rgb="FF79DCFF"/>
       <color rgb="FFA5B0C7"/>
       <color rgb="FF000000"/>
       <color rgb="FF162746"/>
@@ -3347,15 +3508,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
+      <xdr:colOff>171450</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
+      <xdr:colOff>180975</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3370,7 +3531,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16087725" y="4524375"/>
+          <a:off x="14944725" y="4533900"/>
           <a:ext cx="695325" cy="609600"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
@@ -5048,6 +5209,401 @@
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>66676</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>87712</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>561976</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1" descr="머니 아이돌 익스체인져 : 네이버 블로그">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E400590-0F9E-443A-9C63-A9FB608FD279}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect l="54774" t="42624" r="24749" b="7250"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="14154151" y="1525987"/>
+          <a:ext cx="495300" cy="893363"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>352424</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>114299</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="그림 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A68EF345-6732-477C-8B5D-2D650E6B4BDC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:srcRect l="50648" t="67693" r="43829" b="15960"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15125699" y="4743450"/>
+          <a:ext cx="447675" cy="742950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>371476</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>59137</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>180976</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="그림 13" descr="머니 아이돌 익스체인져 : 네이버 블로그">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0DBE13EE-DD50-A21C-81E4-A4A529DBC732}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect l="54774" t="42624" r="24749" b="7250"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="15830551" y="1497412"/>
+          <a:ext cx="495300" cy="893363"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>276226</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>144862</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>85726</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="그림 14" descr="머니 아이돌 익스체인져 : 네이버 블로그">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{739E1CB7-575A-8BA2-44CE-024A3D7CCDEC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect l="54774" t="42624" r="24749" b="7250"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="13677901" y="2002237"/>
+          <a:ext cx="495300" cy="893363"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>219076</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>144862</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>28576</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="그림 15" descr="머니 아이돌 익스체인져 : 네이버 블로그">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E301BAE1-7C32-6FD4-246B-39C8BEA5A0F3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect l="54774" t="42624" r="24749" b="7250"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="16363951" y="2002237"/>
+          <a:ext cx="495300" cy="893363"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>514351</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>125812</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>323851</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="그림 16" descr="머니 아이돌 익스체인져 : 네이버 블로그">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{214DA15E-4F90-C687-F28A-AF6498212E9A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect l="54774" t="42624" r="24749" b="7250"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="13916026" y="4078687"/>
+          <a:ext cx="495300" cy="893363"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>504824</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>266699</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="그림 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB829BA4-53B8-B904-5BA8-A7C12FF45224}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:srcRect l="50648" t="67693" r="43829" b="15960"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15963899" y="4219575"/>
+          <a:ext cx="447675" cy="742950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -5055,23 +5611,924 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>318052</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>28161</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>471486</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>24847</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>16565</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>638176</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="27" name="그룹 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45E8D2F8-25A4-E3B5-62B1-9B158F5A92FC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="6729411" y="2514600"/>
+          <a:ext cx="2909890" cy="3686175"/>
+          <a:chOff x="395286" y="2238375"/>
+          <a:chExt cx="3595690" cy="3686175"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="10" name="직사각형 9">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09EA633E-0BCA-DFED-AE6C-53D45D41358B}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="552450" y="2238375"/>
+            <a:ext cx="3248025" cy="3686175"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="76200">
+            <a:solidFill>
+              <a:srgbClr val="C00000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1100">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>적 제거 영역</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="12" name="직사각형 11">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0070BCF6-BACD-5065-D45E-BC262A5FE27B}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2786061" y="2324100"/>
+            <a:ext cx="909640" cy="314325"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="92D050"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1050">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>그룹</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1050">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>1</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1050" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>영역</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>1</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="13" name="직사각형 12">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{375CB94E-107E-565B-876B-55021BC6DE8E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1440458" y="3076575"/>
+            <a:ext cx="1575762" cy="2343150"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="accent5">
+              <a:lumMod val="20000"/>
+              <a:lumOff val="80000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1600">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>게임 화면</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="14" name="직사각형 13">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D50DBDA9-2B11-42B7-BED1-626B250A15E8}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2181225" y="4991100"/>
+            <a:ext cx="133350" cy="152400"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="16" name="직사각형 15">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04FE4860-BCFC-5AC3-F648-38AF1B485687}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2719386" y="2705100"/>
+            <a:ext cx="909640" cy="314325"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="92D050"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1050">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>그룹</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1050">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>1</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1050" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>영역</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>2</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="17" name="직사각형 16">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15AB5876-3885-12E0-8392-257AE3A6C73B}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1690686" y="2695575"/>
+            <a:ext cx="909640" cy="314325"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="92D050"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1050">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>그룹</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1050">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>1</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1050" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>영역</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>3</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="18" name="직사각형 17">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F31C4265-D518-4A01-B276-611AF442EB96}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="395286" y="3000375"/>
+            <a:ext cx="909640" cy="314325"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:lumMod val="20000"/>
+              <a:lumOff val="80000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1050">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>그룹</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1050">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>2</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1050" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>영역</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>1</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="21" name="직사각형 20">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6566F412-5122-2891-3408-6ED8EF6E0DDD}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="395286" y="3390900"/>
+            <a:ext cx="909640" cy="314325"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:lumMod val="20000"/>
+              <a:lumOff val="80000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1050">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>그룹</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1050">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>2</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1050" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>영역</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>2</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="22" name="직사각형 21">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C8B32AD-E19D-9B3F-A10B-41AFAB9A1D5F}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="395286" y="3781425"/>
+            <a:ext cx="909640" cy="314325"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:lumMod val="20000"/>
+              <a:lumOff val="80000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1050">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>그룹</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1050">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>2</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1050" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>영역</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>3</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="24" name="직사각형 23">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8884F29-E3E5-456C-BF72-4D007B8F6DD9}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1728786" y="5495925"/>
+            <a:ext cx="909640" cy="314325"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="00B050"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1050">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>그룹</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1050">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>3</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1050" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>영역</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>1</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="26" name="직사각형 25">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4762989-7A8E-C618-C906-B3F55022C3E0}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="3081336" y="3076575"/>
+            <a:ext cx="909640" cy="314325"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="92D050"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1050">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>그룹</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1050">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>1</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1050" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>영역</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>4</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="직사각형 9">
+        <xdr:cNvPr id="5" name="순서도: 수행의 시작/종료 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A543E9E-B357-68C8-51B1-61CF818DCD6C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AAAA9155-0A00-CC84-0862-8C2E01F17727}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5079,12 +6536,20 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14986552" y="4666422"/>
-          <a:ext cx="1081708" cy="402534"/>
+          <a:off x="9001125" y="4067175"/>
+          <a:ext cx="2095500" cy="1028700"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom prst="flowChartTerminator">
           <a:avLst/>
         </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="92D050"/>
+        </a:solidFill>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -5103,36 +6568,164 @@
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
-          <a:pPr algn="ctr"/>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
-            <a:t>생성영역</a:t>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1050">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>*</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1050">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>몬스터에게 그룹</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100"/>
-            <a:t>4</a:t>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1050">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1</a:t>
           </a:r>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1050" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>할당 시</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1050" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>영역 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1~4</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1050" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>에서 랜덤하게 생성</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1050" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>670892</xdr:colOff>
+      <xdr:colOff>318675</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>173935</xdr:rowOff>
+      <xdr:rowOff>145360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>364436</xdr:colOff>
+      <xdr:colOff>12219</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>140804</xdr:rowOff>
+      <xdr:rowOff>104260</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5147,8 +6740,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2178327" y="3776870"/>
-          <a:ext cx="381000" cy="380999"/>
+          <a:off x="1776000" y="3783910"/>
+          <a:ext cx="379344" cy="378000"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -5187,16 +6780,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>82827</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>409059</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>173935</xdr:rowOff>
+      <xdr:rowOff>145360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>463827</xdr:colOff>
+      <xdr:colOff>104259</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>140804</xdr:rowOff>
+      <xdr:rowOff>104260</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5211,8 +6804,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1590262" y="3776870"/>
-          <a:ext cx="381000" cy="380999"/>
+          <a:off x="1180584" y="3783910"/>
+          <a:ext cx="381000" cy="378000"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -5252,15 +6845,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>621197</xdr:colOff>
+      <xdr:colOff>226635</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>173935</xdr:rowOff>
+      <xdr:rowOff>145360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>314740</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>605978</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>140804</xdr:rowOff>
+      <xdr:rowOff>104260</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5275,8 +6868,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2816088" y="3776870"/>
-          <a:ext cx="381000" cy="380999"/>
+          <a:off x="2369760" y="3783910"/>
+          <a:ext cx="379343" cy="378000"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -5315,16 +6908,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>99393</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>70818</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>173935</xdr:rowOff>
+      <xdr:rowOff>145360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>480393</xdr:colOff>
+      <xdr:colOff>194643</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>140804</xdr:rowOff>
+      <xdr:rowOff>104260</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5339,8 +6932,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="919371" y="3776870"/>
-          <a:ext cx="381000" cy="380999"/>
+          <a:off x="585168" y="3783910"/>
+          <a:ext cx="381000" cy="378000"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -5380,15 +6973,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>563220</xdr:colOff>
+      <xdr:colOff>134595</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>173934</xdr:rowOff>
+      <xdr:rowOff>145360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>256764</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>513939</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>140803</xdr:rowOff>
+      <xdr:rowOff>104260</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5403,8 +6996,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3445568" y="3776869"/>
-          <a:ext cx="381000" cy="380999"/>
+          <a:off x="2963520" y="3783910"/>
+          <a:ext cx="379344" cy="378000"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -5444,7 +7037,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -6255,7 +7848,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -7139,17 +8732,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FD8A53F-EA3D-42A9-BC36-A057527E3A89}">
   <dimension ref="A1:P28"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="3" width="4.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="38.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="38.25">
       <c r="A1" s="21" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16">
       <c r="A3">
         <v>1</v>
       </c>
@@ -7163,7 +8756,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16">
       <c r="H4" t="s">
         <v>77</v>
       </c>
@@ -7171,12 +8764,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16">
       <c r="P5" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>2</v>
       </c>
@@ -7197,7 +8790,7 @@
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="A1:G38"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="3.75" customWidth="1"/>
     <col min="2" max="2" width="5.375" customWidth="1"/>
@@ -7207,17 +8800,17 @@
     <col min="6" max="6" width="64.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="26.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="26.25">
       <c r="A1" s="47" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="B3" s="8" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="B4" s="10" t="s">
         <v>7</v>
       </c>
@@ -7235,7 +8828,7 @@
       </c>
       <c r="G4" s="11"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="B5" s="11">
         <f t="shared" ref="B5:B12" si="0">ROW()-ROW($B$4)</f>
         <v>1</v>
@@ -7253,7 +8846,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="B6" s="11">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -7271,7 +8864,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="B7" s="11">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -7289,7 +8882,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="B8" s="11">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -7307,7 +8900,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="B9" s="11">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -7325,7 +8918,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="B10" s="11">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -7338,7 +8931,7 @@
       </c>
       <c r="E10" s="13"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="B11" s="11">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -7359,24 +8952,24 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="B12" s="11">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="E12" s="13"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="B13" s="11"/>
       <c r="E13" s="13"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="B14" s="8" t="s">
         <v>39</v>
       </c>
       <c r="E14" s="13"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="B15" s="10" t="s">
         <v>7</v>
       </c>
@@ -7388,7 +8981,7 @@
       </c>
       <c r="E15" s="13"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="B16" s="11">
         <f>ROW()-ROW($B$15)</f>
         <v>1</v>
@@ -7403,7 +8996,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:7">
       <c r="B17" s="11">
         <f>ROW()-ROW($B$15)</f>
         <v>2</v>
@@ -7413,16 +9006,16 @@
       </c>
       <c r="E17" s="13"/>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:7">
       <c r="E18" s="13"/>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:7">
       <c r="B19" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E19" s="13"/>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:7">
       <c r="B20" s="10" t="s">
         <v>7</v>
       </c>
@@ -7439,7 +9032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:7">
       <c r="B21" s="11">
         <f>ROW()-ROW($B$20)</f>
         <v>1</v>
@@ -7457,7 +9050,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:7">
       <c r="B22" s="11">
         <f t="shared" ref="B22:B26" si="1">ROW()-ROW($B$20)</f>
         <v>2</v>
@@ -7475,7 +9068,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:7">
       <c r="B23" s="11">
         <f t="shared" si="1"/>
         <v>3</v>
@@ -7493,7 +9086,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:7">
       <c r="B24" s="11">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -7511,7 +9104,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:7">
       <c r="B25" s="11">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -7524,7 +9117,7 @@
       </c>
       <c r="E25" s="13"/>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:7">
       <c r="B26" s="11">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -7545,12 +9138,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:7">
       <c r="B28" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:7">
       <c r="B29" s="10" t="s">
         <v>7</v>
       </c>
@@ -7568,7 +9161,7 @@
       </c>
       <c r="G29" s="11"/>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:7">
       <c r="B30" s="11">
         <f t="shared" ref="B30:B38" si="2">ROW()-ROW($B$29)</f>
         <v>1</v>
@@ -7583,7 +9176,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:7">
       <c r="B31" s="11">
         <f t="shared" si="2"/>
         <v>2</v>
@@ -7598,7 +9191,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:7">
       <c r="B32" s="11">
         <f t="shared" si="2"/>
         <v>3</v>
@@ -7613,7 +9206,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:6">
       <c r="B33" s="11">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -7628,7 +9221,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:6">
       <c r="B34" s="11">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -7640,7 +9233,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:6">
       <c r="B35" s="11">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -7649,7 +9242,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:6">
       <c r="B36" s="11">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -7658,7 +9251,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:6">
       <c r="B37" s="11">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -7673,7 +9266,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:6">
       <c r="B38" s="11">
         <f t="shared" si="2"/>
         <v>9</v>
@@ -7698,7 +9291,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:U35"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="3.625" customWidth="1"/>
     <col min="2" max="2" width="6.75" customWidth="1"/>
@@ -7708,13 +9301,13 @@
     <col min="16" max="16" width="4.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="26.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="26.25">
       <c r="A1" s="47" t="s">
         <v>46</v>
       </c>
       <c r="E1" s="12"/>
     </row>
-    <row r="2" spans="1:21" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:21" ht="27" thickBot="1">
       <c r="D2" s="9"/>
       <c r="E2" s="12"/>
       <c r="K2" t="s">
@@ -7724,7 +9317,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:21" ht="27" thickBot="1">
       <c r="D3" s="9"/>
       <c r="E3" s="12"/>
       <c r="K3" s="15">
@@ -7742,13 +9335,13 @@
       <c r="T3" s="1"/>
       <c r="U3" s="2"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21">
       <c r="K4" s="3"/>
       <c r="O4" s="4"/>
       <c r="Q4" s="3"/>
       <c r="U4" s="4"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21">
       <c r="B5" t="s">
         <v>47</v>
       </c>
@@ -7757,13 +9350,13 @@
       <c r="Q5" s="3"/>
       <c r="U5" s="4"/>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21">
       <c r="K6" s="3"/>
       <c r="O6" s="4"/>
       <c r="Q6" s="3"/>
       <c r="U6" s="4"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21">
       <c r="B7" s="14" t="s">
         <v>7</v>
       </c>
@@ -7781,7 +9374,7 @@
       <c r="Q7" s="3"/>
       <c r="U7" s="4"/>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21">
       <c r="B8" s="11">
         <v>1</v>
       </c>
@@ -7796,7 +9389,7 @@
       <c r="Q8" s="3"/>
       <c r="U8" s="4"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21">
       <c r="B9" s="11">
         <v>2</v>
       </c>
@@ -7812,19 +9405,19 @@
       <c r="Q9" s="3"/>
       <c r="U9" s="4"/>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21">
       <c r="K10" s="3"/>
       <c r="O10" s="4"/>
       <c r="Q10" s="3"/>
       <c r="U10" s="4"/>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21">
       <c r="K11" s="3"/>
       <c r="O11" s="4"/>
       <c r="Q11" s="3"/>
       <c r="U11" s="4"/>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21">
       <c r="B12" s="8" t="s">
         <v>57</v>
       </c>
@@ -7834,7 +9427,7 @@
       <c r="Q12" s="3"/>
       <c r="U12" s="4"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21">
       <c r="B13" s="10" t="s">
         <v>7</v>
       </c>
@@ -7855,7 +9448,7 @@
       <c r="Q13" s="3"/>
       <c r="U13" s="4"/>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21">
       <c r="B14" s="11">
         <f t="shared" ref="B14:B19" si="0">ROW()-ROW($B$13)</f>
         <v>1</v>
@@ -7874,7 +9467,7 @@
       <c r="Q14" s="3"/>
       <c r="U14" s="4"/>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21">
       <c r="B15" s="11">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -7893,7 +9486,7 @@
       <c r="Q15" s="3"/>
       <c r="U15" s="4"/>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21">
       <c r="B16" s="11">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -7913,7 +9506,7 @@
       <c r="Q16" s="3"/>
       <c r="U16" s="4"/>
     </row>
-    <row r="17" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:21">
       <c r="B17" s="11">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -7929,7 +9522,7 @@
       <c r="Q17" s="3"/>
       <c r="U17" s="4"/>
     </row>
-    <row r="18" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:21">
       <c r="B18" s="11">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -7945,32 +9538,29 @@
       <c r="Q18" s="3"/>
       <c r="U18" s="4"/>
     </row>
-    <row r="19" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B19" s="57">
+    <row r="19" spans="2:21">
+      <c r="B19" s="11">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C19" s="58" t="s">
+      <c r="C19" t="s">
         <v>63</v>
       </c>
-      <c r="D19" s="58"/>
-      <c r="E19" s="57" t="s">
+      <c r="E19" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="F19" s="58"/>
-      <c r="G19" s="58"/>
       <c r="K19" s="3"/>
       <c r="O19" s="4"/>
       <c r="Q19" s="3"/>
       <c r="U19" s="4"/>
     </row>
-    <row r="20" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:21">
       <c r="K20" s="3"/>
       <c r="O20" s="4"/>
       <c r="Q20" s="3"/>
       <c r="U20" s="4"/>
     </row>
-    <row r="21" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:21">
       <c r="B21" s="8" t="s">
         <v>67</v>
       </c>
@@ -7979,7 +9569,7 @@
       <c r="Q21" s="3"/>
       <c r="U21" s="4"/>
     </row>
-    <row r="22" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:21">
       <c r="B22" s="10" t="s">
         <v>7</v>
       </c>
@@ -8000,7 +9590,7 @@
       <c r="Q22" s="3"/>
       <c r="U22" s="4"/>
     </row>
-    <row r="23" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:21">
       <c r="B23" s="11">
         <f>ROW()-ROW($B$22)</f>
         <v>1</v>
@@ -8019,7 +9609,7 @@
       <c r="Q23" s="3"/>
       <c r="U23" s="4"/>
     </row>
-    <row r="24" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:21">
       <c r="B24" s="11">
         <f>ROW()-ROW($B$22)</f>
         <v>2</v>
@@ -8035,7 +9625,7 @@
       <c r="Q24" s="3"/>
       <c r="U24" s="4"/>
     </row>
-    <row r="25" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:21">
       <c r="B25" s="11">
         <f t="shared" ref="B25:B27" si="1">ROW()-ROW($B$22)</f>
         <v>3</v>
@@ -8048,7 +9638,7 @@
       <c r="Q25" s="3"/>
       <c r="U25" s="4"/>
     </row>
-    <row r="26" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:21">
       <c r="B26" s="11">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -8061,7 +9651,7 @@
       <c r="Q26" s="3"/>
       <c r="U26" s="4"/>
     </row>
-    <row r="27" spans="2:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:21" ht="17.25" thickBot="1">
       <c r="B27" s="11">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -8080,17 +9670,17 @@
       <c r="T27" s="6"/>
       <c r="U27" s="7"/>
     </row>
-    <row r="30" spans="2:21" ht="26.25" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:21" ht="26.25">
       <c r="B30" s="39" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="31" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:21">
       <c r="B31" s="14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:21">
       <c r="B32" s="11">
         <v>1</v>
       </c>
@@ -8098,7 +9688,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:3">
       <c r="B33" s="11">
         <v>2</v>
       </c>
@@ -8106,7 +9696,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:3">
       <c r="B34" s="11">
         <v>3</v>
       </c>
@@ -8114,7 +9704,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:3">
       <c r="B35" s="11">
         <v>4</v>
       </c>
@@ -8130,95 +9720,739 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90669897-7B19-41C3-ACE9-893F9F9C4143}">
-  <dimension ref="A1:P51"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5B6D67C-9882-4C75-80BA-1B180D5DF46B}">
+  <dimension ref="A1:U53"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="2.875" customWidth="1"/>
-    <col min="2" max="2" width="4.125" style="8" customWidth="1"/>
-    <col min="3" max="3" width="3.75" customWidth="1"/>
-    <col min="7" max="7" width="9" customWidth="1"/>
-    <col min="9" max="9" width="9" customWidth="1"/>
-    <col min="11" max="11" width="10.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="3" width="3.375" customWidth="1"/>
+    <col min="12" max="17" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="26.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="26.25">
       <c r="A1" s="47" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+      <c r="B1" s="8"/>
+    </row>
+    <row r="2" spans="1:17" ht="16.5" customHeight="1">
       <c r="A2" s="47"/>
-    </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="8"/>
+    </row>
+    <row r="3" spans="1:17" ht="16.5" customHeight="1">
       <c r="A3" s="47"/>
       <c r="B3" s="8" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" ht="16.5" customHeight="1">
+      <c r="A4" s="47"/>
+      <c r="B4" s="8"/>
+      <c r="C4" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="16.5" customHeight="1">
+      <c r="A5" s="47"/>
+      <c r="B5" s="8"/>
+    </row>
+    <row r="6" spans="1:17" ht="16.5" customHeight="1">
+      <c r="B6" s="8" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="16.5" customHeight="1">
+      <c r="B7" s="8"/>
+      <c r="C7" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="16.5" customHeight="1">
+      <c r="B8" s="8"/>
+    </row>
+    <row r="9" spans="1:17" ht="16.5" customHeight="1">
+      <c r="B9" s="8" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="16.5" customHeight="1">
+      <c r="B10" s="8"/>
+      <c r="C10" s="85" t="s">
+        <v>348</v>
+      </c>
+      <c r="L10" s="50" t="s">
+        <v>342</v>
+      </c>
+      <c r="M10" s="52"/>
+      <c r="N10" s="52"/>
+      <c r="O10" s="52"/>
+      <c r="P10" s="51"/>
+      <c r="Q10" s="51"/>
+    </row>
+    <row r="11" spans="1:17" ht="16.5" customHeight="1">
+      <c r="B11" s="8"/>
+      <c r="D11" t="s">
+        <v>345</v>
+      </c>
+      <c r="L11" s="74"/>
+      <c r="M11" s="75"/>
+      <c r="N11" s="75"/>
+      <c r="O11" s="75"/>
+      <c r="P11" s="75"/>
+      <c r="Q11" s="76"/>
+    </row>
+    <row r="12" spans="1:17" ht="16.5" customHeight="1">
+      <c r="B12" s="8"/>
+      <c r="L12" s="68"/>
+      <c r="M12" s="69"/>
+      <c r="N12" s="69"/>
+      <c r="O12" s="69"/>
+      <c r="P12" s="69"/>
+      <c r="Q12" s="70"/>
+    </row>
+    <row r="13" spans="1:17" ht="16.5" customHeight="1">
+      <c r="B13" s="8"/>
+      <c r="D13" t="s">
+        <v>344</v>
+      </c>
+      <c r="L13" s="68"/>
+      <c r="M13" s="69"/>
+      <c r="N13" s="69"/>
+      <c r="O13" s="69"/>
+      <c r="P13" s="69"/>
+      <c r="Q13" s="70"/>
+    </row>
+    <row r="14" spans="1:17" ht="16.5" customHeight="1">
+      <c r="B14" s="8"/>
+      <c r="D14" s="79" t="s">
+        <v>351</v>
+      </c>
+      <c r="L14" s="68"/>
+      <c r="M14" s="69"/>
+      <c r="N14" s="69"/>
+      <c r="O14" s="69"/>
+      <c r="P14" s="69"/>
+      <c r="Q14" s="70"/>
+    </row>
+    <row r="15" spans="1:17" ht="16.5" customHeight="1">
+      <c r="B15" s="8"/>
+      <c r="L15" s="68"/>
+      <c r="M15" s="69"/>
+      <c r="N15" s="69"/>
+      <c r="O15" s="69"/>
+      <c r="P15" s="69"/>
+      <c r="Q15" s="70"/>
+    </row>
+    <row r="16" spans="1:17" ht="16.5" customHeight="1">
+      <c r="B16" s="8"/>
+      <c r="D16" t="s">
+        <v>352</v>
+      </c>
+      <c r="L16" s="68"/>
+      <c r="M16" s="69"/>
+      <c r="N16" s="69"/>
+      <c r="O16" s="69"/>
+      <c r="P16" s="69"/>
+      <c r="Q16" s="70"/>
+    </row>
+    <row r="17" spans="2:17" ht="16.5" customHeight="1">
+      <c r="B17" s="8"/>
+      <c r="D17" t="s">
+        <v>353</v>
+      </c>
+      <c r="L17" s="68"/>
+      <c r="M17" s="69"/>
+      <c r="N17" s="69"/>
+      <c r="O17" s="69"/>
+      <c r="P17" s="69"/>
+      <c r="Q17" s="70"/>
+    </row>
+    <row r="18" spans="2:17" ht="16.5" customHeight="1">
+      <c r="B18" s="8"/>
+      <c r="L18" s="68"/>
+      <c r="M18" s="69"/>
+      <c r="N18" s="69"/>
+      <c r="O18" s="69"/>
+      <c r="P18" s="69"/>
+      <c r="Q18" s="70"/>
+    </row>
+    <row r="19" spans="2:17" ht="16.5" customHeight="1">
+      <c r="B19" s="8"/>
+      <c r="C19" s="85" t="s">
+        <v>354</v>
+      </c>
+      <c r="L19" s="68"/>
+      <c r="M19" s="69"/>
+      <c r="N19" s="69"/>
+      <c r="O19" s="69"/>
+      <c r="P19" s="69"/>
+      <c r="Q19" s="70"/>
+    </row>
+    <row r="20" spans="2:17" ht="16.5" customHeight="1">
+      <c r="B20" s="8"/>
+      <c r="D20" t="s">
+        <v>346</v>
+      </c>
+      <c r="L20" s="68"/>
+      <c r="M20" s="69"/>
+      <c r="N20" s="69"/>
+      <c r="O20" s="69"/>
+      <c r="P20" s="69"/>
+      <c r="Q20" s="70"/>
+    </row>
+    <row r="21" spans="2:17" ht="16.5" customHeight="1">
+      <c r="B21" s="8"/>
+      <c r="D21" t="s">
+        <v>355</v>
+      </c>
+      <c r="L21" s="68"/>
+      <c r="M21" s="69"/>
+      <c r="N21" s="69"/>
+      <c r="O21" s="69"/>
+      <c r="P21" s="69"/>
+      <c r="Q21" s="70"/>
+    </row>
+    <row r="22" spans="2:17" ht="16.5" customHeight="1">
+      <c r="B22" s="8"/>
+      <c r="L22" s="68"/>
+      <c r="M22" s="69"/>
+      <c r="N22" s="69"/>
+      <c r="O22" s="69"/>
+      <c r="P22" s="69"/>
+      <c r="Q22" s="70"/>
+    </row>
+    <row r="23" spans="2:17" ht="16.5" customHeight="1">
+      <c r="B23" s="8"/>
+      <c r="D23" t="s">
+        <v>330</v>
+      </c>
+      <c r="L23" s="68"/>
+      <c r="M23" s="69"/>
+      <c r="N23" s="69"/>
+      <c r="O23" s="69"/>
+      <c r="P23" s="69"/>
+      <c r="Q23" s="70"/>
+    </row>
+    <row r="24" spans="2:17" ht="16.5" customHeight="1">
+      <c r="B24" s="8"/>
+      <c r="L24" s="68"/>
+      <c r="M24" s="69"/>
+      <c r="N24" s="69"/>
+      <c r="O24" s="69"/>
+      <c r="P24" s="69"/>
+      <c r="Q24" s="70"/>
+    </row>
+    <row r="25" spans="2:17" ht="16.5" customHeight="1">
+      <c r="B25" s="8"/>
+      <c r="D25" t="s">
+        <v>332</v>
+      </c>
+      <c r="E25" t="s">
+        <v>335</v>
+      </c>
+      <c r="L25" s="68"/>
+      <c r="M25" s="69"/>
+      <c r="N25" s="69"/>
+      <c r="O25" s="69"/>
+      <c r="P25" s="69"/>
+      <c r="Q25" s="70"/>
+    </row>
+    <row r="26" spans="2:17" ht="16.5" customHeight="1">
+      <c r="B26" s="8"/>
+      <c r="D26" t="s">
+        <v>331</v>
+      </c>
+      <c r="E26" t="s">
+        <v>334</v>
+      </c>
+      <c r="L26" s="68"/>
+      <c r="M26" s="69"/>
+      <c r="N26" s="69"/>
+      <c r="O26" s="69"/>
+      <c r="P26" s="69"/>
+      <c r="Q26" s="70"/>
+    </row>
+    <row r="27" spans="2:17" ht="16.5" customHeight="1">
+      <c r="B27" s="8"/>
+      <c r="L27" s="68"/>
+      <c r="M27" s="69"/>
+      <c r="N27" s="69"/>
+      <c r="O27" s="69"/>
+      <c r="P27" s="69"/>
+      <c r="Q27" s="70"/>
+    </row>
+    <row r="28" spans="2:17" ht="16.5" customHeight="1">
+      <c r="B28" s="8"/>
+      <c r="L28" s="68"/>
+      <c r="M28" s="69"/>
+      <c r="N28" s="69"/>
+      <c r="O28" s="69"/>
+      <c r="P28" s="69"/>
+      <c r="Q28" s="70"/>
+    </row>
+    <row r="29" spans="2:17" ht="16.5" customHeight="1">
+      <c r="B29" s="8"/>
+      <c r="L29" s="68"/>
+      <c r="M29" s="69"/>
+      <c r="N29" s="69"/>
+      <c r="O29" s="69"/>
+      <c r="P29" s="69"/>
+      <c r="Q29" s="70"/>
+    </row>
+    <row r="30" spans="2:17" ht="16.5" customHeight="1">
+      <c r="B30" s="8"/>
+      <c r="L30" s="71"/>
+      <c r="M30" s="72"/>
+      <c r="N30" s="72"/>
+      <c r="O30" s="72"/>
+      <c r="P30" s="72"/>
+      <c r="Q30" s="73"/>
+    </row>
+    <row r="33" spans="2:21">
+      <c r="B33" s="8"/>
+    </row>
+    <row r="34" spans="2:21">
+      <c r="B34" s="8" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21">
+      <c r="B35" s="8"/>
+      <c r="C35" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="36" spans="2:21" ht="17.25" thickBot="1">
+      <c r="B36" s="8"/>
+    </row>
+    <row r="37" spans="2:21">
+      <c r="B37" s="8"/>
+      <c r="D37" s="27" t="s">
+        <v>304</v>
+      </c>
+      <c r="E37" s="77" t="s">
+        <v>284</v>
+      </c>
+      <c r="F37" s="113"/>
+      <c r="G37" s="52" t="s">
+        <v>285</v>
+      </c>
+      <c r="H37" s="52"/>
+      <c r="I37" s="77" t="s">
+        <v>336</v>
+      </c>
+      <c r="J37" s="84"/>
+      <c r="K37" s="107"/>
+      <c r="L37" s="51" t="s">
+        <v>287</v>
+      </c>
+      <c r="M37" s="51"/>
+      <c r="N37" s="49" t="s">
+        <v>286</v>
+      </c>
+      <c r="O37" s="51"/>
+      <c r="P37" s="49" t="s">
+        <v>288</v>
+      </c>
+      <c r="Q37" s="51"/>
+      <c r="R37" s="49" t="s">
+        <v>289</v>
+      </c>
+      <c r="S37" s="52"/>
+      <c r="T37" s="49" t="s">
+        <v>290</v>
+      </c>
+      <c r="U37" s="51"/>
+    </row>
+    <row r="38" spans="2:21">
+      <c r="B38" s="8"/>
+      <c r="D38" s="27" t="s">
+        <v>300</v>
+      </c>
+      <c r="E38" s="108" t="s">
+        <v>301</v>
+      </c>
+      <c r="F38" s="114"/>
+      <c r="G38" s="52" t="s">
+        <v>316</v>
+      </c>
+      <c r="H38" s="52"/>
+      <c r="I38" s="108" t="s">
+        <v>316</v>
+      </c>
+      <c r="J38" s="81"/>
+      <c r="K38" s="109"/>
+      <c r="L38" s="51" t="s">
+        <v>303</v>
+      </c>
+      <c r="M38" s="51"/>
+      <c r="N38" s="49" t="s">
+        <v>300</v>
+      </c>
+      <c r="O38" s="51"/>
+      <c r="P38" s="49" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q38" s="51"/>
+      <c r="R38" s="49" t="s">
+        <v>301</v>
+      </c>
+      <c r="S38" s="52"/>
+      <c r="T38" s="49" t="s">
+        <v>302</v>
+      </c>
+      <c r="U38" s="51"/>
+    </row>
+    <row r="39" spans="2:21" ht="17.25" thickBot="1">
+      <c r="B39" s="8"/>
+      <c r="D39" s="27" t="s">
+        <v>291</v>
+      </c>
+      <c r="E39" s="78" t="s">
+        <v>292</v>
+      </c>
+      <c r="F39" s="115"/>
+      <c r="G39" s="112" t="s">
+        <v>309</v>
+      </c>
+      <c r="H39" s="52"/>
+      <c r="I39" s="78" t="s">
+        <v>337</v>
+      </c>
+      <c r="J39" s="110"/>
+      <c r="K39" s="111"/>
+      <c r="L39" s="51" t="s">
+        <v>294</v>
+      </c>
+      <c r="M39" s="51"/>
+      <c r="N39" s="49" t="s">
+        <v>293</v>
+      </c>
+      <c r="O39" s="51"/>
+      <c r="P39" s="49" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q39" s="51"/>
+      <c r="R39" s="49" t="s">
+        <v>296</v>
+      </c>
+      <c r="S39" s="52"/>
+      <c r="T39" s="49" t="s">
+        <v>297</v>
+      </c>
+      <c r="U39" s="51"/>
+    </row>
+    <row r="40" spans="2:21">
+      <c r="B40" s="8"/>
+      <c r="D40" s="53">
+        <f>ROW()-ROW($D$39)</f>
+        <v>1</v>
+      </c>
+      <c r="E40" s="82">
+        <v>3</v>
+      </c>
+      <c r="F40" s="80"/>
+      <c r="G40" s="80" t="s">
+        <v>298</v>
+      </c>
+      <c r="H40" s="80"/>
+      <c r="I40" s="80" t="s">
+        <v>339</v>
+      </c>
+      <c r="J40" s="80"/>
+      <c r="K40" s="80"/>
+      <c r="L40" s="80" t="s">
+        <v>299</v>
+      </c>
+      <c r="M40" s="80"/>
+      <c r="N40" s="80">
+        <v>5</v>
+      </c>
+      <c r="O40" s="80"/>
+      <c r="P40" s="80">
+        <v>30</v>
+      </c>
+      <c r="Q40" s="80"/>
+      <c r="R40" s="80">
+        <v>30</v>
+      </c>
+      <c r="S40" s="80"/>
+      <c r="T40" s="80" t="s">
+        <v>302</v>
+      </c>
+      <c r="U40" s="86"/>
+    </row>
+    <row r="41" spans="2:21">
+      <c r="B41" s="8"/>
+      <c r="D41" s="53">
+        <f t="shared" ref="D41:D43" si="0">ROW()-ROW($D$39)</f>
+        <v>2</v>
+      </c>
+      <c r="E41" s="80" t="s">
+        <v>302</v>
+      </c>
+      <c r="F41" s="80"/>
+      <c r="G41" s="80" t="s">
+        <v>302</v>
+      </c>
+      <c r="H41" s="80"/>
+      <c r="I41" s="80" t="s">
+        <v>340</v>
+      </c>
+      <c r="J41" s="80"/>
+      <c r="K41" s="80"/>
+      <c r="L41" s="80" t="s">
+        <v>302</v>
+      </c>
+      <c r="M41" s="80"/>
+      <c r="N41" s="83"/>
+      <c r="O41" s="67"/>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="67"/>
+      <c r="R41" s="83"/>
+      <c r="S41" s="67"/>
+      <c r="T41" s="83"/>
+      <c r="U41" s="54"/>
+    </row>
+    <row r="42" spans="2:21">
+      <c r="B42" s="8"/>
+      <c r="D42" s="53">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="E42" s="80" t="s">
+        <v>302</v>
+      </c>
+      <c r="F42" s="80"/>
+      <c r="G42" s="80" t="s">
+        <v>302</v>
+      </c>
+      <c r="H42" s="80"/>
+      <c r="I42" s="80" t="s">
+        <v>349</v>
+      </c>
+      <c r="J42" s="80"/>
+      <c r="K42" s="80"/>
+      <c r="L42" s="80" t="s">
+        <v>302</v>
+      </c>
+      <c r="M42" s="80"/>
+      <c r="N42" s="83"/>
+      <c r="O42" s="67"/>
+      <c r="P42" s="83"/>
+      <c r="Q42" s="67"/>
+      <c r="R42" s="83"/>
+      <c r="S42" s="67"/>
+      <c r="T42" s="83"/>
+      <c r="U42" s="54"/>
+    </row>
+    <row r="43" spans="2:21">
+      <c r="B43" s="8"/>
+      <c r="D43" s="55">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="E43" s="56" t="s">
+        <v>302</v>
+      </c>
+      <c r="F43" s="56"/>
+      <c r="G43" s="56" t="s">
+        <v>302</v>
+      </c>
+      <c r="H43" s="56"/>
+      <c r="I43" s="56" t="s">
+        <v>302</v>
+      </c>
+      <c r="J43" s="56"/>
+      <c r="K43" s="56"/>
+      <c r="L43" s="57" t="s">
+        <v>350</v>
+      </c>
+      <c r="M43" s="57"/>
+      <c r="N43" s="57"/>
+      <c r="O43" s="57"/>
+      <c r="P43" s="57"/>
+      <c r="Q43" s="57"/>
+      <c r="R43" s="57"/>
+      <c r="S43" s="57"/>
+      <c r="T43" s="57"/>
+      <c r="U43" s="58"/>
+    </row>
+    <row r="44" spans="2:21">
+      <c r="B44" s="8"/>
+    </row>
+    <row r="45" spans="2:21">
+      <c r="B45" s="8"/>
+      <c r="D45" t="s">
+        <v>306</v>
+      </c>
+      <c r="G45" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21">
+      <c r="B46" s="8"/>
+      <c r="D46" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21">
+      <c r="B47" s="8"/>
+      <c r="D47" t="s">
+        <v>315</v>
+      </c>
+      <c r="G47" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21">
+      <c r="B48" s="8"/>
+      <c r="D48" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9">
+      <c r="B49" s="8"/>
+      <c r="D49" t="s">
+        <v>313</v>
+      </c>
+      <c r="G49" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9">
+      <c r="B50" s="8"/>
+      <c r="D50" t="s">
+        <v>311</v>
+      </c>
+      <c r="G50" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9">
+      <c r="B51" s="8"/>
+      <c r="D51" s="18" t="s">
+        <v>324</v>
+      </c>
+      <c r="E51" s="18"/>
+      <c r="F51" s="18"/>
+      <c r="G51" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="H51" s="18"/>
+      <c r="I51" s="18"/>
+    </row>
+    <row r="52" spans="2:9">
+      <c r="B52" s="8"/>
+      <c r="D52" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="E52" s="18"/>
+      <c r="F52" s="18"/>
+      <c r="G52" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="H52" s="18"/>
+      <c r="I52" s="18"/>
+    </row>
+    <row r="53" spans="2:9">
+      <c r="B53" s="8"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90669897-7B19-41C3-ACE9-893F9F9C4143}">
+  <dimension ref="A1:V51"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="3.375" customWidth="1"/>
+    <col min="2" max="2" width="3.375" style="8" customWidth="1"/>
+    <col min="3" max="3" width="3.375" customWidth="1"/>
+    <col min="7" max="7" width="9" customWidth="1"/>
+    <col min="9" max="9" width="9" customWidth="1"/>
+    <col min="11" max="15" width="9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="26.25">
+      <c r="A1" s="47" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A2" s="47"/>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A3" s="47"/>
+      <c r="B3" s="8" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1">
       <c r="A4" s="47"/>
       <c r="C4" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1">
       <c r="A5" s="47"/>
       <c r="C5" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1">
       <c r="A6" s="47"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="B7" s="8" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="C8" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4">
       <c r="B10" s="8" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4">
       <c r="C11" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4">
       <c r="C13" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4">
       <c r="D14" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="D15" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C17" s="56" t="s">
-        <v>331</v>
-      </c>
-      <c r="D17" s="56"/>
-      <c r="E17" s="56"/>
-      <c r="F17" s="56"/>
-      <c r="G17" s="56"/>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9">
+      <c r="C17" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9">
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
@@ -8227,7 +10461,7 @@
       <c r="H18" s="8"/>
       <c r="I18" s="8"/>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9">
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
@@ -8236,7 +10470,7 @@
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:9">
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
@@ -8245,7 +10479,7 @@
       <c r="H20" s="8"/>
       <c r="I20" s="8"/>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:9">
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
@@ -8254,7 +10488,7 @@
       <c r="H21" s="8"/>
       <c r="I21" s="8"/>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:9">
       <c r="C22" s="18" t="s">
         <v>275</v>
       </c>
@@ -8264,7 +10498,7 @@
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:9">
       <c r="C23" s="18"/>
       <c r="D23" s="18" t="s">
         <v>276</v>
@@ -8274,24 +10508,24 @@
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:9">
       <c r="B25" s="8" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:9">
       <c r="C26" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="55" t="s">
+      <c r="D26" s="48" t="s">
         <v>259</v>
       </c>
-      <c r="E26" s="55"/>
-      <c r="F26" s="55" t="s">
+      <c r="E26" s="48"/>
+      <c r="F26" s="48" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:9">
       <c r="C27" s="11">
         <f>ROW()-ROW($C$26)</f>
         <v>1</v>
@@ -8303,9 +10537,9 @@
         <v>274</v>
       </c>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:9">
       <c r="C28" s="11">
-        <f t="shared" ref="C28:C31" si="0">ROW()-ROW($C$26)</f>
+        <f>ROW()-ROW($C$26)</f>
         <v>2</v>
       </c>
       <c r="D28" t="s">
@@ -8315,343 +10549,489 @@
         <v>277</v>
       </c>
     </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:9">
       <c r="C29" s="11">
+        <f>ROW()-ROW($C$26)</f>
+        <v>3</v>
+      </c>
+      <c r="D29" t="s">
+        <v>263</v>
+      </c>
+      <c r="F29" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9">
+      <c r="C30" s="11">
+        <f>ROW()-ROW($C$26)</f>
+        <v>4</v>
+      </c>
+      <c r="D30" t="s">
+        <v>264</v>
+      </c>
+      <c r="F30" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9">
+      <c r="C31" s="11">
+        <f>ROW()-ROW($C$26)</f>
+        <v>5</v>
+      </c>
+      <c r="D31" t="s">
+        <v>261</v>
+      </c>
+      <c r="F31" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21">
+      <c r="B33" s="8" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21">
+      <c r="C34" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" ht="17.25" thickBot="1"/>
+    <row r="36" spans="2:21">
+      <c r="D36" s="97" t="s">
+        <v>304</v>
+      </c>
+      <c r="E36" s="89" t="s">
+        <v>284</v>
+      </c>
+      <c r="F36" s="90"/>
+      <c r="G36" s="89" t="s">
+        <v>285</v>
+      </c>
+      <c r="H36" s="90"/>
+      <c r="I36" s="105" t="s">
+        <v>336</v>
+      </c>
+      <c r="J36" s="105"/>
+      <c r="K36" s="106"/>
+      <c r="L36" s="116" t="s">
+        <v>287</v>
+      </c>
+      <c r="M36" s="87"/>
+      <c r="N36" s="87" t="s">
+        <v>286</v>
+      </c>
+      <c r="O36" s="87"/>
+      <c r="P36" s="87" t="s">
+        <v>288</v>
+      </c>
+      <c r="Q36" s="87"/>
+      <c r="R36" s="87" t="s">
+        <v>289</v>
+      </c>
+      <c r="S36" s="117"/>
+      <c r="T36" s="91" t="s">
+        <v>290</v>
+      </c>
+      <c r="U36" s="91"/>
+    </row>
+    <row r="37" spans="2:21">
+      <c r="D37" s="97" t="s">
+        <v>300</v>
+      </c>
+      <c r="E37" s="89" t="s">
+        <v>301</v>
+      </c>
+      <c r="F37" s="90"/>
+      <c r="G37" s="89" t="s">
+        <v>316</v>
+      </c>
+      <c r="H37" s="90"/>
+      <c r="I37" s="105" t="s">
+        <v>316</v>
+      </c>
+      <c r="J37" s="105"/>
+      <c r="K37" s="106"/>
+      <c r="L37" s="118" t="s">
+        <v>303</v>
+      </c>
+      <c r="M37" s="88"/>
+      <c r="N37" s="88" t="s">
+        <v>300</v>
+      </c>
+      <c r="O37" s="88"/>
+      <c r="P37" s="88" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q37" s="88"/>
+      <c r="R37" s="88" t="s">
+        <v>301</v>
+      </c>
+      <c r="S37" s="119"/>
+      <c r="T37" s="91" t="s">
+        <v>302</v>
+      </c>
+      <c r="U37" s="91"/>
+    </row>
+    <row r="38" spans="2:21" ht="17.25" thickBot="1">
+      <c r="D38" s="97" t="s">
+        <v>291</v>
+      </c>
+      <c r="E38" s="92" t="s">
+        <v>292</v>
+      </c>
+      <c r="F38" s="90"/>
+      <c r="G38" s="92" t="s">
+        <v>309</v>
+      </c>
+      <c r="H38" s="90"/>
+      <c r="I38" s="105" t="s">
+        <v>337</v>
+      </c>
+      <c r="J38" s="105"/>
+      <c r="K38" s="106"/>
+      <c r="L38" s="120" t="s">
+        <v>294</v>
+      </c>
+      <c r="M38" s="121"/>
+      <c r="N38" s="121" t="s">
+        <v>293</v>
+      </c>
+      <c r="O38" s="121"/>
+      <c r="P38" s="121" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q38" s="121"/>
+      <c r="R38" s="121" t="s">
+        <v>296</v>
+      </c>
+      <c r="S38" s="122"/>
+      <c r="T38" s="91" t="s">
+        <v>297</v>
+      </c>
+      <c r="U38" s="91"/>
+    </row>
+    <row r="39" spans="2:21">
+      <c r="D39" s="98">
+        <f>ROW()-ROW($D$38)</f>
+        <v>1</v>
+      </c>
+      <c r="E39" s="93">
+        <v>3</v>
+      </c>
+      <c r="F39" s="94"/>
+      <c r="G39" s="94" t="s">
+        <v>298</v>
+      </c>
+      <c r="H39" s="94"/>
+      <c r="I39" s="94" t="s">
+        <v>339</v>
+      </c>
+      <c r="J39" s="94"/>
+      <c r="K39" s="94"/>
+      <c r="L39" s="94" t="s">
+        <v>299</v>
+      </c>
+      <c r="M39" s="94"/>
+      <c r="N39" s="94">
+        <v>5</v>
+      </c>
+      <c r="O39" s="94"/>
+      <c r="P39" s="94">
+        <v>30</v>
+      </c>
+      <c r="Q39" s="94"/>
+      <c r="R39" s="94">
+        <v>30</v>
+      </c>
+      <c r="S39" s="94"/>
+      <c r="T39" s="94" t="s">
+        <v>302</v>
+      </c>
+      <c r="U39" s="99"/>
+    </row>
+    <row r="40" spans="2:21">
+      <c r="D40" s="98">
+        <f t="shared" ref="D40:D42" si="0">ROW()-ROW($D$38)</f>
+        <v>2</v>
+      </c>
+      <c r="E40" s="94" t="s">
+        <v>302</v>
+      </c>
+      <c r="F40" s="94"/>
+      <c r="G40" s="94" t="s">
+        <v>302</v>
+      </c>
+      <c r="H40" s="94"/>
+      <c r="I40" s="94" t="s">
+        <v>340</v>
+      </c>
+      <c r="J40" s="94"/>
+      <c r="K40" s="94"/>
+      <c r="L40" s="94" t="s">
+        <v>302</v>
+      </c>
+      <c r="M40" s="94"/>
+      <c r="N40" s="95"/>
+      <c r="O40" s="96"/>
+      <c r="P40" s="95"/>
+      <c r="Q40" s="96"/>
+      <c r="R40" s="95"/>
+      <c r="S40" s="96"/>
+      <c r="T40" s="95"/>
+      <c r="U40" s="100"/>
+    </row>
+    <row r="41" spans="2:21">
+      <c r="D41" s="98">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D29" t="s">
-        <v>263</v>
-      </c>
-      <c r="F29" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C30" s="11">
+      <c r="E41" s="94" t="s">
+        <v>302</v>
+      </c>
+      <c r="F41" s="94"/>
+      <c r="G41" s="94" t="s">
+        <v>302</v>
+      </c>
+      <c r="H41" s="94"/>
+      <c r="I41" s="94" t="s">
+        <v>349</v>
+      </c>
+      <c r="J41" s="94"/>
+      <c r="K41" s="94"/>
+      <c r="L41" s="94" t="s">
+        <v>302</v>
+      </c>
+      <c r="M41" s="94"/>
+      <c r="N41" s="95"/>
+      <c r="O41" s="96"/>
+      <c r="P41" s="95"/>
+      <c r="Q41" s="96"/>
+      <c r="R41" s="95"/>
+      <c r="S41" s="96"/>
+      <c r="T41" s="95"/>
+      <c r="U41" s="100"/>
+    </row>
+    <row r="42" spans="2:21">
+      <c r="D42" s="101">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="D30" t="s">
-        <v>264</v>
-      </c>
-      <c r="F30" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C31" s="11">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="D31" t="s">
-        <v>261</v>
-      </c>
-      <c r="F31" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B33" s="8" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C34" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="35" spans="2:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="36" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D36" s="19" t="s">
-        <v>309</v>
-      </c>
-      <c r="E36" s="60" t="s">
-        <v>284</v>
-      </c>
-      <c r="F36" s="61"/>
-      <c r="G36" s="60" t="s">
-        <v>285</v>
-      </c>
-      <c r="H36" s="61"/>
-      <c r="I36" s="59" t="s">
-        <v>301</v>
-      </c>
-      <c r="J36" s="62"/>
-      <c r="K36" s="60" t="s">
-        <v>304</v>
-      </c>
-      <c r="L36" s="63" t="s">
-        <v>287</v>
-      </c>
-      <c r="M36" s="64" t="s">
-        <v>286</v>
-      </c>
-      <c r="N36" s="64" t="s">
-        <v>288</v>
-      </c>
-      <c r="O36" s="65" t="s">
-        <v>289</v>
-      </c>
-      <c r="P36" s="20" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D37" s="19" t="s">
+      <c r="E42" s="102" t="s">
         <v>302</v>
       </c>
-      <c r="E37" s="60" t="s">
-        <v>303</v>
-      </c>
-      <c r="F37" s="61"/>
-      <c r="G37" s="60" t="s">
-        <v>325</v>
-      </c>
-      <c r="H37" s="61"/>
-      <c r="I37" s="60" t="s">
-        <v>325</v>
-      </c>
-      <c r="J37" s="62"/>
-      <c r="K37" s="60" t="s">
+      <c r="F42" s="102"/>
+      <c r="G42" s="102" t="s">
+        <v>302</v>
+      </c>
+      <c r="H42" s="102"/>
+      <c r="I42" s="102" t="s">
+        <v>302</v>
+      </c>
+      <c r="J42" s="102"/>
+      <c r="K42" s="102"/>
+      <c r="L42" s="103" t="s">
+        <v>350</v>
+      </c>
+      <c r="M42" s="103"/>
+      <c r="N42" s="103"/>
+      <c r="O42" s="103"/>
+      <c r="P42" s="103"/>
+      <c r="Q42" s="103"/>
+      <c r="R42" s="103"/>
+      <c r="S42" s="103"/>
+      <c r="T42" s="103"/>
+      <c r="U42" s="104"/>
+    </row>
+    <row r="44" spans="2:21">
+      <c r="D44" t="s">
+        <v>306</v>
+      </c>
+      <c r="G44" t="s">
         <v>305</v>
       </c>
-      <c r="L37" s="66" t="s">
+    </row>
+    <row r="45" spans="2:21">
+      <c r="D45" s="18" t="s">
+        <v>307</v>
+      </c>
+      <c r="G45" t="s">
         <v>308</v>
       </c>
-      <c r="M37" s="67" t="s">
-        <v>302</v>
-      </c>
-      <c r="N37" s="67" t="s">
-        <v>303</v>
-      </c>
-      <c r="O37" s="68" t="s">
-        <v>303</v>
-      </c>
-      <c r="P37" s="20"/>
-    </row>
-    <row r="38" spans="2:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D38" s="19" t="s">
-        <v>291</v>
-      </c>
-      <c r="E38" s="60" t="s">
-        <v>292</v>
-      </c>
-      <c r="F38" s="61"/>
-      <c r="G38" s="86" t="s">
+    </row>
+    <row r="46" spans="2:21">
+      <c r="D46" s="18" t="s">
+        <v>315</v>
+      </c>
+      <c r="G46" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21">
+      <c r="D47" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="G47" s="18" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21">
+      <c r="D48" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="G48" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="H38" s="61"/>
-      <c r="I38" s="59" t="s">
-        <v>293</v>
-      </c>
-      <c r="J38" s="62"/>
-      <c r="K38" s="60" t="s">
-        <v>307</v>
-      </c>
-      <c r="L38" s="69" t="s">
-        <v>295</v>
-      </c>
-      <c r="M38" s="70" t="s">
-        <v>294</v>
-      </c>
-      <c r="N38" s="70" t="s">
-        <v>296</v>
-      </c>
-      <c r="O38" s="71" t="s">
-        <v>297</v>
-      </c>
-      <c r="P38" s="20" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D39" s="72">
-        <f>ROW()-ROW($D$38)</f>
-        <v>1</v>
-      </c>
-      <c r="E39" s="73">
-        <v>3</v>
-      </c>
-      <c r="F39" s="74"/>
-      <c r="G39" s="75" t="s">
-        <v>299</v>
-      </c>
-      <c r="H39" s="74"/>
-      <c r="I39" s="74" t="s">
+    </row>
+    <row r="49" spans="4:22">
+      <c r="D49" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="50" spans="4:22">
+      <c r="D50" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="E50" s="18"/>
+      <c r="F50" s="18"/>
+      <c r="G50" s="8" t="s">
         <v>326</v>
       </c>
-      <c r="J39" s="74"/>
-      <c r="K39" s="76"/>
-      <c r="L39" s="77" t="s">
-        <v>300</v>
-      </c>
-      <c r="M39" s="77">
-        <v>5</v>
-      </c>
-      <c r="N39" s="77">
-        <v>30</v>
-      </c>
-      <c r="O39" s="77">
-        <v>30</v>
-      </c>
-      <c r="P39" s="78"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D40" s="72">
-        <f t="shared" ref="D40:D42" si="1">ROW()-ROW($D$38)</f>
-        <v>2</v>
-      </c>
-      <c r="E40" s="73" t="s">
-        <v>306</v>
-      </c>
-      <c r="F40" s="74"/>
-      <c r="G40" s="75" t="s">
-        <v>306</v>
-      </c>
-      <c r="H40" s="74"/>
-      <c r="I40" s="74" t="s">
+      <c r="H50" s="18"/>
+    </row>
+    <row r="51" spans="4:22">
+      <c r="D51" s="8" t="s">
         <v>327</v>
       </c>
-      <c r="J40" s="74"/>
-      <c r="K40" s="77"/>
-      <c r="L40" s="77"/>
-      <c r="M40" s="77"/>
-      <c r="N40" s="77"/>
-      <c r="O40" s="77"/>
-      <c r="P40" s="79"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D41" s="72">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="E41" s="73" t="s">
-        <v>306</v>
-      </c>
-      <c r="F41" s="74"/>
-      <c r="G41" s="75" t="s">
-        <v>306</v>
-      </c>
-      <c r="H41" s="74"/>
-      <c r="I41" s="74" t="s">
+      <c r="E51" s="18"/>
+      <c r="F51" s="18"/>
+      <c r="G51" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="J41" s="74"/>
-      <c r="K41" s="77"/>
-      <c r="L41" s="77"/>
-      <c r="M41" s="77"/>
-      <c r="N41" s="77"/>
-      <c r="O41" s="77"/>
-      <c r="P41" s="79"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D42" s="80">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="E42" s="85" t="s">
-        <v>306</v>
-      </c>
-      <c r="F42" s="82"/>
-      <c r="G42" s="81" t="s">
-        <v>306</v>
-      </c>
-      <c r="H42" s="82"/>
-      <c r="I42" s="82" t="s">
-        <v>306</v>
-      </c>
-      <c r="J42" s="82"/>
-      <c r="K42" s="83"/>
-      <c r="L42" s="83"/>
-      <c r="M42" s="83"/>
-      <c r="N42" s="83"/>
-      <c r="O42" s="83"/>
-      <c r="P42" s="84"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D44" t="s">
-        <v>311</v>
-      </c>
-      <c r="G44" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D45" t="s">
-        <v>312</v>
-      </c>
-      <c r="G45" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D46" t="s">
-        <v>324</v>
-      </c>
-      <c r="G46" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D47" t="s">
-        <v>316</v>
-      </c>
-      <c r="G47" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D48" t="s">
-        <v>318</v>
-      </c>
-      <c r="G48" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="49" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D49" t="s">
-        <v>320</v>
-      </c>
-      <c r="G49" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="50" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D50" t="s">
-        <v>322</v>
-      </c>
-      <c r="G50" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="51" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D51" t="s">
-        <v>329</v>
-      </c>
+      <c r="H51" s="18"/>
+      <c r="Q51" s="18"/>
+      <c r="R51" s="18"/>
+      <c r="S51" s="18"/>
+      <c r="T51" s="18"/>
+      <c r="U51" s="18"/>
+      <c r="V51" s="18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96B3948A-F2EB-4210-816C-FE29D536AFF8}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <dimension ref="A1:G32"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="3" width="3.375" customWidth="1"/>
+    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="11" max="12" width="9" customWidth="1"/>
+    <col min="14" max="16" width="9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="26.25">
+      <c r="A1" s="47" t="s">
+        <v>321</v>
+      </c>
+      <c r="B1" s="8"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A2" s="47"/>
+      <c r="B2" s="8"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A3" s="47"/>
+      <c r="B3" s="8" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A4" s="47"/>
+      <c r="B4" s="8"/>
+      <c r="C4" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A5" s="47"/>
+      <c r="B5" s="8"/>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" customHeight="1">
+      <c r="B6" s="8" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" customHeight="1">
+      <c r="B7" s="8"/>
+      <c r="C7" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" customHeight="1">
+      <c r="B8" s="8"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="B9" s="8" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="C10" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="B12" s="8"/>
+      <c r="C12" s="123" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="C13" s="8"/>
+      <c r="D13" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="48" t="s">
+        <v>356</v>
+      </c>
+      <c r="F13" s="48"/>
+      <c r="G13" s="48" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="C14" s="8"/>
+      <c r="D14" s="11">
+        <f>ROW()-ROW($D$13)</f>
+        <v>1</v>
+      </c>
+      <c r="E14" t="s">
+        <v>265</v>
+      </c>
+      <c r="G14" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32" s="8"/>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3FA637D-A4E4-43F5-99C7-0DE64168A271}">
   <dimension ref="A1:L46"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="12.5" style="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="43.25" style="11" bestFit="1" customWidth="1"/>
@@ -8667,39 +11047,39 @@
     <col min="12" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="31.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="31.5">
       <c r="A1" s="31" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12">
       <c r="A3" s="32" t="s">
         <v>143</v>
       </c>
       <c r="B3" s="33"/>
       <c r="C3" s="33"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B5" s="51" t="s">
+    <row r="5" spans="1:12">
+      <c r="B5" s="65" t="s">
         <v>129</v>
       </c>
-      <c r="C5" s="51"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48" t="s">
+      <c r="C5" s="65"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60" t="s">
         <v>126</v>
       </c>
-      <c r="F5" s="50"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="48" t="s">
+      <c r="F5" s="66"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="60" t="s">
         <v>136</v>
       </c>
-      <c r="I5" s="49"/>
-      <c r="J5" s="48" t="s">
+      <c r="I5" s="61"/>
+      <c r="J5" s="60" t="s">
         <v>141</v>
       </c>
-      <c r="K5" s="49"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K5" s="61"/>
+    </row>
+    <row r="6" spans="1:12">
       <c r="B6" s="25" t="s">
         <v>128</v>
       </c>
@@ -8731,7 +11111,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12">
       <c r="A7" s="19" t="s">
         <v>127</v>
       </c>
@@ -8766,30 +11146,30 @@
         <v>181</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="48" t="s">
+    <row r="9" spans="1:12">
+      <c r="B9" s="60" t="s">
         <v>151</v>
       </c>
-      <c r="C9" s="49"/>
-      <c r="D9" s="48" t="s">
+      <c r="C9" s="61"/>
+      <c r="D9" s="60" t="s">
         <v>153</v>
       </c>
-      <c r="E9" s="50"/>
-      <c r="F9" s="49"/>
-      <c r="G9" s="48" t="s">
+      <c r="E9" s="66"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="60" t="s">
         <v>136</v>
       </c>
-      <c r="H9" s="49"/>
-      <c r="I9" s="48" t="s">
+      <c r="H9" s="61"/>
+      <c r="I9" s="60" t="s">
         <v>141</v>
       </c>
-      <c r="J9" s="49"/>
-      <c r="K9" s="48" t="s">
+      <c r="J9" s="61"/>
+      <c r="K9" s="60" t="s">
         <v>178</v>
       </c>
-      <c r="L9" s="49"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L9" s="61"/>
+    </row>
+    <row r="10" spans="1:12">
       <c r="B10" s="25" t="s">
         <v>152</v>
       </c>
@@ -8824,7 +11204,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12">
       <c r="A11" s="19" t="s">
         <v>149</v>
       </c>
@@ -8862,8 +11242,8 @@
         <v>181</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="52" t="s">
+    <row r="14" spans="1:12">
+      <c r="A14" s="62" t="s">
         <v>155</v>
       </c>
       <c r="D14" s="27" t="s">
@@ -8872,14 +11252,14 @@
       <c r="E14" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="F14" s="51" t="s">
+      <c r="F14" s="65" t="s">
         <v>165</v>
       </c>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="53"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="65"/>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="63"/>
       <c r="D15" s="34" t="s">
         <v>157</v>
       </c>
@@ -8890,8 +11270,8 @@
         <v>166</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="53"/>
+    <row r="16" spans="1:12">
+      <c r="A16" s="63"/>
       <c r="D16" s="35" t="s">
         <v>158</v>
       </c>
@@ -8899,8 +11279,8 @@
         <v>161</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="53"/>
+    <row r="17" spans="1:6">
+      <c r="A17" s="63"/>
       <c r="D17" s="23" t="s">
         <v>159</v>
       </c>
@@ -8911,92 +11291,92 @@
         <v>182</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="53"/>
+    <row r="18" spans="1:6">
+      <c r="A18" s="63"/>
       <c r="D18" s="13" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="53"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="53"/>
+    <row r="19" spans="1:6">
+      <c r="A19" s="63"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="63"/>
       <c r="E20" s="36" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="53"/>
+    <row r="21" spans="1:6">
+      <c r="A21" s="63"/>
       <c r="E21" s="13" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="53"/>
+    <row r="22" spans="1:6">
+      <c r="A22" s="63"/>
       <c r="E22" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="53"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="53"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="53"/>
+    <row r="23" spans="1:6">
+      <c r="A23" s="63"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="63"/>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="63"/>
       <c r="E25" s="11" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="53"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="53"/>
+    <row r="26" spans="1:6">
+      <c r="A26" s="63"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="63"/>
       <c r="E27" s="13" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="53"/>
+    <row r="28" spans="1:6">
+      <c r="A28" s="63"/>
       <c r="E28" s="13" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="53"/>
+    <row r="29" spans="1:6">
+      <c r="A29" s="63"/>
       <c r="E29" s="11" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="53"/>
+    <row r="30" spans="1:6">
+      <c r="A30" s="63"/>
       <c r="E30" s="13" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="54"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6">
+      <c r="A31" s="64"/>
+    </row>
+    <row r="33" spans="1:7">
       <c r="B33" s="27" t="s">
         <v>151</v>
       </c>
       <c r="C33" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="D33" s="48" t="s">
+      <c r="D33" s="60" t="s">
         <v>189</v>
       </c>
-      <c r="E33" s="49"/>
-      <c r="F33" s="48" t="s">
+      <c r="E33" s="61"/>
+      <c r="F33" s="60" t="s">
         <v>178</v>
       </c>
-      <c r="G33" s="49"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G33" s="61"/>
+    </row>
+    <row r="34" spans="1:7">
       <c r="B34" s="26" t="s">
         <v>150</v>
       </c>
@@ -9016,7 +11396,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7">
       <c r="A35" s="19" t="s">
         <v>183</v>
       </c>
@@ -9039,7 +11419,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7">
       <c r="B38" s="19" t="s">
         <v>213</v>
       </c>
@@ -9053,7 +11433,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7">
       <c r="A39" s="19" t="s">
         <v>206</v>
       </c>
@@ -9070,42 +11450,42 @@
         <v>222</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="33">
       <c r="E40" s="38" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7">
       <c r="B41" s="13"/>
       <c r="C41" s="13"/>
       <c r="D41" s="13"/>
       <c r="E41" s="13"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7">
       <c r="B42" s="13"/>
       <c r="C42" s="13"/>
       <c r="D42" s="13"/>
       <c r="E42" s="13"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7">
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
       <c r="D43" s="13"/>
       <c r="E43" s="13"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7">
       <c r="B44" s="13"/>
       <c r="C44" s="13"/>
       <c r="D44" s="13"/>
       <c r="E44" s="13"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7">
       <c r="B45" s="13"/>
       <c r="C45" s="13"/>
       <c r="D45" s="13"/>
       <c r="E45" s="13"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7">
       <c r="B46" s="13"/>
       <c r="C46" s="13"/>
       <c r="D46" s="13"/>
@@ -9113,11 +11493,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="A14:A31"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="B9:C9"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="G9:H9"/>
     <mergeCell ref="K9:L9"/>
@@ -9126,6 +11501,11 @@
     <mergeCell ref="E5:G5"/>
     <mergeCell ref="J5:K5"/>
     <mergeCell ref="H5:I5"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="A14:A31"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="B9:C9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9133,22 +11513,22 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{511B7746-4A5E-454B-8602-7B4B353E7BEF}">
-  <dimension ref="A1:Y20"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Y24"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="4.625" customWidth="1"/>
     <col min="2" max="2" width="8.5" customWidth="1"/>
     <col min="3" max="3" width="5.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="26.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" ht="26.25">
       <c r="A1" s="39" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25">
       <c r="B3" t="s">
         <v>201</v>
       </c>
@@ -9165,7 +11545,7 @@
       <c r="V3" s="40"/>
       <c r="W3" s="40"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25">
       <c r="B4" t="s">
         <v>202</v>
       </c>
@@ -9185,7 +11565,7 @@
       <c r="V4" s="40"/>
       <c r="W4" s="40"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25">
       <c r="B5" t="s">
         <v>203</v>
       </c>
@@ -9193,7 +11573,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="21.75" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" ht="21.75">
       <c r="B6" t="s">
         <v>204</v>
       </c>
@@ -9215,7 +11595,7 @@
       <c r="X6" s="43"/>
       <c r="Y6" s="43"/>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25">
       <c r="N7" s="43"/>
       <c r="O7" s="43"/>
       <c r="P7" s="43"/>
@@ -9229,7 +11609,7 @@
       <c r="X7" s="43"/>
       <c r="Y7" s="43"/>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25">
       <c r="B8">
         <v>1</v>
       </c>
@@ -9251,7 +11631,7 @@
       <c r="X8" s="43"/>
       <c r="Y8" s="43"/>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25">
       <c r="C9" t="s">
         <v>234</v>
       </c>
@@ -9268,7 +11648,7 @@
       <c r="X9" s="43"/>
       <c r="Y9" s="43"/>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25">
       <c r="N10" s="45" t="s">
         <v>248</v>
       </c>
@@ -9284,7 +11664,7 @@
       <c r="X10" s="43"/>
       <c r="Y10" s="43"/>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25">
       <c r="B11">
         <v>2</v>
       </c>
@@ -9306,12 +11686,12 @@
       <c r="X11" s="43"/>
       <c r="Y11" s="43"/>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25">
       <c r="C12" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25">
       <c r="B14">
         <v>3</v>
       </c>
@@ -9319,17 +11699,17 @@
         <v>242</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25">
       <c r="C15" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25">
       <c r="C16" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:3">
       <c r="B18">
         <v>4</v>
       </c>
@@ -9337,9 +11717,23 @@
         <v>240</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:3">
       <c r="B20" t="s">
         <v>247</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3">
+      <c r="B22" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3">
+      <c r="B24" s="59">
+        <f>1920/3</f>
+        <v>640</v>
+      </c>
+      <c r="C24" t="s">
+        <v>319</v>
       </c>
     </row>
   </sheetData>
@@ -9348,13 +11742,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FEA1851-41A0-400A-9D42-CA24EB0A5B33}">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="B2:S47"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="3.75" customWidth="1"/>
     <col min="2" max="2" width="5.375" style="11" customWidth="1"/>
@@ -9366,7 +11760,7 @@
     <col min="18" max="18" width="4.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:19">
       <c r="B2" s="14" t="s">
         <v>7</v>
       </c>
@@ -9378,7 +11772,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:19">
       <c r="B3" s="22">
         <v>1</v>
       </c>
@@ -9395,7 +11789,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:19">
       <c r="E4" t="s">
         <v>84</v>
       </c>
@@ -9403,17 +11797,17 @@
         <v>86</v>
       </c>
     </row>
-    <row r="5" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:19">
       <c r="E5" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="6" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:19">
       <c r="E6" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="8" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:19">
       <c r="B8" s="11">
         <v>2</v>
       </c>
@@ -9427,7 +11821,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="10" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:19">
       <c r="B10" s="11">
         <v>3</v>
       </c>
@@ -9441,7 +11835,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="12" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:19">
       <c r="B12" s="11">
         <v>4</v>
       </c>
@@ -9458,7 +11852,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="13" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:19">
       <c r="C13" t="s">
         <v>94</v>
       </c>
@@ -9469,7 +11863,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="15" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:19">
       <c r="B15" s="22">
         <v>5</v>
       </c>
@@ -9483,10 +11877,10 @@
         <v>121</v>
       </c>
     </row>
-    <row r="16" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:19">
       <c r="B16"/>
     </row>
-    <row r="17" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:19">
       <c r="B17">
         <v>5.25</v>
       </c>
@@ -9500,12 +11894,12 @@
         <v>122</v>
       </c>
     </row>
-    <row r="18" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:19">
       <c r="S18" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="19" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:19">
       <c r="B19" s="11">
         <v>5.5</v>
       </c>
@@ -9519,7 +11913,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:19">
       <c r="E20" t="s">
         <v>116</v>
       </c>
@@ -9527,17 +11921,17 @@
         <v>124</v>
       </c>
     </row>
-    <row r="22" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:19">
       <c r="D22" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="24" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:19">
       <c r="D24" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="26" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:19">
       <c r="B26" s="11">
         <v>6</v>
       </c>
@@ -9545,7 +11939,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="27" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:19">
       <c r="C27" t="s">
         <v>98</v>
       </c>
@@ -9556,7 +11950,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:19">
       <c r="C29" t="s">
         <v>101</v>
       </c>
@@ -9564,12 +11958,12 @@
         <v>102</v>
       </c>
     </row>
-    <row r="30" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:19">
       <c r="D30" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="32" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:19">
       <c r="C32" t="s">
         <v>103</v>
       </c>
@@ -9577,7 +11971,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:4">
       <c r="C34" t="s">
         <v>106</v>
       </c>
@@ -9585,7 +11979,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:4">
       <c r="C36" t="s">
         <v>108</v>
       </c>
@@ -9593,12 +11987,12 @@
         <v>109</v>
       </c>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:4">
       <c r="D37" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:4">
       <c r="B39" s="11">
         <v>7</v>
       </c>
@@ -9606,7 +12000,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:4">
       <c r="B41" s="33">
         <v>8</v>
       </c>
@@ -9617,7 +12011,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:4">
       <c r="B43" s="11">
         <v>9</v>
       </c>
@@ -9625,7 +12019,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:4">
       <c r="B45" s="46">
         <v>10</v>
       </c>
@@ -9633,7 +12027,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:4">
       <c r="C47" t="s">
         <v>255</v>
       </c>

--- a/Document/정책문서.xlsx
+++ b/Document/정책문서.xlsx
@@ -1,27 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git_fork\ProjectShoot\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E558F32E-01BF-419A-8E3E-C87A5283094E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8735F56-8997-49E8-A511-2FE4FEFBAD4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="711" firstSheet="1" activeTab="5" xr2:uid="{F9E8F865-F741-4425-897D-555A2E4B3EBE}"/>
+    <workbookView xWindow="32235" yWindow="4755" windowWidth="21600" windowHeight="11295" tabRatio="711" firstSheet="1" activeTab="1" xr2:uid="{F9E8F865-F741-4425-897D-555A2E4B3EBE}"/>
   </bookViews>
   <sheets>
     <sheet name="깃포크 공부" sheetId="11" state="hidden" r:id="rId1"/>
-    <sheet name="player" sheetId="3" r:id="rId2"/>
-    <sheet name="enemy" sheetId="6" r:id="rId3"/>
-    <sheet name="Spawn" sheetId="18" r:id="rId4"/>
-    <sheet name="Formation" sheetId="16" r:id="rId5"/>
-    <sheet name="Move_Pattern" sheetId="17" r:id="rId6"/>
-    <sheet name="생애주기" sheetId="13" r:id="rId7"/>
-    <sheet name="카메라 " sheetId="15" r:id="rId8"/>
-    <sheet name="개발요청" sheetId="12" r:id="rId9"/>
+    <sheet name="History" sheetId="19" r:id="rId2"/>
+    <sheet name="player" sheetId="3" r:id="rId3"/>
+    <sheet name="enemy" sheetId="6" r:id="rId4"/>
+    <sheet name="Spawn" sheetId="18" r:id="rId5"/>
+    <sheet name="Formation" sheetId="16" r:id="rId6"/>
+    <sheet name="Move_Pattern" sheetId="17" r:id="rId7"/>
+    <sheet name="생애주기" sheetId="13" r:id="rId8"/>
+    <sheet name="카메라 " sheetId="15" r:id="rId9"/>
+    <sheet name="개발요청" sheetId="12" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,8 +42,646 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>user</author>
+  </authors>
+  <commentList>
+    <comment ref="K36" authorId="0" shapeId="0" xr:uid="{1F2FBBAA-7E7D-48B9-BCB3-CD040A8DAE96}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>user:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>진형</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>편집기를</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>만들어서</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>진형이름과</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> xy</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>좌표</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>설정</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">, </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>생성한뒤에</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>그때그때</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>가져다</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>쓰면</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>안되나요</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>???</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>user</author>
+  </authors>
+  <commentList>
+    <comment ref="D14" authorId="0" shapeId="0" xr:uid="{17B81B10-DFF1-4D44-B5B0-6A2782D16F0A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>user:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>복잡한</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>물리</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>엔진</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>대신</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">, </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>유니티의</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> '</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>베지에</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>곡선</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Bezier Curve)'</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>이나</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> 'iTween/DoTween </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>패스</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">' </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>툴을</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>쓰면</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>코드</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>몇</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>줄로</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>완벽하게</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>부드러운</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> U</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>자</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>궤적이</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>나옵니다</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="393">
   <si>
     <t>설명</t>
   </si>
@@ -1368,10 +2007,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">몬스터가 행동하는 형태 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>행동 종류</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1528,63 +2163,157 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>행동 형태</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">행동의 경우 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>이동</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">과 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>사격</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 두종류로 나눔 </t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이동 종류</t>
+    <t>이동형태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STAY_Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>O</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>형태 설명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PASS_THROUGH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>생성될 시점 플레이어를 향해 돌진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">몬스터가 스폰 후 이동하는 형태 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정 Y에서 멈춰서 공격 후 돌진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SWOOP_Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정 Y에서 멈춰서 공격 후 이탈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STAYRUSH_Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정 Y에서 멈춰서 공격 (죽을 때 까지)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Enum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Positioning Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>체류좌표 Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Positioning Time</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>체류시간 (초)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">STAYRUSH_Y </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">행동 패턴 정보 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>생성 후 체류하는 y 좌표</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>생성 후 체류하는 시간</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y컬럼(소수점 첫째자리)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시간컬럼 (소수점 첫째자리)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">추후 추가될 가능성 있음 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이현경</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">페이지 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유형</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작성자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>날짜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>번호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>히스토리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>페이지 편집</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 히스토리 시트 생성 (커밋로그 쓸때 참조용)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내용 수정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>포메이션
+무브 패턴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 진형 셀에 색 강조(회의 필요: 이거 xy로 진형 형태 조절할거면 미리 형태를 만드는 이유가 있나?)
+- 무브 패턴 내용 작성</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1595,7 +2324,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1748,14 +2477,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF0066FF"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
@@ -1786,8 +2507,46 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF0066FF"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1842,8 +2601,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="38">
+  <borders count="42">
     <border>
       <left/>
       <right/>
@@ -2310,6 +3075,56 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -2319,7 +3134,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2482,9 +3297,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2494,40 +3306,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="33" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="34" xfId="0" applyFill="1" applyBorder="1">
@@ -2560,32 +3345,20 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
@@ -2596,20 +3369,8 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2620,9 +3381,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2632,28 +3390,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2668,29 +3411,125 @@
     <xf numFmtId="0" fontId="15" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2701,8 +3540,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF0066FF"/>
       <color rgb="FF79DCFF"/>
-      <color rgb="FF0066FF"/>
       <color rgb="FFFF66CC"/>
       <color rgb="FFB2B5BA"/>
       <color rgb="FFFF99CC"/>
@@ -7041,6 +7880,749 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>598674</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>484009</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="직사각형 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{923EB5A3-FD7F-723E-9397-0FF142256D67}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7666224" y="2657475"/>
+          <a:ext cx="2628535" cy="3686175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="76200">
+          <a:solidFill>
+            <a:srgbClr val="C00000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>적 제거 영역</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>631514</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>535134</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="직사각형 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80B9559D-29DD-CA65-B32D-FF88994D6F63}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8384864" y="3495675"/>
+          <a:ext cx="1275220" cy="2343150"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1600">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>게임 화면</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>545196</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>653112</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="직사각형 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1BA83FEE-E00C-FC7A-C70D-D071EE57DA01}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8984346" y="5410200"/>
+          <a:ext cx="107916" cy="152400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="16" name="직선 화살표 연결선 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2840088D-EAE5-9630-404B-FF294BD5E1FA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9848850" y="3514725"/>
+          <a:ext cx="0" cy="2305050"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="57150">
+          <a:solidFill>
+            <a:srgbClr val="FFC000"/>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>250371</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="직사각형 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E25D03F-2F2E-499C-9419-CBB5760423B3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10010775" y="5686425"/>
+          <a:ext cx="736146" cy="314325"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Y</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1050" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>0</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>128588</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="19" name="직선 화살표 연결선 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B33F69D6-023B-EB10-4526-0E438B19CCC0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="17" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="9686925" y="5838825"/>
+          <a:ext cx="323850" cy="4763"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>212271</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="직사각형 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B5930C7-5CE8-4EC6-9804-0987A9165161}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9972675" y="3343275"/>
+          <a:ext cx="736146" cy="314325"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Y</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1050" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>100</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>523875</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>90488</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="23" name="직선 화살표 연결선 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2F7A997-29A1-48AF-B688-6E73F0AE4405}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="22" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="9648825" y="3495675"/>
+          <a:ext cx="323850" cy="4763"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="순서도: 수행의 시작/종료 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1D41D03-6E33-4A12-8E19-A1CD485AFF8C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13201650" y="4095750"/>
+          <a:ext cx="2343150" cy="1028700"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartTerminator">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4"/>
+        </a:solidFill>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1050">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>스폰 후 거점을 설정하기 위해 </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1050">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1050">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>별도의 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1050">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Y</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1050">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>컬럼을 사용</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1050">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>,</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1050">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>적의 위치를 제어한다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1050">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1050">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1050">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>소수점 첫째자리 </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1050">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>28575</xdr:colOff>
       <xdr:row>13</xdr:row>
@@ -7848,7 +9430,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -8784,7 +10366,570 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FEA1851-41A0-400A-9D42-CA24EB0A5B33}">
+  <sheetPr>
+    <tabColor rgb="FFFFC000"/>
+  </sheetPr>
+  <dimension ref="B2:S47"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="3.75" customWidth="1"/>
+    <col min="2" max="2" width="5.375" style="11" customWidth="1"/>
+    <col min="3" max="3" width="4" customWidth="1"/>
+    <col min="4" max="4" width="38.875" customWidth="1"/>
+    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.5" customWidth="1"/>
+    <col min="11" max="11" width="5.75" customWidth="1"/>
+    <col min="18" max="18" width="4.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:19">
+      <c r="B2" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="D2" s="16"/>
+      <c r="H2" s="16" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="2:19">
+      <c r="B3" s="22">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="2:19">
+      <c r="E4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="2:19">
+      <c r="E5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="2:19">
+      <c r="E6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="8" spans="2:19">
+      <c r="B8" s="11">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
+        <v>87</v>
+      </c>
+      <c r="E8" s="37" t="s">
+        <v>207</v>
+      </c>
+      <c r="H8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" spans="2:19">
+      <c r="B10" s="11">
+        <v>3</v>
+      </c>
+      <c r="C10" t="s">
+        <v>91</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>208</v>
+      </c>
+      <c r="H10" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="12" spans="2:19">
+      <c r="B12" s="11">
+        <v>4</v>
+      </c>
+      <c r="C12" t="s">
+        <v>92</v>
+      </c>
+      <c r="E12" t="s">
+        <v>93</v>
+      </c>
+      <c r="H12" t="s">
+        <v>95</v>
+      </c>
+      <c r="J12" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" spans="2:19">
+      <c r="C13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E13" s="37" t="s">
+        <v>209</v>
+      </c>
+      <c r="J13" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="15" spans="2:19">
+      <c r="B15" s="22">
+        <v>5</v>
+      </c>
+      <c r="C15" t="s">
+        <v>96</v>
+      </c>
+      <c r="H15" t="s">
+        <v>111</v>
+      </c>
+      <c r="S15" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="16" spans="2:19">
+      <c r="B16"/>
+    </row>
+    <row r="17" spans="2:19">
+      <c r="B17">
+        <v>5.25</v>
+      </c>
+      <c r="C17" t="s">
+        <v>119</v>
+      </c>
+      <c r="H17" t="s">
+        <v>120</v>
+      </c>
+      <c r="S17" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="18" spans="2:19">
+      <c r="S18" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="19" spans="2:19">
+      <c r="B19" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="C19" t="s">
+        <v>114</v>
+      </c>
+      <c r="E19" t="s">
+        <v>115</v>
+      </c>
+      <c r="H19" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="2:19">
+      <c r="E20" t="s">
+        <v>116</v>
+      </c>
+      <c r="S20" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="22" spans="2:19">
+      <c r="D22" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="24" spans="2:19">
+      <c r="D24" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="26" spans="2:19">
+      <c r="B26" s="11">
+        <v>6</v>
+      </c>
+      <c r="C26" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="27" spans="2:19">
+      <c r="C27" t="s">
+        <v>98</v>
+      </c>
+      <c r="D27" t="s">
+        <v>99</v>
+      </c>
+      <c r="E27" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="2:19">
+      <c r="C29" t="s">
+        <v>101</v>
+      </c>
+      <c r="D29" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="30" spans="2:19">
+      <c r="D30" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="32" spans="2:19">
+      <c r="C32" t="s">
+        <v>103</v>
+      </c>
+      <c r="D32" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4">
+      <c r="C34" t="s">
+        <v>106</v>
+      </c>
+      <c r="D34" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4">
+      <c r="C36" t="s">
+        <v>108</v>
+      </c>
+      <c r="D36" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4">
+      <c r="D37" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4">
+      <c r="B39" s="11">
+        <v>7</v>
+      </c>
+      <c r="C39" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4">
+      <c r="B41" s="33">
+        <v>8</v>
+      </c>
+      <c r="C41" t="s">
+        <v>224</v>
+      </c>
+      <c r="D41" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4">
+      <c r="B43" s="11">
+        <v>9</v>
+      </c>
+      <c r="C43" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4">
+      <c r="B45" s="46">
+        <v>10</v>
+      </c>
+      <c r="C45" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4">
+      <c r="C47" t="s">
+        <v>255</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D96FDAC-DED2-464C-8F36-7438D20848EF}">
+  <dimension ref="A1:R11"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="2" max="2" width="9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="33.75">
+      <c r="A1" s="120" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
+      <c r="A3" s="27" t="s">
+        <v>386</v>
+      </c>
+      <c r="B3" s="50" t="s">
+        <v>385</v>
+      </c>
+      <c r="C3" s="51"/>
+      <c r="D3" s="19" t="s">
+        <v>384</v>
+      </c>
+      <c r="E3" s="52" t="s">
+        <v>383</v>
+      </c>
+      <c r="F3" s="52"/>
+      <c r="G3" s="50" t="s">
+        <v>382</v>
+      </c>
+      <c r="H3" s="51"/>
+      <c r="I3" s="52" t="s">
+        <v>381</v>
+      </c>
+      <c r="J3" s="52"/>
+      <c r="K3" s="52"/>
+      <c r="L3" s="52"/>
+      <c r="M3" s="52"/>
+      <c r="N3" s="52"/>
+      <c r="O3" s="52"/>
+      <c r="P3" s="52"/>
+      <c r="Q3" s="52"/>
+      <c r="R3" s="51"/>
+    </row>
+    <row r="4" spans="1:18" ht="50.25" customHeight="1">
+      <c r="A4" s="118">
+        <f t="shared" ref="A4:A11" si="0">ROW()-ROW($A$3)</f>
+        <v>1</v>
+      </c>
+      <c r="B4" s="119">
+        <v>46185</v>
+      </c>
+      <c r="C4" s="116"/>
+      <c r="D4" s="118" t="s">
+        <v>380</v>
+      </c>
+      <c r="E4" s="117" t="s">
+        <v>388</v>
+      </c>
+      <c r="F4" s="116"/>
+      <c r="G4" s="115" t="s">
+        <v>387</v>
+      </c>
+      <c r="H4" s="114"/>
+      <c r="I4" s="121" t="s">
+        <v>389</v>
+      </c>
+      <c r="J4" s="122"/>
+      <c r="K4" s="122"/>
+      <c r="L4" s="122"/>
+      <c r="M4" s="122"/>
+      <c r="N4" s="122"/>
+      <c r="O4" s="122"/>
+      <c r="P4" s="122"/>
+      <c r="Q4" s="122"/>
+      <c r="R4" s="123"/>
+    </row>
+    <row r="5" spans="1:18" ht="50.25" customHeight="1">
+      <c r="A5" s="118">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="B5" s="119">
+        <v>46185</v>
+      </c>
+      <c r="C5" s="116"/>
+      <c r="D5" s="118" t="s">
+        <v>380</v>
+      </c>
+      <c r="E5" s="117" t="s">
+        <v>390</v>
+      </c>
+      <c r="F5" s="116"/>
+      <c r="G5" s="131" t="s">
+        <v>391</v>
+      </c>
+      <c r="H5" s="114"/>
+      <c r="I5" s="121" t="s">
+        <v>392</v>
+      </c>
+      <c r="J5" s="122"/>
+      <c r="K5" s="122"/>
+      <c r="L5" s="122"/>
+      <c r="M5" s="122"/>
+      <c r="N5" s="122"/>
+      <c r="O5" s="122"/>
+      <c r="P5" s="122"/>
+      <c r="Q5" s="122"/>
+      <c r="R5" s="123"/>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="A6" s="118">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B6" s="119"/>
+      <c r="C6" s="116"/>
+      <c r="D6" s="118"/>
+      <c r="E6" s="117"/>
+      <c r="F6" s="116"/>
+      <c r="G6" s="115"/>
+      <c r="H6" s="114"/>
+      <c r="I6" s="121"/>
+      <c r="J6" s="122"/>
+      <c r="K6" s="122"/>
+      <c r="L6" s="122"/>
+      <c r="M6" s="122"/>
+      <c r="N6" s="122"/>
+      <c r="O6" s="122"/>
+      <c r="P6" s="122"/>
+      <c r="Q6" s="122"/>
+      <c r="R6" s="123"/>
+    </row>
+    <row r="7" spans="1:18">
+      <c r="A7" s="118">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B7" s="119"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="117"/>
+      <c r="F7" s="116"/>
+      <c r="G7" s="115"/>
+      <c r="H7" s="114"/>
+      <c r="I7" s="121"/>
+      <c r="J7" s="122"/>
+      <c r="K7" s="122"/>
+      <c r="L7" s="122"/>
+      <c r="M7" s="122"/>
+      <c r="N7" s="122"/>
+      <c r="O7" s="122"/>
+      <c r="P7" s="122"/>
+      <c r="Q7" s="122"/>
+      <c r="R7" s="123"/>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="A8" s="118">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B8" s="119"/>
+      <c r="C8" s="116"/>
+      <c r="D8" s="118"/>
+      <c r="E8" s="117"/>
+      <c r="F8" s="116"/>
+      <c r="G8" s="115"/>
+      <c r="H8" s="114"/>
+      <c r="I8" s="121"/>
+      <c r="J8" s="122"/>
+      <c r="K8" s="122"/>
+      <c r="L8" s="122"/>
+      <c r="M8" s="122"/>
+      <c r="N8" s="122"/>
+      <c r="O8" s="122"/>
+      <c r="P8" s="122"/>
+      <c r="Q8" s="122"/>
+      <c r="R8" s="123"/>
+    </row>
+    <row r="9" spans="1:18">
+      <c r="A9" s="118">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B9" s="119"/>
+      <c r="C9" s="116"/>
+      <c r="D9" s="118"/>
+      <c r="E9" s="117"/>
+      <c r="F9" s="116"/>
+      <c r="G9" s="115"/>
+      <c r="H9" s="114"/>
+      <c r="I9" s="121"/>
+      <c r="J9" s="122"/>
+      <c r="K9" s="122"/>
+      <c r="L9" s="122"/>
+      <c r="M9" s="122"/>
+      <c r="N9" s="122"/>
+      <c r="O9" s="122"/>
+      <c r="P9" s="122"/>
+      <c r="Q9" s="122"/>
+      <c r="R9" s="123"/>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="A10" s="118">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B10" s="119"/>
+      <c r="C10" s="116"/>
+      <c r="D10" s="118"/>
+      <c r="E10" s="117"/>
+      <c r="F10" s="116"/>
+      <c r="G10" s="115"/>
+      <c r="H10" s="114"/>
+      <c r="I10" s="121"/>
+      <c r="J10" s="122"/>
+      <c r="K10" s="122"/>
+      <c r="L10" s="122"/>
+      <c r="M10" s="122"/>
+      <c r="N10" s="122"/>
+      <c r="O10" s="122"/>
+      <c r="P10" s="122"/>
+      <c r="Q10" s="122"/>
+      <c r="R10" s="123"/>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="A11" s="118">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B11" s="119"/>
+      <c r="C11" s="116"/>
+      <c r="D11" s="118"/>
+      <c r="E11" s="117"/>
+      <c r="F11" s="116"/>
+      <c r="G11" s="115"/>
+      <c r="H11" s="114"/>
+      <c r="I11" s="121"/>
+      <c r="J11" s="122"/>
+      <c r="K11" s="122"/>
+      <c r="L11" s="122"/>
+      <c r="M11" s="122"/>
+      <c r="N11" s="122"/>
+      <c r="O11" s="122"/>
+      <c r="P11" s="122"/>
+      <c r="Q11" s="122"/>
+      <c r="R11" s="123"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="I10:R10"/>
+    <mergeCell ref="I11:R11"/>
+    <mergeCell ref="I4:R4"/>
+    <mergeCell ref="I5:R5"/>
+    <mergeCell ref="I6:R6"/>
+    <mergeCell ref="I7:R7"/>
+    <mergeCell ref="I8:R8"/>
+    <mergeCell ref="I9:R9"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53EED6F7-E2A1-46EB-98A7-F79E280C4A2A}">
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
@@ -9285,7 +11430,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F061614-43B1-4419-882C-4D7535310A1A}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -9719,9 +11864,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5B6D67C-9882-4C75-80BA-1B180D5DF46B}">
-  <dimension ref="A1:U53"/>
+  <dimension ref="A1:X55"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="3" width="3.375" customWidth="1"/>
@@ -9730,7 +11875,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="26.25">
       <c r="A1" s="47" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B1" s="8"/>
     </row>
@@ -9748,7 +11893,7 @@
       <c r="A4" s="47"/>
       <c r="B4" s="8"/>
       <c r="C4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="16.5" customHeight="1">
@@ -9763,7 +11908,7 @@
     <row r="7" spans="1:17" ht="16.5" customHeight="1">
       <c r="B7" s="8"/>
       <c r="C7" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="16.5" customHeight="1">
@@ -9771,16 +11916,16 @@
     </row>
     <row r="9" spans="1:17" ht="16.5" customHeight="1">
       <c r="B9" s="8" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="16.5" customHeight="1">
       <c r="B10" s="8"/>
-      <c r="C10" s="85" t="s">
-        <v>348</v>
+      <c r="C10" s="74" t="s">
+        <v>347</v>
       </c>
       <c r="L10" s="50" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="M10" s="52"/>
       <c r="N10" s="52"/>
@@ -9791,496 +11936,527 @@
     <row r="11" spans="1:17" ht="16.5" customHeight="1">
       <c r="B11" s="8"/>
       <c r="D11" t="s">
-        <v>345</v>
-      </c>
-      <c r="L11" s="74"/>
-      <c r="M11" s="75"/>
-      <c r="N11" s="75"/>
-      <c r="O11" s="75"/>
-      <c r="P11" s="75"/>
-      <c r="Q11" s="76"/>
+        <v>344</v>
+      </c>
+      <c r="L11" s="64"/>
+      <c r="M11" s="65"/>
+      <c r="N11" s="65"/>
+      <c r="O11" s="65"/>
+      <c r="P11" s="65"/>
+      <c r="Q11" s="66"/>
     </row>
     <row r="12" spans="1:17" ht="16.5" customHeight="1">
       <c r="B12" s="8"/>
-      <c r="L12" s="68"/>
-      <c r="M12" s="69"/>
-      <c r="N12" s="69"/>
-      <c r="O12" s="69"/>
-      <c r="P12" s="69"/>
-      <c r="Q12" s="70"/>
+      <c r="L12" s="58"/>
+      <c r="M12" s="59"/>
+      <c r="N12" s="59"/>
+      <c r="O12" s="59"/>
+      <c r="P12" s="59"/>
+      <c r="Q12" s="60"/>
     </row>
     <row r="13" spans="1:17" ht="16.5" customHeight="1">
       <c r="B13" s="8"/>
       <c r="D13" t="s">
-        <v>344</v>
-      </c>
-      <c r="L13" s="68"/>
-      <c r="M13" s="69"/>
-      <c r="N13" s="69"/>
-      <c r="O13" s="69"/>
-      <c r="P13" s="69"/>
-      <c r="Q13" s="70"/>
+        <v>343</v>
+      </c>
+      <c r="L13" s="58"/>
+      <c r="M13" s="59"/>
+      <c r="N13" s="59"/>
+      <c r="O13" s="59"/>
+      <c r="P13" s="59"/>
+      <c r="Q13" s="60"/>
     </row>
     <row r="14" spans="1:17" ht="16.5" customHeight="1">
       <c r="B14" s="8"/>
-      <c r="D14" s="79" t="s">
-        <v>351</v>
-      </c>
-      <c r="L14" s="68"/>
-      <c r="M14" s="69"/>
-      <c r="N14" s="69"/>
-      <c r="O14" s="69"/>
-      <c r="P14" s="69"/>
-      <c r="Q14" s="70"/>
+      <c r="D14" s="69" t="s">
+        <v>350</v>
+      </c>
+      <c r="L14" s="58"/>
+      <c r="M14" s="59"/>
+      <c r="N14" s="59"/>
+      <c r="O14" s="59"/>
+      <c r="P14" s="59"/>
+      <c r="Q14" s="60"/>
     </row>
     <row r="15" spans="1:17" ht="16.5" customHeight="1">
       <c r="B15" s="8"/>
-      <c r="L15" s="68"/>
-      <c r="M15" s="69"/>
-      <c r="N15" s="69"/>
-      <c r="O15" s="69"/>
-      <c r="P15" s="69"/>
-      <c r="Q15" s="70"/>
+      <c r="L15" s="58"/>
+      <c r="M15" s="59"/>
+      <c r="N15" s="59"/>
+      <c r="O15" s="59"/>
+      <c r="P15" s="59"/>
+      <c r="Q15" s="60"/>
     </row>
     <row r="16" spans="1:17" ht="16.5" customHeight="1">
       <c r="B16" s="8"/>
       <c r="D16" t="s">
-        <v>352</v>
-      </c>
-      <c r="L16" s="68"/>
-      <c r="M16" s="69"/>
-      <c r="N16" s="69"/>
-      <c r="O16" s="69"/>
-      <c r="P16" s="69"/>
-      <c r="Q16" s="70"/>
+        <v>351</v>
+      </c>
+      <c r="L16" s="58"/>
+      <c r="M16" s="59"/>
+      <c r="N16" s="59"/>
+      <c r="O16" s="59"/>
+      <c r="P16" s="59"/>
+      <c r="Q16" s="60"/>
     </row>
     <row r="17" spans="2:17" ht="16.5" customHeight="1">
       <c r="B17" s="8"/>
       <c r="D17" t="s">
-        <v>353</v>
-      </c>
-      <c r="L17" s="68"/>
-      <c r="M17" s="69"/>
-      <c r="N17" s="69"/>
-      <c r="O17" s="69"/>
-      <c r="P17" s="69"/>
-      <c r="Q17" s="70"/>
+        <v>352</v>
+      </c>
+      <c r="L17" s="58"/>
+      <c r="M17" s="59"/>
+      <c r="N17" s="59"/>
+      <c r="O17" s="59"/>
+      <c r="P17" s="59"/>
+      <c r="Q17" s="60"/>
     </row>
     <row r="18" spans="2:17" ht="16.5" customHeight="1">
       <c r="B18" s="8"/>
-      <c r="L18" s="68"/>
-      <c r="M18" s="69"/>
-      <c r="N18" s="69"/>
-      <c r="O18" s="69"/>
-      <c r="P18" s="69"/>
-      <c r="Q18" s="70"/>
+      <c r="L18" s="58"/>
+      <c r="M18" s="59"/>
+      <c r="N18" s="59"/>
+      <c r="O18" s="59"/>
+      <c r="P18" s="59"/>
+      <c r="Q18" s="60"/>
     </row>
     <row r="19" spans="2:17" ht="16.5" customHeight="1">
       <c r="B19" s="8"/>
-      <c r="C19" s="85" t="s">
-        <v>354</v>
-      </c>
-      <c r="L19" s="68"/>
-      <c r="M19" s="69"/>
-      <c r="N19" s="69"/>
-      <c r="O19" s="69"/>
-      <c r="P19" s="69"/>
-      <c r="Q19" s="70"/>
+      <c r="C19" s="74" t="s">
+        <v>353</v>
+      </c>
+      <c r="L19" s="58"/>
+      <c r="M19" s="59"/>
+      <c r="N19" s="59"/>
+      <c r="O19" s="59"/>
+      <c r="P19" s="59"/>
+      <c r="Q19" s="60"/>
     </row>
     <row r="20" spans="2:17" ht="16.5" customHeight="1">
       <c r="B20" s="8"/>
       <c r="D20" t="s">
-        <v>346</v>
-      </c>
-      <c r="L20" s="68"/>
-      <c r="M20" s="69"/>
-      <c r="N20" s="69"/>
-      <c r="O20" s="69"/>
-      <c r="P20" s="69"/>
-      <c r="Q20" s="70"/>
+        <v>345</v>
+      </c>
+      <c r="L20" s="58"/>
+      <c r="M20" s="59"/>
+      <c r="N20" s="59"/>
+      <c r="O20" s="59"/>
+      <c r="P20" s="59"/>
+      <c r="Q20" s="60"/>
     </row>
     <row r="21" spans="2:17" ht="16.5" customHeight="1">
       <c r="B21" s="8"/>
       <c r="D21" t="s">
-        <v>355</v>
-      </c>
-      <c r="L21" s="68"/>
-      <c r="M21" s="69"/>
-      <c r="N21" s="69"/>
-      <c r="O21" s="69"/>
-      <c r="P21" s="69"/>
-      <c r="Q21" s="70"/>
+        <v>354</v>
+      </c>
+      <c r="L21" s="58"/>
+      <c r="M21" s="59"/>
+      <c r="N21" s="59"/>
+      <c r="O21" s="59"/>
+      <c r="P21" s="59"/>
+      <c r="Q21" s="60"/>
     </row>
     <row r="22" spans="2:17" ht="16.5" customHeight="1">
       <c r="B22" s="8"/>
-      <c r="L22" s="68"/>
-      <c r="M22" s="69"/>
-      <c r="N22" s="69"/>
-      <c r="O22" s="69"/>
-      <c r="P22" s="69"/>
-      <c r="Q22" s="70"/>
+      <c r="L22" s="58"/>
+      <c r="M22" s="59"/>
+      <c r="N22" s="59"/>
+      <c r="O22" s="59"/>
+      <c r="P22" s="59"/>
+      <c r="Q22" s="60"/>
     </row>
     <row r="23" spans="2:17" ht="16.5" customHeight="1">
       <c r="B23" s="8"/>
       <c r="D23" t="s">
-        <v>330</v>
-      </c>
-      <c r="L23" s="68"/>
-      <c r="M23" s="69"/>
-      <c r="N23" s="69"/>
-      <c r="O23" s="69"/>
-      <c r="P23" s="69"/>
-      <c r="Q23" s="70"/>
+        <v>329</v>
+      </c>
+      <c r="L23" s="58"/>
+      <c r="M23" s="59"/>
+      <c r="N23" s="59"/>
+      <c r="O23" s="59"/>
+      <c r="P23" s="59"/>
+      <c r="Q23" s="60"/>
     </row>
     <row r="24" spans="2:17" ht="16.5" customHeight="1">
       <c r="B24" s="8"/>
-      <c r="L24" s="68"/>
-      <c r="M24" s="69"/>
-      <c r="N24" s="69"/>
-      <c r="O24" s="69"/>
-      <c r="P24" s="69"/>
-      <c r="Q24" s="70"/>
+      <c r="L24" s="58"/>
+      <c r="M24" s="59"/>
+      <c r="N24" s="59"/>
+      <c r="O24" s="59"/>
+      <c r="P24" s="59"/>
+      <c r="Q24" s="60"/>
     </row>
     <row r="25" spans="2:17" ht="16.5" customHeight="1">
       <c r="B25" s="8"/>
       <c r="D25" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E25" t="s">
-        <v>335</v>
-      </c>
-      <c r="L25" s="68"/>
-      <c r="M25" s="69"/>
-      <c r="N25" s="69"/>
-      <c r="O25" s="69"/>
-      <c r="P25" s="69"/>
-      <c r="Q25" s="70"/>
+        <v>334</v>
+      </c>
+      <c r="L25" s="58"/>
+      <c r="M25" s="59"/>
+      <c r="N25" s="59"/>
+      <c r="O25" s="59"/>
+      <c r="P25" s="59"/>
+      <c r="Q25" s="60"/>
     </row>
     <row r="26" spans="2:17" ht="16.5" customHeight="1">
       <c r="B26" s="8"/>
       <c r="D26" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E26" t="s">
-        <v>334</v>
-      </c>
-      <c r="L26" s="68"/>
-      <c r="M26" s="69"/>
-      <c r="N26" s="69"/>
-      <c r="O26" s="69"/>
-      <c r="P26" s="69"/>
-      <c r="Q26" s="70"/>
+        <v>333</v>
+      </c>
+      <c r="L26" s="58"/>
+      <c r="M26" s="59"/>
+      <c r="N26" s="59"/>
+      <c r="O26" s="59"/>
+      <c r="P26" s="59"/>
+      <c r="Q26" s="60"/>
     </row>
     <row r="27" spans="2:17" ht="16.5" customHeight="1">
       <c r="B27" s="8"/>
-      <c r="L27" s="68"/>
-      <c r="M27" s="69"/>
-      <c r="N27" s="69"/>
-      <c r="O27" s="69"/>
-      <c r="P27" s="69"/>
-      <c r="Q27" s="70"/>
+      <c r="L27" s="58"/>
+      <c r="M27" s="59"/>
+      <c r="N27" s="59"/>
+      <c r="O27" s="59"/>
+      <c r="P27" s="59"/>
+      <c r="Q27" s="60"/>
     </row>
     <row r="28" spans="2:17" ht="16.5" customHeight="1">
       <c r="B28" s="8"/>
-      <c r="L28" s="68"/>
-      <c r="M28" s="69"/>
-      <c r="N28" s="69"/>
-      <c r="O28" s="69"/>
-      <c r="P28" s="69"/>
-      <c r="Q28" s="70"/>
+      <c r="L28" s="58"/>
+      <c r="M28" s="59"/>
+      <c r="N28" s="59"/>
+      <c r="O28" s="59"/>
+      <c r="P28" s="59"/>
+      <c r="Q28" s="60"/>
     </row>
     <row r="29" spans="2:17" ht="16.5" customHeight="1">
       <c r="B29" s="8"/>
-      <c r="L29" s="68"/>
-      <c r="M29" s="69"/>
-      <c r="N29" s="69"/>
-      <c r="O29" s="69"/>
-      <c r="P29" s="69"/>
-      <c r="Q29" s="70"/>
+      <c r="L29" s="58"/>
+      <c r="M29" s="59"/>
+      <c r="N29" s="59"/>
+      <c r="O29" s="59"/>
+      <c r="P29" s="59"/>
+      <c r="Q29" s="60"/>
     </row>
     <row r="30" spans="2:17" ht="16.5" customHeight="1">
       <c r="B30" s="8"/>
-      <c r="L30" s="71"/>
-      <c r="M30" s="72"/>
-      <c r="N30" s="72"/>
-      <c r="O30" s="72"/>
-      <c r="P30" s="72"/>
-      <c r="Q30" s="73"/>
-    </row>
-    <row r="33" spans="2:21">
+      <c r="L30" s="61"/>
+      <c r="M30" s="62"/>
+      <c r="N30" s="62"/>
+      <c r="O30" s="62"/>
+      <c r="P30" s="62"/>
+      <c r="Q30" s="63"/>
+    </row>
+    <row r="33" spans="2:24">
       <c r="B33" s="8"/>
     </row>
-    <row r="34" spans="2:21">
+    <row r="34" spans="2:24">
       <c r="B34" s="8" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="35" spans="2:21">
+    <row r="35" spans="2:24">
       <c r="B35" s="8"/>
       <c r="C35" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="36" spans="2:21" ht="17.25" thickBot="1">
+    <row r="36" spans="2:24" ht="17.25" thickBot="1">
       <c r="B36" s="8"/>
     </row>
-    <row r="37" spans="2:21">
+    <row r="37" spans="2:24">
       <c r="B37" s="8"/>
       <c r="D37" s="27" t="s">
         <v>304</v>
       </c>
-      <c r="E37" s="77" t="s">
+      <c r="E37" s="67" t="s">
         <v>284</v>
       </c>
-      <c r="F37" s="113"/>
+      <c r="F37" s="89"/>
       <c r="G37" s="52" t="s">
         <v>285</v>
       </c>
       <c r="H37" s="52"/>
-      <c r="I37" s="77" t="s">
-        <v>336</v>
-      </c>
-      <c r="J37" s="84"/>
-      <c r="K37" s="107"/>
-      <c r="L37" s="51" t="s">
+      <c r="I37" s="67" t="s">
+        <v>335</v>
+      </c>
+      <c r="J37" s="89"/>
+      <c r="K37" s="51" t="s">
         <v>287</v>
       </c>
-      <c r="M37" s="51"/>
-      <c r="N37" s="49" t="s">
+      <c r="L37" s="51"/>
+      <c r="M37" s="49" t="s">
         <v>286</v>
       </c>
-      <c r="O37" s="51"/>
-      <c r="P37" s="49" t="s">
+      <c r="N37" s="51"/>
+      <c r="O37" s="49" t="s">
         <v>288</v>
       </c>
-      <c r="Q37" s="51"/>
-      <c r="R37" s="49" t="s">
+      <c r="P37" s="51"/>
+      <c r="Q37" s="49" t="s">
         <v>289</v>
       </c>
-      <c r="S37" s="52"/>
-      <c r="T37" s="49" t="s">
+      <c r="R37" s="52"/>
+      <c r="S37" s="75" t="s">
         <v>290</v>
       </c>
-      <c r="U37" s="51"/>
-    </row>
-    <row r="38" spans="2:21">
+      <c r="T37" s="76"/>
+      <c r="U37" s="75" t="s">
+        <v>370</v>
+      </c>
+      <c r="V37" s="76"/>
+      <c r="W37" s="75" t="s">
+        <v>372</v>
+      </c>
+      <c r="X37" s="77"/>
+    </row>
+    <row r="38" spans="2:24">
       <c r="B38" s="8"/>
       <c r="D38" s="27" t="s">
         <v>300</v>
       </c>
-      <c r="E38" s="108" t="s">
+      <c r="E38" s="86" t="s">
         <v>301</v>
       </c>
-      <c r="F38" s="114"/>
+      <c r="F38" s="90"/>
       <c r="G38" s="52" t="s">
         <v>316</v>
       </c>
       <c r="H38" s="52"/>
-      <c r="I38" s="108" t="s">
+      <c r="I38" s="86" t="s">
         <v>316</v>
       </c>
-      <c r="J38" s="81"/>
-      <c r="K38" s="109"/>
-      <c r="L38" s="51" t="s">
+      <c r="J38" s="90"/>
+      <c r="K38" s="51" t="s">
         <v>303</v>
       </c>
-      <c r="M38" s="51"/>
-      <c r="N38" s="49" t="s">
+      <c r="L38" s="51"/>
+      <c r="M38" s="49" t="s">
         <v>300</v>
       </c>
-      <c r="O38" s="51"/>
-      <c r="P38" s="49" t="s">
+      <c r="N38" s="51"/>
+      <c r="O38" s="49" t="s">
         <v>301</v>
       </c>
-      <c r="Q38" s="51"/>
-      <c r="R38" s="49" t="s">
+      <c r="P38" s="51"/>
+      <c r="Q38" s="49" t="s">
         <v>301</v>
       </c>
-      <c r="S38" s="52"/>
-      <c r="T38" s="49" t="s">
-        <v>302</v>
-      </c>
-      <c r="U38" s="51"/>
-    </row>
-    <row r="39" spans="2:21" ht="17.25" thickBot="1">
+      <c r="R38" s="52"/>
+      <c r="S38" s="75" t="s">
+        <v>368</v>
+      </c>
+      <c r="T38" s="76"/>
+      <c r="U38" s="75" t="s">
+        <v>301</v>
+      </c>
+      <c r="V38" s="76"/>
+      <c r="W38" s="75" t="s">
+        <v>301</v>
+      </c>
+      <c r="X38" s="77"/>
+    </row>
+    <row r="39" spans="2:24" ht="17.25" thickBot="1">
       <c r="B39" s="8"/>
       <c r="D39" s="27" t="s">
         <v>291</v>
       </c>
-      <c r="E39" s="78" t="s">
+      <c r="E39" s="68" t="s">
         <v>292</v>
       </c>
-      <c r="F39" s="115"/>
-      <c r="G39" s="112" t="s">
+      <c r="F39" s="91"/>
+      <c r="G39" s="88" t="s">
         <v>309</v>
       </c>
       <c r="H39" s="52"/>
-      <c r="I39" s="78" t="s">
-        <v>337</v>
-      </c>
-      <c r="J39" s="110"/>
-      <c r="K39" s="111"/>
-      <c r="L39" s="51" t="s">
+      <c r="I39" s="68" t="s">
+        <v>336</v>
+      </c>
+      <c r="J39" s="91"/>
+      <c r="K39" s="51" t="s">
         <v>294</v>
       </c>
-      <c r="M39" s="51"/>
-      <c r="N39" s="49" t="s">
+      <c r="L39" s="51"/>
+      <c r="M39" s="49" t="s">
         <v>293</v>
       </c>
-      <c r="O39" s="51"/>
-      <c r="P39" s="49" t="s">
+      <c r="N39" s="51"/>
+      <c r="O39" s="49" t="s">
         <v>295</v>
       </c>
-      <c r="Q39" s="51"/>
-      <c r="R39" s="49" t="s">
+      <c r="P39" s="51"/>
+      <c r="Q39" s="49" t="s">
         <v>296</v>
       </c>
-      <c r="S39" s="52"/>
-      <c r="T39" s="49" t="s">
+      <c r="R39" s="52"/>
+      <c r="S39" s="78" t="s">
         <v>297</v>
       </c>
-      <c r="U39" s="51"/>
-    </row>
-    <row r="40" spans="2:21">
+      <c r="T39" s="76"/>
+      <c r="U39" s="78" t="s">
+        <v>369</v>
+      </c>
+      <c r="V39" s="76"/>
+      <c r="W39" s="78" t="s">
+        <v>371</v>
+      </c>
+      <c r="X39" s="77"/>
+    </row>
+    <row r="40" spans="2:24">
       <c r="B40" s="8"/>
       <c r="D40" s="53">
         <f>ROW()-ROW($D$39)</f>
         <v>1</v>
       </c>
-      <c r="E40" s="82">
+      <c r="E40" s="72">
         <v>3</v>
       </c>
-      <c r="F40" s="80"/>
-      <c r="G40" s="80" t="s">
+      <c r="F40" s="70"/>
+      <c r="G40" s="70" t="s">
         <v>298</v>
       </c>
-      <c r="H40" s="80"/>
-      <c r="I40" s="80" t="s">
-        <v>339</v>
-      </c>
-      <c r="J40" s="80"/>
-      <c r="K40" s="80"/>
-      <c r="L40" s="80" t="s">
+      <c r="H40" s="70"/>
+      <c r="I40" s="70" t="s">
+        <v>338</v>
+      </c>
+      <c r="J40" s="70"/>
+      <c r="K40" s="70" t="s">
         <v>299</v>
       </c>
-      <c r="M40" s="80"/>
-      <c r="N40" s="80">
+      <c r="L40" s="70"/>
+      <c r="M40" s="70">
         <v>5</v>
       </c>
-      <c r="O40" s="80"/>
-      <c r="P40" s="80">
+      <c r="N40" s="70"/>
+      <c r="O40" s="70">
         <v>30</v>
       </c>
-      <c r="Q40" s="80"/>
-      <c r="R40" s="80">
+      <c r="P40" s="70"/>
+      <c r="Q40" s="70">
         <v>30</v>
       </c>
-      <c r="S40" s="80"/>
-      <c r="T40" s="80" t="s">
-        <v>302</v>
-      </c>
-      <c r="U40" s="86"/>
-    </row>
-    <row r="41" spans="2:21">
+      <c r="R40" s="70"/>
+      <c r="S40" s="93" t="s">
+        <v>373</v>
+      </c>
+      <c r="T40" s="93"/>
+      <c r="U40" s="93">
+        <v>75</v>
+      </c>
+      <c r="V40" s="93"/>
+      <c r="W40" s="93">
+        <v>30</v>
+      </c>
+      <c r="X40" s="81"/>
+    </row>
+    <row r="41" spans="2:24">
       <c r="B41" s="8"/>
       <c r="D41" s="53">
         <f t="shared" ref="D41:D43" si="0">ROW()-ROW($D$39)</f>
         <v>2</v>
       </c>
-      <c r="E41" s="80" t="s">
+      <c r="E41" s="70" t="s">
         <v>302</v>
       </c>
-      <c r="F41" s="80"/>
-      <c r="G41" s="80" t="s">
+      <c r="F41" s="70"/>
+      <c r="G41" s="70" t="s">
         <v>302</v>
       </c>
-      <c r="H41" s="80"/>
-      <c r="I41" s="80" t="s">
-        <v>340</v>
-      </c>
-      <c r="J41" s="80"/>
-      <c r="K41" s="80"/>
-      <c r="L41" s="80" t="s">
+      <c r="H41" s="70"/>
+      <c r="I41" s="70" t="s">
+        <v>339</v>
+      </c>
+      <c r="J41" s="70"/>
+      <c r="K41" s="70" t="s">
         <v>302</v>
       </c>
-      <c r="M41" s="80"/>
-      <c r="N41" s="83"/>
-      <c r="O41" s="67"/>
-      <c r="P41" s="83"/>
-      <c r="Q41" s="67"/>
-      <c r="R41" s="83"/>
-      <c r="S41" s="67"/>
-      <c r="T41" s="83"/>
-      <c r="U41" s="54"/>
-    </row>
-    <row r="42" spans="2:21">
+      <c r="L41" s="70"/>
+      <c r="M41" s="11"/>
+      <c r="O41" s="11"/>
+      <c r="Q41" s="11"/>
+      <c r="S41" s="93"/>
+      <c r="T41" s="93"/>
+      <c r="U41" s="93"/>
+      <c r="V41" s="93"/>
+      <c r="W41" s="93"/>
+      <c r="X41" s="81"/>
+    </row>
+    <row r="42" spans="2:24">
       <c r="B42" s="8"/>
       <c r="D42" s="53">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="E42" s="80" t="s">
+      <c r="E42" s="70" t="s">
         <v>302</v>
       </c>
-      <c r="F42" s="80"/>
-      <c r="G42" s="80" t="s">
+      <c r="F42" s="70"/>
+      <c r="G42" s="70" t="s">
         <v>302</v>
       </c>
-      <c r="H42" s="80"/>
-      <c r="I42" s="80" t="s">
-        <v>349</v>
-      </c>
-      <c r="J42" s="80"/>
-      <c r="K42" s="80"/>
-      <c r="L42" s="80" t="s">
+      <c r="H42" s="70"/>
+      <c r="I42" s="70" t="s">
+        <v>348</v>
+      </c>
+      <c r="J42" s="70"/>
+      <c r="K42" s="70" t="s">
         <v>302</v>
       </c>
-      <c r="M42" s="80"/>
-      <c r="N42" s="83"/>
-      <c r="O42" s="67"/>
-      <c r="P42" s="83"/>
-      <c r="Q42" s="67"/>
-      <c r="R42" s="83"/>
-      <c r="S42" s="67"/>
-      <c r="T42" s="83"/>
-      <c r="U42" s="54"/>
-    </row>
-    <row r="43" spans="2:21">
+      <c r="L42" s="70"/>
+      <c r="M42" s="11"/>
+      <c r="O42" s="11"/>
+      <c r="Q42" s="11"/>
+      <c r="S42" s="93"/>
+      <c r="T42" s="93"/>
+      <c r="U42" s="93"/>
+      <c r="V42" s="93"/>
+      <c r="W42" s="93"/>
+      <c r="X42" s="81"/>
+    </row>
+    <row r="43" spans="2:24">
       <c r="B43" s="8"/>
-      <c r="D43" s="55">
+      <c r="D43" s="54">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="E43" s="56" t="s">
+      <c r="E43" s="55" t="s">
         <v>302</v>
       </c>
-      <c r="F43" s="56"/>
-      <c r="G43" s="56" t="s">
+      <c r="F43" s="55"/>
+      <c r="G43" s="55" t="s">
         <v>302</v>
       </c>
-      <c r="H43" s="56"/>
-      <c r="I43" s="56" t="s">
+      <c r="H43" s="55"/>
+      <c r="I43" s="55" t="s">
         <v>302</v>
       </c>
-      <c r="J43" s="56"/>
-      <c r="K43" s="56"/>
-      <c r="L43" s="57" t="s">
-        <v>350</v>
-      </c>
-      <c r="M43" s="57"/>
-      <c r="N43" s="57"/>
-      <c r="O43" s="57"/>
-      <c r="P43" s="57"/>
-      <c r="Q43" s="57"/>
-      <c r="R43" s="57"/>
-      <c r="S43" s="57"/>
-      <c r="T43" s="57"/>
-      <c r="U43" s="58"/>
-    </row>
-    <row r="44" spans="2:21">
+      <c r="J43" s="55"/>
+      <c r="K43" s="56" t="s">
+        <v>349</v>
+      </c>
+      <c r="L43" s="56"/>
+      <c r="M43" s="56"/>
+      <c r="N43" s="56"/>
+      <c r="O43" s="56"/>
+      <c r="P43" s="56"/>
+      <c r="Q43" s="56"/>
+      <c r="R43" s="56"/>
+      <c r="S43" s="83"/>
+      <c r="T43" s="83"/>
+      <c r="U43" s="83"/>
+      <c r="V43" s="83"/>
+      <c r="W43" s="83"/>
+      <c r="X43" s="110"/>
+    </row>
+    <row r="44" spans="2:24">
       <c r="B44" s="8"/>
     </row>
-    <row r="45" spans="2:21">
+    <row r="45" spans="2:24">
       <c r="B45" s="8"/>
       <c r="D45" t="s">
         <v>306</v>
@@ -10289,7 +12465,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="46" spans="2:21">
+    <row r="46" spans="2:24">
       <c r="B46" s="8"/>
       <c r="D46" s="8" t="s">
         <v>307</v>
@@ -10298,7 +12474,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="47" spans="2:21">
+    <row r="47" spans="2:24">
       <c r="B47" s="8"/>
       <c r="D47" t="s">
         <v>315</v>
@@ -10307,13 +12483,13 @@
         <v>310</v>
       </c>
     </row>
-    <row r="48" spans="2:21">
+    <row r="48" spans="2:24">
       <c r="B48" s="8"/>
       <c r="D48" s="8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="49" spans="2:9">
@@ -10337,12 +12513,12 @@
     <row r="51" spans="2:9">
       <c r="B51" s="8"/>
       <c r="D51" s="18" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E51" s="18"/>
       <c r="F51" s="18"/>
       <c r="G51" s="18" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H51" s="18"/>
       <c r="I51" s="18"/>
@@ -10350,18 +12526,46 @@
     <row r="52" spans="2:9">
       <c r="B52" s="8"/>
       <c r="D52" s="18" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E52" s="18"/>
       <c r="F52" s="18"/>
       <c r="G52" s="18" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H52" s="18"/>
       <c r="I52" s="18"/>
     </row>
     <row r="53" spans="2:9">
       <c r="B53" s="8"/>
+      <c r="D53" s="18" t="s">
+        <v>297</v>
+      </c>
+      <c r="E53" s="18"/>
+      <c r="F53" s="18"/>
+      <c r="G53" s="18" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9">
+      <c r="D54" s="18" t="s">
+        <v>369</v>
+      </c>
+      <c r="E54" s="18"/>
+      <c r="F54" s="18"/>
+      <c r="G54" s="18" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9">
+      <c r="D55" s="18" t="s">
+        <v>371</v>
+      </c>
+      <c r="E55" s="18"/>
+      <c r="F55" s="18"/>
+      <c r="G55" s="18" t="s">
+        <v>376</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -10370,9 +12574,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90669897-7B19-41C3-ACE9-893F9F9C4143}">
-  <dimension ref="A1:V51"/>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90669897-7B19-41C3-ACE9-893F9F9C4143}">
+  <dimension ref="A1:X54"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="3.375" customWidth="1"/>
@@ -10585,264 +12789,301 @@
         <v>280</v>
       </c>
     </row>
-    <row r="33" spans="2:21">
+    <row r="33" spans="2:24">
       <c r="B33" s="8" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="34" spans="2:21">
+    <row r="34" spans="2:24">
       <c r="C34" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="35" spans="2:21" ht="17.25" thickBot="1"/>
-    <row r="36" spans="2:21">
-      <c r="D36" s="97" t="s">
+    <row r="35" spans="2:24" ht="17.25" thickBot="1"/>
+    <row r="36" spans="2:24">
+      <c r="D36" s="79" t="s">
         <v>304</v>
       </c>
-      <c r="E36" s="89" t="s">
+      <c r="E36" s="75" t="s">
         <v>284</v>
       </c>
-      <c r="F36" s="90"/>
-      <c r="G36" s="89" t="s">
+      <c r="F36" s="76"/>
+      <c r="G36" s="75" t="s">
         <v>285</v>
       </c>
-      <c r="H36" s="90"/>
-      <c r="I36" s="105" t="s">
+      <c r="H36" s="76"/>
+      <c r="I36" s="85" t="s">
+        <v>335</v>
+      </c>
+      <c r="J36" s="85"/>
+      <c r="K36" s="112" t="s">
+        <v>287</v>
+      </c>
+      <c r="L36" s="113"/>
+      <c r="M36" s="73" t="s">
+        <v>286</v>
+      </c>
+      <c r="N36" s="73"/>
+      <c r="O36" s="73" t="s">
+        <v>288</v>
+      </c>
+      <c r="P36" s="73"/>
+      <c r="Q36" s="73" t="s">
+        <v>289</v>
+      </c>
+      <c r="R36" s="89"/>
+      <c r="S36" s="75" t="s">
+        <v>290</v>
+      </c>
+      <c r="T36" s="76"/>
+      <c r="U36" s="75" t="s">
+        <v>370</v>
+      </c>
+      <c r="V36" s="76"/>
+      <c r="W36" s="75" t="s">
+        <v>372</v>
+      </c>
+      <c r="X36" s="77"/>
+    </row>
+    <row r="37" spans="2:24">
+      <c r="D37" s="79" t="s">
+        <v>300</v>
+      </c>
+      <c r="E37" s="75" t="s">
+        <v>301</v>
+      </c>
+      <c r="F37" s="76"/>
+      <c r="G37" s="75" t="s">
+        <v>316</v>
+      </c>
+      <c r="H37" s="76"/>
+      <c r="I37" s="85" t="s">
+        <v>316</v>
+      </c>
+      <c r="J37" s="85"/>
+      <c r="K37" s="86" t="s">
+        <v>303</v>
+      </c>
+      <c r="L37" s="71"/>
+      <c r="M37" s="71" t="s">
+        <v>300</v>
+      </c>
+      <c r="N37" s="71"/>
+      <c r="O37" s="71" t="s">
+        <v>301</v>
+      </c>
+      <c r="P37" s="71"/>
+      <c r="Q37" s="71" t="s">
+        <v>301</v>
+      </c>
+      <c r="R37" s="90"/>
+      <c r="S37" s="75" t="s">
+        <v>368</v>
+      </c>
+      <c r="T37" s="76"/>
+      <c r="U37" s="75" t="s">
+        <v>301</v>
+      </c>
+      <c r="V37" s="76"/>
+      <c r="W37" s="75" t="s">
+        <v>301</v>
+      </c>
+      <c r="X37" s="77"/>
+    </row>
+    <row r="38" spans="2:24" ht="17.25" thickBot="1">
+      <c r="D38" s="79" t="s">
+        <v>291</v>
+      </c>
+      <c r="E38" s="78" t="s">
+        <v>292</v>
+      </c>
+      <c r="F38" s="76"/>
+      <c r="G38" s="78" t="s">
+        <v>309</v>
+      </c>
+      <c r="H38" s="76"/>
+      <c r="I38" s="85" t="s">
         <v>336</v>
       </c>
-      <c r="J36" s="105"/>
-      <c r="K36" s="106"/>
-      <c r="L36" s="116" t="s">
-        <v>287</v>
-      </c>
-      <c r="M36" s="87"/>
-      <c r="N36" s="87" t="s">
-        <v>286</v>
-      </c>
-      <c r="O36" s="87"/>
-      <c r="P36" s="87" t="s">
-        <v>288</v>
-      </c>
-      <c r="Q36" s="87"/>
-      <c r="R36" s="87" t="s">
-        <v>289</v>
-      </c>
-      <c r="S36" s="117"/>
-      <c r="T36" s="91" t="s">
-        <v>290</v>
-      </c>
-      <c r="U36" s="91"/>
-    </row>
-    <row r="37" spans="2:21">
-      <c r="D37" s="97" t="s">
-        <v>300</v>
-      </c>
-      <c r="E37" s="89" t="s">
-        <v>301</v>
-      </c>
-      <c r="F37" s="90"/>
-      <c r="G37" s="89" t="s">
-        <v>316</v>
-      </c>
-      <c r="H37" s="90"/>
-      <c r="I37" s="105" t="s">
-        <v>316</v>
-      </c>
-      <c r="J37" s="105"/>
-      <c r="K37" s="106"/>
-      <c r="L37" s="118" t="s">
-        <v>303</v>
-      </c>
-      <c r="M37" s="88"/>
-      <c r="N37" s="88" t="s">
-        <v>300</v>
-      </c>
-      <c r="O37" s="88"/>
-      <c r="P37" s="88" t="s">
-        <v>301</v>
-      </c>
-      <c r="Q37" s="88"/>
-      <c r="R37" s="88" t="s">
-        <v>301</v>
-      </c>
-      <c r="S37" s="119"/>
-      <c r="T37" s="91" t="s">
-        <v>302</v>
-      </c>
-      <c r="U37" s="91"/>
-    </row>
-    <row r="38" spans="2:21" ht="17.25" thickBot="1">
-      <c r="D38" s="97" t="s">
-        <v>291</v>
-      </c>
-      <c r="E38" s="92" t="s">
-        <v>292</v>
-      </c>
-      <c r="F38" s="90"/>
-      <c r="G38" s="92" t="s">
-        <v>309</v>
-      </c>
-      <c r="H38" s="90"/>
-      <c r="I38" s="105" t="s">
-        <v>337</v>
-      </c>
-      <c r="J38" s="105"/>
-      <c r="K38" s="106"/>
-      <c r="L38" s="120" t="s">
+      <c r="J38" s="85"/>
+      <c r="K38" s="68" t="s">
         <v>294</v>
       </c>
-      <c r="M38" s="121"/>
-      <c r="N38" s="121" t="s">
+      <c r="L38" s="87"/>
+      <c r="M38" s="87" t="s">
         <v>293</v>
       </c>
-      <c r="O38" s="121"/>
-      <c r="P38" s="121" t="s">
+      <c r="N38" s="87"/>
+      <c r="O38" s="87" t="s">
         <v>295</v>
       </c>
-      <c r="Q38" s="121"/>
-      <c r="R38" s="121" t="s">
+      <c r="P38" s="87"/>
+      <c r="Q38" s="87" t="s">
         <v>296</v>
       </c>
-      <c r="S38" s="122"/>
-      <c r="T38" s="91" t="s">
+      <c r="R38" s="91"/>
+      <c r="S38" s="78" t="s">
         <v>297</v>
       </c>
-      <c r="U38" s="91"/>
-    </row>
-    <row r="39" spans="2:21">
-      <c r="D39" s="98">
+      <c r="T38" s="76"/>
+      <c r="U38" s="78" t="s">
+        <v>369</v>
+      </c>
+      <c r="V38" s="76"/>
+      <c r="W38" s="78" t="s">
+        <v>371</v>
+      </c>
+      <c r="X38" s="77"/>
+    </row>
+    <row r="39" spans="2:24">
+      <c r="D39" s="80">
         <f>ROW()-ROW($D$38)</f>
         <v>1</v>
       </c>
-      <c r="E39" s="93">
+      <c r="E39" s="92">
         <v>3</v>
       </c>
-      <c r="F39" s="94"/>
-      <c r="G39" s="94" t="s">
+      <c r="F39" s="93"/>
+      <c r="G39" s="93" t="s">
         <v>298</v>
       </c>
-      <c r="H39" s="94"/>
-      <c r="I39" s="94" t="s">
-        <v>339</v>
-      </c>
-      <c r="J39" s="94"/>
-      <c r="K39" s="94"/>
-      <c r="L39" s="94" t="s">
+      <c r="H39" s="93"/>
+      <c r="I39" s="93" t="s">
+        <v>338</v>
+      </c>
+      <c r="J39" s="93"/>
+      <c r="K39" s="93" t="s">
         <v>299</v>
       </c>
-      <c r="M39" s="94"/>
-      <c r="N39" s="94">
+      <c r="L39" s="93"/>
+      <c r="M39" s="93">
         <v>5</v>
       </c>
-      <c r="O39" s="94"/>
-      <c r="P39" s="94">
+      <c r="N39" s="93"/>
+      <c r="O39" s="93">
         <v>30</v>
       </c>
-      <c r="Q39" s="94"/>
-      <c r="R39" s="94">
+      <c r="P39" s="93"/>
+      <c r="Q39" s="93">
         <v>30</v>
       </c>
-      <c r="S39" s="94"/>
-      <c r="T39" s="94" t="s">
-        <v>302</v>
-      </c>
-      <c r="U39" s="99"/>
-    </row>
-    <row r="40" spans="2:21">
-      <c r="D40" s="98">
+      <c r="R39" s="93"/>
+      <c r="S39" s="93" t="s">
+        <v>373</v>
+      </c>
+      <c r="T39" s="93"/>
+      <c r="U39" s="93">
+        <v>75</v>
+      </c>
+      <c r="V39" s="93"/>
+      <c r="W39" s="93">
+        <v>30</v>
+      </c>
+      <c r="X39" s="81"/>
+    </row>
+    <row r="40" spans="2:24">
+      <c r="D40" s="80">
         <f t="shared" ref="D40:D42" si="0">ROW()-ROW($D$38)</f>
         <v>2</v>
       </c>
-      <c r="E40" s="94" t="s">
+      <c r="E40" s="93" t="s">
         <v>302</v>
       </c>
-      <c r="F40" s="94"/>
-      <c r="G40" s="94" t="s">
+      <c r="F40" s="93"/>
+      <c r="G40" s="93" t="s">
         <v>302</v>
       </c>
-      <c r="H40" s="94"/>
-      <c r="I40" s="94" t="s">
-        <v>340</v>
-      </c>
-      <c r="J40" s="94"/>
-      <c r="K40" s="94"/>
-      <c r="L40" s="94" t="s">
+      <c r="H40" s="93"/>
+      <c r="I40" s="93" t="s">
+        <v>339</v>
+      </c>
+      <c r="J40" s="93"/>
+      <c r="K40" s="93" t="s">
         <v>302</v>
       </c>
+      <c r="L40" s="93"/>
       <c r="M40" s="94"/>
-      <c r="N40" s="95"/>
-      <c r="O40" s="96"/>
-      <c r="P40" s="95"/>
-      <c r="Q40" s="96"/>
-      <c r="R40" s="95"/>
-      <c r="S40" s="96"/>
-      <c r="T40" s="95"/>
-      <c r="U40" s="100"/>
-    </row>
-    <row r="41" spans="2:21">
-      <c r="D41" s="98">
+      <c r="N40" s="18"/>
+      <c r="O40" s="94"/>
+      <c r="P40" s="18"/>
+      <c r="Q40" s="94"/>
+      <c r="R40" s="18"/>
+      <c r="S40" s="93"/>
+      <c r="T40" s="93"/>
+      <c r="U40" s="93"/>
+      <c r="V40" s="93"/>
+      <c r="W40" s="93"/>
+      <c r="X40" s="81"/>
+    </row>
+    <row r="41" spans="2:24">
+      <c r="D41" s="80">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="E41" s="94" t="s">
+      <c r="E41" s="93" t="s">
         <v>302</v>
       </c>
-      <c r="F41" s="94"/>
-      <c r="G41" s="94" t="s">
+      <c r="F41" s="93"/>
+      <c r="G41" s="93" t="s">
         <v>302</v>
       </c>
-      <c r="H41" s="94"/>
-      <c r="I41" s="94" t="s">
-        <v>349</v>
-      </c>
-      <c r="J41" s="94"/>
-      <c r="K41" s="94"/>
-      <c r="L41" s="94" t="s">
+      <c r="H41" s="93"/>
+      <c r="I41" s="93" t="s">
+        <v>348</v>
+      </c>
+      <c r="J41" s="93"/>
+      <c r="K41" s="93" t="s">
         <v>302</v>
       </c>
+      <c r="L41" s="93"/>
       <c r="M41" s="94"/>
-      <c r="N41" s="95"/>
-      <c r="O41" s="96"/>
-      <c r="P41" s="95"/>
-      <c r="Q41" s="96"/>
-      <c r="R41" s="95"/>
-      <c r="S41" s="96"/>
-      <c r="T41" s="95"/>
-      <c r="U41" s="100"/>
-    </row>
-    <row r="42" spans="2:21">
-      <c r="D42" s="101">
+      <c r="N41" s="18"/>
+      <c r="O41" s="94"/>
+      <c r="P41" s="18"/>
+      <c r="Q41" s="94"/>
+      <c r="R41" s="18"/>
+      <c r="S41" s="93"/>
+      <c r="T41" s="93"/>
+      <c r="U41" s="93"/>
+      <c r="V41" s="93"/>
+      <c r="W41" s="93"/>
+      <c r="X41" s="81"/>
+    </row>
+    <row r="42" spans="2:24">
+      <c r="D42" s="82">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="E42" s="102" t="s">
+      <c r="E42" s="83" t="s">
         <v>302</v>
       </c>
-      <c r="F42" s="102"/>
-      <c r="G42" s="102" t="s">
+      <c r="F42" s="83"/>
+      <c r="G42" s="83" t="s">
         <v>302</v>
       </c>
-      <c r="H42" s="102"/>
-      <c r="I42" s="102" t="s">
+      <c r="H42" s="83"/>
+      <c r="I42" s="83" t="s">
         <v>302</v>
       </c>
-      <c r="J42" s="102"/>
-      <c r="K42" s="102"/>
-      <c r="L42" s="103" t="s">
-        <v>350</v>
-      </c>
-      <c r="M42" s="103"/>
-      <c r="N42" s="103"/>
-      <c r="O42" s="103"/>
-      <c r="P42" s="103"/>
-      <c r="Q42" s="103"/>
-      <c r="R42" s="103"/>
-      <c r="S42" s="103"/>
-      <c r="T42" s="103"/>
-      <c r="U42" s="104"/>
-    </row>
-    <row r="44" spans="2:21">
+      <c r="J42" s="83"/>
+      <c r="K42" s="84" t="s">
+        <v>349</v>
+      </c>
+      <c r="L42" s="84"/>
+      <c r="M42" s="84"/>
+      <c r="N42" s="84"/>
+      <c r="O42" s="84"/>
+      <c r="P42" s="84"/>
+      <c r="Q42" s="84"/>
+      <c r="R42" s="84"/>
+      <c r="S42" s="83"/>
+      <c r="T42" s="83"/>
+      <c r="U42" s="83"/>
+      <c r="V42" s="83"/>
+      <c r="W42" s="83"/>
+      <c r="X42" s="110"/>
+    </row>
+    <row r="44" spans="2:24">
       <c r="D44" t="s">
         <v>306</v>
       </c>
@@ -10850,7 +13091,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="45" spans="2:21">
+    <row r="45" spans="2:24">
       <c r="D45" s="18" t="s">
         <v>307</v>
       </c>
@@ -10858,7 +13099,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="46" spans="2:21">
+    <row r="46" spans="2:24">
       <c r="D46" s="18" t="s">
         <v>315</v>
       </c>
@@ -10866,15 +13107,15 @@
         <v>310</v>
       </c>
     </row>
-    <row r="47" spans="2:21">
+    <row r="47" spans="2:24">
       <c r="D47" s="18" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G47" s="18" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="48" spans="2:21">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24">
       <c r="D48" s="8" t="s">
         <v>313</v>
       </c>
@@ -10892,23 +13133,23 @@
     </row>
     <row r="50" spans="4:22">
       <c r="D50" s="8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E50" s="18"/>
       <c r="F50" s="18"/>
       <c r="G50" s="8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H50" s="18"/>
     </row>
     <row r="51" spans="4:22">
       <c r="D51" s="8" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E51" s="18"/>
       <c r="F51" s="18"/>
       <c r="G51" s="8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H51" s="18"/>
       <c r="Q51" s="18"/>
@@ -10918,117 +13159,848 @@
       <c r="U51" s="18"/>
       <c r="V51" s="18"/>
     </row>
+    <row r="52" spans="4:22">
+      <c r="D52" s="18" t="s">
+        <v>297</v>
+      </c>
+      <c r="E52" s="18"/>
+      <c r="F52" s="18"/>
+      <c r="G52" s="18" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="53" spans="4:22">
+      <c r="D53" s="18" t="s">
+        <v>369</v>
+      </c>
+      <c r="E53" s="18"/>
+      <c r="F53" s="18"/>
+      <c r="G53" s="18" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="54" spans="4:22">
+      <c r="D54" s="18" t="s">
+        <v>371</v>
+      </c>
+      <c r="E54" s="18"/>
+      <c r="F54" s="18"/>
+      <c r="G54" s="18" t="s">
+        <v>376</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96B3948A-F2EB-4210-816C-FE29D536AFF8}">
-  <dimension ref="A1:G32"/>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96B3948A-F2EB-4210-816C-FE29D536AFF8}">
+  <dimension ref="A1:X54"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="3" width="3.375" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
-    <col min="11" max="12" width="9" customWidth="1"/>
-    <col min="14" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="9" customWidth="1"/>
+    <col min="24" max="26" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="26.25">
+    <row r="1" spans="1:22" ht="26.25">
       <c r="A1" s="47" t="s">
         <v>321</v>
       </c>
       <c r="B1" s="8"/>
     </row>
-    <row r="2" spans="1:7" ht="15.75" customHeight="1">
+    <row r="2" spans="1:22" ht="15.75" customHeight="1">
       <c r="A2" s="47"/>
       <c r="B2" s="8"/>
     </row>
-    <row r="3" spans="1:7" ht="15.75" customHeight="1">
+    <row r="3" spans="1:22" ht="15.75" customHeight="1">
       <c r="A3" s="47"/>
       <c r="B3" s="8" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" customHeight="1">
+    <row r="4" spans="1:22" ht="15.75" customHeight="1">
       <c r="A4" s="47"/>
       <c r="B4" s="8"/>
       <c r="C4" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15.75" customHeight="1">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="15.75" customHeight="1">
       <c r="A5" s="47"/>
       <c r="B5" s="8"/>
     </row>
-    <row r="6" spans="1:7" ht="15.75" customHeight="1">
+    <row r="6" spans="1:22" ht="15.75" customHeight="1">
       <c r="B6" s="8" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" customHeight="1">
+    <row r="7" spans="1:22" ht="15.75" customHeight="1">
       <c r="B7" s="8"/>
       <c r="C7" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15.75" customHeight="1">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="15.75" customHeight="1">
       <c r="B8" s="8"/>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:22">
       <c r="B9" s="8" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22">
+      <c r="C10" s="8"/>
+    </row>
+    <row r="11" spans="1:22">
+      <c r="C11" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="48" t="s">
+        <v>355</v>
+      </c>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48" t="s">
+        <v>359</v>
+      </c>
+      <c r="G11" s="48"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="48" t="s">
+        <v>377</v>
+      </c>
+      <c r="K11" s="48"/>
+      <c r="L11" s="48"/>
+      <c r="M11" s="48" t="s">
+        <v>378</v>
+      </c>
+      <c r="N11" s="48"/>
+      <c r="O11" s="48"/>
+      <c r="Q11" s="50" t="s">
+        <v>341</v>
+      </c>
+      <c r="R11" s="52"/>
+      <c r="S11" s="52"/>
+      <c r="T11" s="52"/>
+      <c r="U11" s="51"/>
+      <c r="V11" s="51"/>
+    </row>
+    <row r="12" spans="1:22">
+      <c r="C12" s="11">
+        <f t="shared" ref="C12:C20" si="0">ROW()-ROW($C$11)</f>
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>356</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>367</v>
+      </c>
+      <c r="G12" s="70"/>
+      <c r="H12" s="70"/>
+      <c r="I12" s="70"/>
+      <c r="J12" s="70" t="s">
+        <v>357</v>
+      </c>
+      <c r="K12" s="70"/>
+      <c r="L12" s="70"/>
+      <c r="M12" s="70" t="s">
+        <v>358</v>
+      </c>
+      <c r="N12" s="70"/>
+      <c r="O12" s="70"/>
+      <c r="Q12" s="64"/>
+      <c r="R12" s="65"/>
+      <c r="S12" s="65"/>
+      <c r="T12" s="65"/>
+      <c r="U12" s="65"/>
+      <c r="V12" s="66"/>
+    </row>
+    <row r="13" spans="1:22">
+      <c r="C13" s="11">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D13" t="s">
+        <v>366</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>363</v>
+      </c>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70"/>
+      <c r="I13" s="70"/>
+      <c r="J13" s="70" t="s">
+        <v>357</v>
+      </c>
+      <c r="K13" s="70"/>
+      <c r="L13" s="70"/>
+      <c r="M13" s="70" t="s">
+        <v>357</v>
+      </c>
+      <c r="N13" s="70"/>
+      <c r="O13" s="70"/>
+      <c r="Q13" s="58"/>
+      <c r="R13" s="59"/>
+      <c r="S13" s="59"/>
+      <c r="T13" s="59"/>
+      <c r="U13" s="59"/>
+      <c r="V13" s="60"/>
+    </row>
+    <row r="14" spans="1:22">
+      <c r="C14" s="11">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="D14" t="s">
+        <v>364</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="70" t="s">
+        <v>357</v>
+      </c>
+      <c r="K14" s="70"/>
+      <c r="L14" s="70"/>
+      <c r="M14" s="70" t="s">
+        <v>357</v>
+      </c>
+      <c r="N14" s="70"/>
+      <c r="O14" s="70"/>
+      <c r="Q14" s="58"/>
+      <c r="R14" s="59"/>
+      <c r="S14" s="59"/>
+      <c r="T14" s="59"/>
+      <c r="U14" s="59"/>
+      <c r="V14" s="60"/>
+    </row>
+    <row r="15" spans="1:22">
+      <c r="C15" s="11">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="D15" t="s">
+        <v>360</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="70" t="s">
+        <v>358</v>
+      </c>
+      <c r="K15" s="70"/>
+      <c r="L15" s="70"/>
+      <c r="M15" s="70" t="s">
+        <v>358</v>
+      </c>
+      <c r="N15" s="70"/>
+      <c r="O15" s="70"/>
+      <c r="Q15" s="58"/>
+      <c r="R15" s="59"/>
+      <c r="S15" s="59"/>
+      <c r="T15" s="59"/>
+      <c r="U15" s="59"/>
+      <c r="V15" s="60"/>
+    </row>
+    <row r="16" spans="1:22">
+      <c r="C16" s="11">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="D16" t="s">
+        <v>379</v>
+      </c>
+      <c r="F16" s="13"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="70"/>
+      <c r="K16" s="70"/>
+      <c r="L16" s="70"/>
+      <c r="M16" s="70"/>
+      <c r="N16" s="70"/>
+      <c r="O16" s="70"/>
+      <c r="Q16" s="58"/>
+      <c r="R16" s="59"/>
+      <c r="S16" s="59"/>
+      <c r="T16" s="59"/>
+      <c r="U16" s="59"/>
+      <c r="V16" s="60"/>
+    </row>
+    <row r="17" spans="2:22">
+      <c r="C17" s="11">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="Q17" s="58"/>
+      <c r="R17" s="59"/>
+      <c r="S17" s="59"/>
+      <c r="T17" s="59"/>
+      <c r="U17" s="59"/>
+      <c r="V17" s="60"/>
+    </row>
+    <row r="18" spans="2:22">
+      <c r="C18" s="11">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="Q18" s="58"/>
+      <c r="R18" s="59"/>
+      <c r="S18" s="59"/>
+      <c r="T18" s="59"/>
+      <c r="U18" s="59"/>
+      <c r="V18" s="60"/>
+    </row>
+    <row r="19" spans="2:22">
+      <c r="C19" s="11">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="Q19" s="58"/>
+      <c r="R19" s="59"/>
+      <c r="S19" s="59"/>
+      <c r="T19" s="59"/>
+      <c r="U19" s="59"/>
+      <c r="V19" s="60"/>
+    </row>
+    <row r="20" spans="2:22">
+      <c r="C20" s="11">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="Q20" s="58"/>
+      <c r="R20" s="59"/>
+      <c r="S20" s="59"/>
+      <c r="T20" s="59"/>
+      <c r="U20" s="59"/>
+      <c r="V20" s="60"/>
+    </row>
+    <row r="21" spans="2:22">
+      <c r="Q21" s="58"/>
+      <c r="R21" s="59"/>
+      <c r="S21" s="59"/>
+      <c r="T21" s="59"/>
+      <c r="U21" s="59"/>
+      <c r="V21" s="60"/>
+    </row>
+    <row r="22" spans="2:22">
+      <c r="Q22" s="58"/>
+      <c r="R22" s="59"/>
+      <c r="S22" s="59"/>
+      <c r="T22" s="59"/>
+      <c r="U22" s="59"/>
+      <c r="V22" s="60"/>
+    </row>
+    <row r="23" spans="2:22">
+      <c r="Q23" s="58"/>
+      <c r="R23" s="59"/>
+      <c r="S23" s="59"/>
+      <c r="T23" s="59"/>
+      <c r="U23" s="59"/>
+      <c r="V23" s="60"/>
+    </row>
+    <row r="24" spans="2:22">
+      <c r="H24" s="111"/>
+      <c r="Q24" s="58"/>
+      <c r="R24" s="59"/>
+      <c r="S24" s="59"/>
+      <c r="T24" s="59"/>
+      <c r="U24" s="59"/>
+      <c r="V24" s="60"/>
+    </row>
+    <row r="25" spans="2:22">
+      <c r="Q25" s="58"/>
+      <c r="R25" s="59"/>
+      <c r="S25" s="59"/>
+      <c r="T25" s="59"/>
+      <c r="U25" s="59"/>
+      <c r="V25" s="60"/>
+    </row>
+    <row r="26" spans="2:22">
+      <c r="Q26" s="58"/>
+      <c r="R26" s="59"/>
+      <c r="S26" s="59"/>
+      <c r="T26" s="59"/>
+      <c r="U26" s="59"/>
+      <c r="V26" s="60"/>
+    </row>
+    <row r="27" spans="2:22">
+      <c r="Q27" s="58"/>
+      <c r="R27" s="59"/>
+      <c r="S27" s="59"/>
+      <c r="T27" s="59"/>
+      <c r="U27" s="59"/>
+      <c r="V27" s="60"/>
+    </row>
+    <row r="28" spans="2:22">
+      <c r="Q28" s="58"/>
+      <c r="R28" s="59"/>
+      <c r="S28" s="59"/>
+      <c r="T28" s="59"/>
+      <c r="U28" s="59"/>
+      <c r="V28" s="60"/>
+    </row>
+    <row r="29" spans="2:22">
+      <c r="B29" s="8"/>
+      <c r="Q29" s="58"/>
+      <c r="R29" s="59"/>
+      <c r="S29" s="59"/>
+      <c r="T29" s="59"/>
+      <c r="U29" s="59"/>
+      <c r="V29" s="60"/>
+    </row>
+    <row r="30" spans="2:22">
+      <c r="Q30" s="58"/>
+      <c r="R30" s="59"/>
+      <c r="S30" s="59"/>
+      <c r="T30" s="59"/>
+      <c r="U30" s="59"/>
+      <c r="V30" s="60"/>
+    </row>
+    <row r="31" spans="2:22">
+      <c r="Q31" s="61"/>
+      <c r="R31" s="62"/>
+      <c r="S31" s="62"/>
+      <c r="T31" s="62"/>
+      <c r="U31" s="62"/>
+      <c r="V31" s="63"/>
+    </row>
+    <row r="33" spans="2:24">
+      <c r="B33" s="8" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24">
+      <c r="B34" s="8"/>
+      <c r="C34" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" ht="17.25" thickBot="1">
+      <c r="B35" s="8"/>
+    </row>
+    <row r="36" spans="2:24">
+      <c r="B36" s="8"/>
+      <c r="D36" s="79" t="s">
+        <v>304</v>
+      </c>
+      <c r="E36" s="75" t="s">
+        <v>284</v>
+      </c>
+      <c r="F36" s="76"/>
+      <c r="G36" s="75" t="s">
+        <v>285</v>
+      </c>
+      <c r="H36" s="76"/>
+      <c r="I36" s="85" t="s">
+        <v>335</v>
+      </c>
+      <c r="J36" s="85"/>
+      <c r="K36" s="75" t="s">
+        <v>287</v>
+      </c>
+      <c r="L36" s="76"/>
+      <c r="M36" s="75" t="s">
+        <v>286</v>
+      </c>
+      <c r="N36" s="76"/>
+      <c r="O36" s="75" t="s">
+        <v>288</v>
+      </c>
+      <c r="P36" s="76"/>
+      <c r="Q36" s="75" t="s">
+        <v>289</v>
+      </c>
+      <c r="R36" s="76"/>
+      <c r="S36" s="67" t="s">
+        <v>290</v>
+      </c>
+      <c r="T36" s="73"/>
+      <c r="U36" s="102" t="s">
+        <v>370</v>
+      </c>
+      <c r="V36" s="102"/>
+      <c r="W36" s="103" t="s">
+        <v>372</v>
+      </c>
+      <c r="X36" s="104"/>
+    </row>
+    <row r="37" spans="2:24">
+      <c r="B37" s="8"/>
+      <c r="D37" s="79" t="s">
+        <v>300</v>
+      </c>
+      <c r="E37" s="75" t="s">
+        <v>301</v>
+      </c>
+      <c r="F37" s="76"/>
+      <c r="G37" s="75" t="s">
+        <v>316</v>
+      </c>
+      <c r="H37" s="76"/>
+      <c r="I37" s="85" t="s">
+        <v>316</v>
+      </c>
+      <c r="J37" s="85"/>
+      <c r="K37" s="75" t="s">
+        <v>303</v>
+      </c>
+      <c r="L37" s="76"/>
+      <c r="M37" s="75" t="s">
+        <v>300</v>
+      </c>
+      <c r="N37" s="76"/>
+      <c r="O37" s="75" t="s">
+        <v>301</v>
+      </c>
+      <c r="P37" s="76"/>
+      <c r="Q37" s="75" t="s">
+        <v>301</v>
+      </c>
+      <c r="R37" s="76"/>
+      <c r="S37" s="86" t="s">
+        <v>368</v>
+      </c>
+      <c r="T37" s="71"/>
+      <c r="U37" s="105" t="s">
+        <v>301</v>
+      </c>
+      <c r="V37" s="105"/>
+      <c r="W37" s="106" t="s">
+        <v>301</v>
+      </c>
+      <c r="X37" s="107"/>
+    </row>
+    <row r="38" spans="2:24">
+      <c r="B38" s="8"/>
+      <c r="D38" s="79" t="s">
+        <v>291</v>
+      </c>
+      <c r="E38" s="78" t="s">
+        <v>292</v>
+      </c>
+      <c r="F38" s="76"/>
+      <c r="G38" s="78" t="s">
+        <v>309</v>
+      </c>
+      <c r="H38" s="76"/>
+      <c r="I38" s="85" t="s">
+        <v>336</v>
+      </c>
+      <c r="J38" s="85"/>
+      <c r="K38" s="78" t="s">
+        <v>294</v>
+      </c>
+      <c r="L38" s="76"/>
+      <c r="M38" s="78" t="s">
+        <v>293</v>
+      </c>
+      <c r="N38" s="76"/>
+      <c r="O38" s="78" t="s">
+        <v>295</v>
+      </c>
+      <c r="P38" s="76"/>
+      <c r="Q38" s="78" t="s">
+        <v>296</v>
+      </c>
+      <c r="R38" s="76"/>
+      <c r="S38" s="86" t="s">
+        <v>297</v>
+      </c>
+      <c r="T38" s="71"/>
+      <c r="U38" s="108" t="s">
+        <v>369</v>
+      </c>
+      <c r="V38" s="105"/>
+      <c r="W38" s="109" t="s">
+        <v>371</v>
+      </c>
+      <c r="X38" s="107"/>
+    </row>
+    <row r="39" spans="2:24">
+      <c r="B39" s="8"/>
+      <c r="D39" s="80">
+        <f>ROW()-ROW($D$38)</f>
+        <v>1</v>
+      </c>
+      <c r="E39" s="92">
+        <v>3</v>
+      </c>
+      <c r="F39" s="93"/>
+      <c r="G39" s="93" t="s">
+        <v>298</v>
+      </c>
+      <c r="H39" s="93"/>
+      <c r="I39" s="93" t="s">
+        <v>338</v>
+      </c>
+      <c r="J39" s="93"/>
+      <c r="K39" s="93" t="s">
+        <v>299</v>
+      </c>
+      <c r="L39" s="93"/>
+      <c r="M39" s="93">
+        <v>5</v>
+      </c>
+      <c r="N39" s="93"/>
+      <c r="O39" s="93">
+        <v>30</v>
+      </c>
+      <c r="P39" s="93"/>
+      <c r="Q39" s="93">
+        <v>30</v>
+      </c>
+      <c r="R39" s="93"/>
+      <c r="S39" s="95" t="s">
+        <v>373</v>
+      </c>
+      <c r="T39" s="93"/>
+      <c r="U39" s="92">
+        <v>75</v>
+      </c>
+      <c r="V39" s="93"/>
+      <c r="W39" s="92">
+        <v>30</v>
+      </c>
+      <c r="X39" s="96"/>
+    </row>
+    <row r="40" spans="2:24">
+      <c r="B40" s="8"/>
+      <c r="D40" s="80">
+        <f t="shared" ref="D40:D42" si="1">ROW()-ROW($D$38)</f>
+        <v>2</v>
+      </c>
+      <c r="E40" s="93" t="s">
+        <v>302</v>
+      </c>
+      <c r="F40" s="93"/>
+      <c r="G40" s="93" t="s">
+        <v>302</v>
+      </c>
+      <c r="H40" s="93"/>
+      <c r="I40" s="93" t="s">
+        <v>339</v>
+      </c>
+      <c r="J40" s="93"/>
+      <c r="K40" s="93" t="s">
+        <v>302</v>
+      </c>
+      <c r="L40" s="93"/>
+      <c r="M40" s="94"/>
+      <c r="N40" s="18"/>
+      <c r="O40" s="94"/>
+      <c r="P40" s="18"/>
+      <c r="Q40" s="94"/>
+      <c r="R40" s="18"/>
+      <c r="S40" s="97"/>
+      <c r="T40" s="18"/>
+      <c r="U40" s="94"/>
+      <c r="V40" s="18"/>
+      <c r="W40" s="94"/>
+      <c r="X40" s="98"/>
+    </row>
+    <row r="41" spans="2:24">
+      <c r="B41" s="8"/>
+      <c r="D41" s="80">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="E41" s="93" t="s">
+        <v>302</v>
+      </c>
+      <c r="F41" s="93"/>
+      <c r="G41" s="93" t="s">
+        <v>302</v>
+      </c>
+      <c r="H41" s="93"/>
+      <c r="I41" s="93" t="s">
+        <v>348</v>
+      </c>
+      <c r="J41" s="93"/>
+      <c r="K41" s="93" t="s">
+        <v>302</v>
+      </c>
+      <c r="L41" s="93"/>
+      <c r="M41" s="94"/>
+      <c r="N41" s="18"/>
+      <c r="O41" s="94"/>
+      <c r="P41" s="18"/>
+      <c r="Q41" s="94"/>
+      <c r="R41" s="18"/>
+      <c r="S41" s="97"/>
+      <c r="T41" s="18"/>
+      <c r="U41" s="94"/>
+      <c r="V41" s="18"/>
+      <c r="W41" s="94"/>
+      <c r="X41" s="98"/>
+    </row>
+    <row r="42" spans="2:24" ht="17.25" thickBot="1">
+      <c r="B42" s="8"/>
+      <c r="D42" s="82">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="E42" s="83" t="s">
+        <v>302</v>
+      </c>
+      <c r="F42" s="83"/>
+      <c r="G42" s="83" t="s">
+        <v>302</v>
+      </c>
+      <c r="H42" s="83"/>
+      <c r="I42" s="83" t="s">
+        <v>302</v>
+      </c>
+      <c r="J42" s="83"/>
+      <c r="K42" s="84" t="s">
+        <v>349</v>
+      </c>
+      <c r="L42" s="84"/>
+      <c r="M42" s="84"/>
+      <c r="N42" s="84"/>
+      <c r="O42" s="84"/>
+      <c r="P42" s="84"/>
+      <c r="Q42" s="84"/>
+      <c r="R42" s="84"/>
+      <c r="S42" s="99"/>
+      <c r="T42" s="100"/>
+      <c r="U42" s="100"/>
+      <c r="V42" s="100"/>
+      <c r="W42" s="100"/>
+      <c r="X42" s="101"/>
+    </row>
+    <row r="43" spans="2:24">
+      <c r="B43" s="8"/>
+    </row>
+    <row r="44" spans="2:24">
+      <c r="B44" s="8"/>
+      <c r="D44" s="18" t="s">
+        <v>306</v>
+      </c>
+      <c r="G44" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24">
+      <c r="B45" s="8"/>
+      <c r="D45" s="18" t="s">
+        <v>307</v>
+      </c>
+      <c r="G45" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24">
+      <c r="B46" s="8"/>
+      <c r="D46" s="18" t="s">
+        <v>315</v>
+      </c>
+      <c r="G46" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24">
+      <c r="B47" s="8"/>
+      <c r="D47" s="18" t="s">
+        <v>337</v>
+      </c>
+      <c r="G47" s="18" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24">
+      <c r="B48" s="8"/>
+      <c r="D48" s="18" t="s">
+        <v>313</v>
+      </c>
+      <c r="G48" s="18" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="49" spans="2:23">
+      <c r="B49" s="8"/>
+      <c r="D49" s="18" t="s">
+        <v>311</v>
+      </c>
+      <c r="G49" s="18" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="50" spans="2:23">
+      <c r="B50" s="8"/>
+      <c r="D50" s="18" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="C10" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="B12" s="8"/>
-      <c r="C12" s="123" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="C13" s="8"/>
-      <c r="D13" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="48" t="s">
-        <v>356</v>
-      </c>
-      <c r="F13" s="48"/>
-      <c r="G13" s="48" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="C14" s="8"/>
-      <c r="D14" s="11">
-        <f>ROW()-ROW($D$13)</f>
-        <v>1</v>
-      </c>
-      <c r="E14" t="s">
-        <v>265</v>
-      </c>
-      <c r="G14" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2">
-      <c r="B32" s="8"/>
+      <c r="E50" s="18"/>
+      <c r="F50" s="18"/>
+      <c r="G50" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="H50" s="18"/>
+    </row>
+    <row r="51" spans="2:23">
+      <c r="B51" s="8"/>
+      <c r="D51" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="E51" s="18"/>
+      <c r="F51" s="18"/>
+      <c r="G51" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="H51" s="18"/>
+      <c r="S51" s="18"/>
+      <c r="T51" s="18"/>
+      <c r="U51" s="18"/>
+      <c r="V51" s="18"/>
+      <c r="W51" s="18"/>
+    </row>
+    <row r="52" spans="2:23">
+      <c r="D52" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="53" spans="2:23">
+      <c r="D53" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="54" spans="2:23">
+      <c r="D54" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>376</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3FA637D-A4E4-43F5-99C7-0DE64168A271}">
   <dimension ref="A1:L46"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
@@ -11060,24 +14032,24 @@
       <c r="C3" s="33"/>
     </row>
     <row r="5" spans="1:12">
-      <c r="B5" s="65" t="s">
+      <c r="B5" s="127" t="s">
         <v>129</v>
       </c>
-      <c r="C5" s="65"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60" t="s">
+      <c r="C5" s="127"/>
+      <c r="D5" s="124"/>
+      <c r="E5" s="124" t="s">
         <v>126</v>
       </c>
-      <c r="F5" s="66"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="60" t="s">
+      <c r="F5" s="126"/>
+      <c r="G5" s="125"/>
+      <c r="H5" s="124" t="s">
         <v>136</v>
       </c>
-      <c r="I5" s="61"/>
-      <c r="J5" s="60" t="s">
+      <c r="I5" s="125"/>
+      <c r="J5" s="124" t="s">
         <v>141</v>
       </c>
-      <c r="K5" s="61"/>
+      <c r="K5" s="125"/>
     </row>
     <row r="6" spans="1:12">
       <c r="B6" s="25" t="s">
@@ -11147,27 +14119,27 @@
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="B9" s="60" t="s">
+      <c r="B9" s="124" t="s">
         <v>151</v>
       </c>
-      <c r="C9" s="61"/>
-      <c r="D9" s="60" t="s">
+      <c r="C9" s="125"/>
+      <c r="D9" s="124" t="s">
         <v>153</v>
       </c>
-      <c r="E9" s="66"/>
-      <c r="F9" s="61"/>
-      <c r="G9" s="60" t="s">
+      <c r="E9" s="126"/>
+      <c r="F9" s="125"/>
+      <c r="G9" s="124" t="s">
         <v>136</v>
       </c>
-      <c r="H9" s="61"/>
-      <c r="I9" s="60" t="s">
+      <c r="H9" s="125"/>
+      <c r="I9" s="124" t="s">
         <v>141</v>
       </c>
-      <c r="J9" s="61"/>
-      <c r="K9" s="60" t="s">
+      <c r="J9" s="125"/>
+      <c r="K9" s="124" t="s">
         <v>178</v>
       </c>
-      <c r="L9" s="61"/>
+      <c r="L9" s="125"/>
     </row>
     <row r="10" spans="1:12">
       <c r="B10" s="25" t="s">
@@ -11243,7 +14215,7 @@
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="62" t="s">
+      <c r="A14" s="128" t="s">
         <v>155</v>
       </c>
       <c r="D14" s="27" t="s">
@@ -11252,14 +14224,14 @@
       <c r="E14" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="F14" s="65" t="s">
+      <c r="F14" s="127" t="s">
         <v>165</v>
       </c>
-      <c r="G14" s="65"/>
-      <c r="H14" s="65"/>
+      <c r="G14" s="127"/>
+      <c r="H14" s="127"/>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="63"/>
+      <c r="A15" s="129"/>
       <c r="D15" s="34" t="s">
         <v>157</v>
       </c>
@@ -11271,7 +14243,7 @@
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="63"/>
+      <c r="A16" s="129"/>
       <c r="D16" s="35" t="s">
         <v>158</v>
       </c>
@@ -11280,7 +14252,7 @@
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="63"/>
+      <c r="A17" s="129"/>
       <c r="D17" s="23" t="s">
         <v>159</v>
       </c>
@@ -11292,73 +14264,73 @@
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="63"/>
+      <c r="A18" s="129"/>
       <c r="D18" s="13" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="63"/>
+      <c r="A19" s="129"/>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="63"/>
+      <c r="A20" s="129"/>
       <c r="E20" s="36" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="63"/>
+      <c r="A21" s="129"/>
       <c r="E21" s="13" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="63"/>
+      <c r="A22" s="129"/>
       <c r="E22" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="63"/>
+      <c r="A23" s="129"/>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="63"/>
+      <c r="A24" s="129"/>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="63"/>
+      <c r="A25" s="129"/>
       <c r="E25" s="11" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="63"/>
+      <c r="A26" s="129"/>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="63"/>
+      <c r="A27" s="129"/>
       <c r="E27" s="13" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="63"/>
+      <c r="A28" s="129"/>
       <c r="E28" s="13" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="29" spans="1:6">
-      <c r="A29" s="63"/>
+      <c r="A29" s="129"/>
       <c r="E29" s="11" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="30" spans="1:6">
-      <c r="A30" s="63"/>
+      <c r="A30" s="129"/>
       <c r="E30" s="13" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="64"/>
+      <c r="A31" s="130"/>
     </row>
     <row r="33" spans="1:7">
       <c r="B33" s="27" t="s">
@@ -11367,14 +14339,14 @@
       <c r="C33" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="D33" s="60" t="s">
+      <c r="D33" s="124" t="s">
         <v>189</v>
       </c>
-      <c r="E33" s="61"/>
-      <c r="F33" s="60" t="s">
+      <c r="E33" s="125"/>
+      <c r="F33" s="124" t="s">
         <v>178</v>
       </c>
-      <c r="G33" s="61"/>
+      <c r="G33" s="125"/>
     </row>
     <row r="34" spans="1:7">
       <c r="B34" s="26" t="s">
@@ -11493,6 +14465,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="A14:A31"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="G9:H9"/>
     <mergeCell ref="K9:L9"/>
@@ -11501,11 +14478,6 @@
     <mergeCell ref="E5:G5"/>
     <mergeCell ref="J5:K5"/>
     <mergeCell ref="H5:I5"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="A14:A31"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="B9:C9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11513,7 +14485,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{511B7746-4A5E-454B-8602-7B4B353E7BEF}">
   <dimension ref="A1:Y24"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
@@ -11728,7 +14700,7 @@
       </c>
     </row>
     <row r="24" spans="2:3">
-      <c r="B24" s="59">
+      <c r="B24" s="57">
         <f>1920/3</f>
         <v>640</v>
       </c>
@@ -11740,302 +14712,4 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FEA1851-41A0-400A-9D42-CA24EB0A5B33}">
-  <sheetPr>
-    <tabColor rgb="FFFFC000"/>
-  </sheetPr>
-  <dimension ref="B2:S47"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
-  <cols>
-    <col min="1" max="1" width="3.75" customWidth="1"/>
-    <col min="2" max="2" width="5.375" style="11" customWidth="1"/>
-    <col min="3" max="3" width="4" customWidth="1"/>
-    <col min="4" max="4" width="38.875" customWidth="1"/>
-    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.5" customWidth="1"/>
-    <col min="11" max="11" width="5.75" customWidth="1"/>
-    <col min="18" max="18" width="4.75" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:19">
-      <c r="B2" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="D2" s="16"/>
-      <c r="H2" s="16" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="3" spans="2:19">
-      <c r="B3" s="22">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="2:19">
-      <c r="E4" t="s">
-        <v>84</v>
-      </c>
-      <c r="F4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="5" spans="2:19">
-      <c r="E5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="6" spans="2:19">
-      <c r="E6" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="8" spans="2:19">
-      <c r="B8" s="11">
-        <v>2</v>
-      </c>
-      <c r="C8" t="s">
-        <v>87</v>
-      </c>
-      <c r="E8" s="37" t="s">
-        <v>207</v>
-      </c>
-      <c r="H8" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="10" spans="2:19">
-      <c r="B10" s="11">
-        <v>3</v>
-      </c>
-      <c r="C10" t="s">
-        <v>91</v>
-      </c>
-      <c r="F10" s="37" t="s">
-        <v>208</v>
-      </c>
-      <c r="H10" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="12" spans="2:19">
-      <c r="B12" s="11">
-        <v>4</v>
-      </c>
-      <c r="C12" t="s">
-        <v>92</v>
-      </c>
-      <c r="E12" t="s">
-        <v>93</v>
-      </c>
-      <c r="H12" t="s">
-        <v>95</v>
-      </c>
-      <c r="J12" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="13" spans="2:19">
-      <c r="C13" t="s">
-        <v>94</v>
-      </c>
-      <c r="E13" s="37" t="s">
-        <v>209</v>
-      </c>
-      <c r="J13" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="15" spans="2:19">
-      <c r="B15" s="22">
-        <v>5</v>
-      </c>
-      <c r="C15" t="s">
-        <v>96</v>
-      </c>
-      <c r="H15" t="s">
-        <v>111</v>
-      </c>
-      <c r="S15" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="16" spans="2:19">
-      <c r="B16"/>
-    </row>
-    <row r="17" spans="2:19">
-      <c r="B17">
-        <v>5.25</v>
-      </c>
-      <c r="C17" t="s">
-        <v>119</v>
-      </c>
-      <c r="H17" t="s">
-        <v>120</v>
-      </c>
-      <c r="S17" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="18" spans="2:19">
-      <c r="S18" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="19" spans="2:19">
-      <c r="B19" s="11">
-        <v>5.5</v>
-      </c>
-      <c r="C19" t="s">
-        <v>114</v>
-      </c>
-      <c r="E19" t="s">
-        <v>115</v>
-      </c>
-      <c r="H19" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="20" spans="2:19">
-      <c r="E20" t="s">
-        <v>116</v>
-      </c>
-      <c r="S20" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="22" spans="2:19">
-      <c r="D22" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="24" spans="2:19">
-      <c r="D24" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="26" spans="2:19">
-      <c r="B26" s="11">
-        <v>6</v>
-      </c>
-      <c r="C26" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="27" spans="2:19">
-      <c r="C27" t="s">
-        <v>98</v>
-      </c>
-      <c r="D27" t="s">
-        <v>99</v>
-      </c>
-      <c r="E27" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="2:19">
-      <c r="C29" t="s">
-        <v>101</v>
-      </c>
-      <c r="D29" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="30" spans="2:19">
-      <c r="D30" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="32" spans="2:19">
-      <c r="C32" t="s">
-        <v>103</v>
-      </c>
-      <c r="D32" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4">
-      <c r="C34" t="s">
-        <v>106</v>
-      </c>
-      <c r="D34" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4">
-      <c r="C36" t="s">
-        <v>108</v>
-      </c>
-      <c r="D36" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4">
-      <c r="D37" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4">
-      <c r="B39" s="11">
-        <v>7</v>
-      </c>
-      <c r="C39" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4">
-      <c r="B41" s="33">
-        <v>8</v>
-      </c>
-      <c r="C41" t="s">
-        <v>224</v>
-      </c>
-      <c r="D41" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4">
-      <c r="B43" s="11">
-        <v>9</v>
-      </c>
-      <c r="C43" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="45" spans="2:4">
-      <c r="B45" s="46">
-        <v>10</v>
-      </c>
-      <c r="C45" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="47" spans="2:4">
-      <c r="C47" t="s">
-        <v>255</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
 </file>
--- a/Document/정책문서.xlsx
+++ b/Document/정책문서.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git_fork\ProjectShoot\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8735F56-8997-49E8-A511-2FE4FEFBAD4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DDE17B5-0E54-4BB8-A59B-DF68287F3E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32235" yWindow="4755" windowWidth="21600" windowHeight="11295" tabRatio="711" firstSheet="1" activeTab="1" xr2:uid="{F9E8F865-F741-4425-897D-555A2E4B3EBE}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="711" firstSheet="1" activeTab="1" xr2:uid="{F9E8F865-F741-4425-897D-555A2E4B3EBE}"/>
   </bookViews>
   <sheets>
     <sheet name="깃포크 공부" sheetId="11" state="hidden" r:id="rId1"/>
@@ -681,7 +681,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="395">
   <si>
     <t>설명</t>
   </si>
@@ -2314,6 +2314,14 @@
   <si>
     <t>- 진형 셀에 색 강조(회의 필요: 이거 xy로 진형 형태 조절할거면 미리 형태를 만드는 이유가 있나?)
 - 무브 패턴 내용 작성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>포메이션</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 포매이션의 경우 별도의 코딩이 아닌 기획적 작성임을 회의를 통해 합의</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2546,7 +2554,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2598,12 +2606,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3134,7 +3136,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3471,12 +3473,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
@@ -3497,6 +3493,9 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3527,9 +3526,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -7873,6 +7869,69 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="직사각형 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{041B3E31-A37A-A0DD-B5CD-91093769C648}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4324350" y="5495925"/>
+          <a:ext cx="2324100" cy="676275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            <a:t>기획적 다짐</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -10666,14 +10725,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D96FDAC-DED2-464C-8F36-7438D20848EF}">
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="33.75">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="118" t="s">
         <v>387</v>
       </c>
     </row>
@@ -10709,220 +10768,251 @@
       <c r="Q3" s="52"/>
       <c r="R3" s="51"/>
     </row>
-    <row r="4" spans="1:18" ht="50.25" customHeight="1">
-      <c r="A4" s="118">
-        <f t="shared" ref="A4:A11" si="0">ROW()-ROW($A$3)</f>
+    <row r="4" spans="1:18">
+      <c r="A4" s="116"/>
+      <c r="B4" s="117"/>
+      <c r="C4" s="114"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="120"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="121"/>
+      <c r="L4" s="121"/>
+      <c r="M4" s="121"/>
+      <c r="N4" s="121"/>
+      <c r="O4" s="121"/>
+      <c r="P4" s="121"/>
+      <c r="Q4" s="121"/>
+      <c r="R4" s="122"/>
+    </row>
+    <row r="5" spans="1:18" ht="50.25" customHeight="1">
+      <c r="A5" s="116">
+        <f t="shared" ref="A5:A12" si="0">ROW()-ROW($A$4)</f>
         <v>1</v>
       </c>
-      <c r="B4" s="119">
+      <c r="B5" s="117">
         <v>46185</v>
       </c>
-      <c r="C4" s="116"/>
-      <c r="D4" s="118" t="s">
+      <c r="C5" s="114"/>
+      <c r="D5" s="116" t="s">
         <v>380</v>
       </c>
-      <c r="E4" s="117" t="s">
-        <v>388</v>
-      </c>
-      <c r="F4" s="116"/>
-      <c r="G4" s="115" t="s">
-        <v>387</v>
-      </c>
-      <c r="H4" s="114"/>
-      <c r="I4" s="121" t="s">
-        <v>389</v>
-      </c>
-      <c r="J4" s="122"/>
-      <c r="K4" s="122"/>
-      <c r="L4" s="122"/>
-      <c r="M4" s="122"/>
-      <c r="N4" s="122"/>
-      <c r="O4" s="122"/>
-      <c r="P4" s="122"/>
-      <c r="Q4" s="122"/>
-      <c r="R4" s="123"/>
-    </row>
-    <row r="5" spans="1:18" ht="50.25" customHeight="1">
-      <c r="A5" s="118">
+      <c r="E5" s="115" t="s">
+        <v>390</v>
+      </c>
+      <c r="F5" s="114"/>
+      <c r="G5" s="119" t="s">
+        <v>393</v>
+      </c>
+      <c r="H5" s="112"/>
+      <c r="I5" s="120" t="s">
+        <v>394</v>
+      </c>
+      <c r="J5" s="121"/>
+      <c r="K5" s="121"/>
+      <c r="L5" s="121"/>
+      <c r="M5" s="121"/>
+      <c r="N5" s="121"/>
+      <c r="O5" s="121"/>
+      <c r="P5" s="121"/>
+      <c r="Q5" s="121"/>
+      <c r="R5" s="122"/>
+    </row>
+    <row r="6" spans="1:18" ht="50.25" customHeight="1">
+      <c r="A6" s="116">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="B5" s="119">
+      <c r="B6" s="117">
         <v>46185</v>
       </c>
-      <c r="C5" s="116"/>
-      <c r="D5" s="118" t="s">
+      <c r="C6" s="114"/>
+      <c r="D6" s="116" t="s">
         <v>380</v>
       </c>
-      <c r="E5" s="117" t="s">
+      <c r="E6" s="115" t="s">
         <v>390</v>
       </c>
-      <c r="F5" s="116"/>
-      <c r="G5" s="131" t="s">
+      <c r="F6" s="114"/>
+      <c r="G6" s="119" t="s">
         <v>391</v>
       </c>
-      <c r="H5" s="114"/>
-      <c r="I5" s="121" t="s">
+      <c r="H6" s="112"/>
+      <c r="I6" s="120" t="s">
         <v>392</v>
       </c>
-      <c r="J5" s="122"/>
-      <c r="K5" s="122"/>
-      <c r="L5" s="122"/>
-      <c r="M5" s="122"/>
-      <c r="N5" s="122"/>
-      <c r="O5" s="122"/>
-      <c r="P5" s="122"/>
-      <c r="Q5" s="122"/>
-      <c r="R5" s="123"/>
-    </row>
-    <row r="6" spans="1:18">
-      <c r="A6" s="118">
+      <c r="J6" s="121"/>
+      <c r="K6" s="121"/>
+      <c r="L6" s="121"/>
+      <c r="M6" s="121"/>
+      <c r="N6" s="121"/>
+      <c r="O6" s="121"/>
+      <c r="P6" s="121"/>
+      <c r="Q6" s="121"/>
+      <c r="R6" s="122"/>
+    </row>
+    <row r="7" spans="1:18">
+      <c r="A7" s="116">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B6" s="119"/>
-      <c r="C6" s="116"/>
-      <c r="D6" s="118"/>
-      <c r="E6" s="117"/>
-      <c r="F6" s="116"/>
-      <c r="G6" s="115"/>
-      <c r="H6" s="114"/>
-      <c r="I6" s="121"/>
-      <c r="J6" s="122"/>
-      <c r="K6" s="122"/>
-      <c r="L6" s="122"/>
-      <c r="M6" s="122"/>
-      <c r="N6" s="122"/>
-      <c r="O6" s="122"/>
-      <c r="P6" s="122"/>
-      <c r="Q6" s="122"/>
-      <c r="R6" s="123"/>
-    </row>
-    <row r="7" spans="1:18">
-      <c r="A7" s="118">
+      <c r="B7" s="117">
+        <v>46185</v>
+      </c>
+      <c r="C7" s="114"/>
+      <c r="D7" s="116" t="s">
+        <v>380</v>
+      </c>
+      <c r="E7" s="115" t="s">
+        <v>388</v>
+      </c>
+      <c r="F7" s="114"/>
+      <c r="G7" s="113" t="s">
+        <v>387</v>
+      </c>
+      <c r="H7" s="112"/>
+      <c r="I7" s="120" t="s">
+        <v>389</v>
+      </c>
+      <c r="J7" s="121"/>
+      <c r="K7" s="121"/>
+      <c r="L7" s="121"/>
+      <c r="M7" s="121"/>
+      <c r="N7" s="121"/>
+      <c r="O7" s="121"/>
+      <c r="P7" s="121"/>
+      <c r="Q7" s="121"/>
+      <c r="R7" s="122"/>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="A8" s="116">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B7" s="119"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="118"/>
-      <c r="E7" s="117"/>
-      <c r="F7" s="116"/>
-      <c r="G7" s="115"/>
-      <c r="H7" s="114"/>
-      <c r="I7" s="121"/>
-      <c r="J7" s="122"/>
-      <c r="K7" s="122"/>
-      <c r="L7" s="122"/>
-      <c r="M7" s="122"/>
-      <c r="N7" s="122"/>
-      <c r="O7" s="122"/>
-      <c r="P7" s="122"/>
-      <c r="Q7" s="122"/>
-      <c r="R7" s="123"/>
-    </row>
-    <row r="8" spans="1:18">
-      <c r="A8" s="118">
+      <c r="B8" s="117"/>
+      <c r="C8" s="114"/>
+      <c r="D8" s="116"/>
+      <c r="E8" s="115"/>
+      <c r="F8" s="114"/>
+      <c r="G8" s="113"/>
+      <c r="H8" s="112"/>
+      <c r="I8" s="120"/>
+      <c r="J8" s="121"/>
+      <c r="K8" s="121"/>
+      <c r="L8" s="121"/>
+      <c r="M8" s="121"/>
+      <c r="N8" s="121"/>
+      <c r="O8" s="121"/>
+      <c r="P8" s="121"/>
+      <c r="Q8" s="121"/>
+      <c r="R8" s="122"/>
+    </row>
+    <row r="9" spans="1:18">
+      <c r="A9" s="116">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B8" s="119"/>
-      <c r="C8" s="116"/>
-      <c r="D8" s="118"/>
-      <c r="E8" s="117"/>
-      <c r="F8" s="116"/>
-      <c r="G8" s="115"/>
-      <c r="H8" s="114"/>
-      <c r="I8" s="121"/>
-      <c r="J8" s="122"/>
-      <c r="K8" s="122"/>
-      <c r="L8" s="122"/>
-      <c r="M8" s="122"/>
-      <c r="N8" s="122"/>
-      <c r="O8" s="122"/>
-      <c r="P8" s="122"/>
-      <c r="Q8" s="122"/>
-      <c r="R8" s="123"/>
-    </row>
-    <row r="9" spans="1:18">
-      <c r="A9" s="118">
+      <c r="B9" s="117"/>
+      <c r="C9" s="114"/>
+      <c r="D9" s="116"/>
+      <c r="E9" s="115"/>
+      <c r="F9" s="114"/>
+      <c r="G9" s="113"/>
+      <c r="H9" s="112"/>
+      <c r="I9" s="120"/>
+      <c r="J9" s="121"/>
+      <c r="K9" s="121"/>
+      <c r="L9" s="121"/>
+      <c r="M9" s="121"/>
+      <c r="N9" s="121"/>
+      <c r="O9" s="121"/>
+      <c r="P9" s="121"/>
+      <c r="Q9" s="121"/>
+      <c r="R9" s="122"/>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="A10" s="116">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B9" s="119"/>
-      <c r="C9" s="116"/>
-      <c r="D9" s="118"/>
-      <c r="E9" s="117"/>
-      <c r="F9" s="116"/>
-      <c r="G9" s="115"/>
-      <c r="H9" s="114"/>
-      <c r="I9" s="121"/>
-      <c r="J9" s="122"/>
-      <c r="K9" s="122"/>
-      <c r="L9" s="122"/>
-      <c r="M9" s="122"/>
-      <c r="N9" s="122"/>
-      <c r="O9" s="122"/>
-      <c r="P9" s="122"/>
-      <c r="Q9" s="122"/>
-      <c r="R9" s="123"/>
-    </row>
-    <row r="10" spans="1:18">
-      <c r="A10" s="118">
+      <c r="B10" s="117"/>
+      <c r="C10" s="114"/>
+      <c r="D10" s="116"/>
+      <c r="E10" s="115"/>
+      <c r="F10" s="114"/>
+      <c r="G10" s="113"/>
+      <c r="H10" s="112"/>
+      <c r="I10" s="120"/>
+      <c r="J10" s="121"/>
+      <c r="K10" s="121"/>
+      <c r="L10" s="121"/>
+      <c r="M10" s="121"/>
+      <c r="N10" s="121"/>
+      <c r="O10" s="121"/>
+      <c r="P10" s="121"/>
+      <c r="Q10" s="121"/>
+      <c r="R10" s="122"/>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="A11" s="116">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B10" s="119"/>
-      <c r="C10" s="116"/>
-      <c r="D10" s="118"/>
-      <c r="E10" s="117"/>
-      <c r="F10" s="116"/>
-      <c r="G10" s="115"/>
-      <c r="H10" s="114"/>
-      <c r="I10" s="121"/>
-      <c r="J10" s="122"/>
-      <c r="K10" s="122"/>
-      <c r="L10" s="122"/>
-      <c r="M10" s="122"/>
-      <c r="N10" s="122"/>
-      <c r="O10" s="122"/>
-      <c r="P10" s="122"/>
-      <c r="Q10" s="122"/>
-      <c r="R10" s="123"/>
-    </row>
-    <row r="11" spans="1:18">
-      <c r="A11" s="118">
+      <c r="B11" s="117"/>
+      <c r="C11" s="114"/>
+      <c r="D11" s="116"/>
+      <c r="E11" s="115"/>
+      <c r="F11" s="114"/>
+      <c r="G11" s="113"/>
+      <c r="H11" s="112"/>
+      <c r="I11" s="120"/>
+      <c r="J11" s="121"/>
+      <c r="K11" s="121"/>
+      <c r="L11" s="121"/>
+      <c r="M11" s="121"/>
+      <c r="N11" s="121"/>
+      <c r="O11" s="121"/>
+      <c r="P11" s="121"/>
+      <c r="Q11" s="121"/>
+      <c r="R11" s="122"/>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="A12" s="116">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B11" s="119"/>
-      <c r="C11" s="116"/>
-      <c r="D11" s="118"/>
-      <c r="E11" s="117"/>
-      <c r="F11" s="116"/>
-      <c r="G11" s="115"/>
-      <c r="H11" s="114"/>
-      <c r="I11" s="121"/>
-      <c r="J11" s="122"/>
-      <c r="K11" s="122"/>
-      <c r="L11" s="122"/>
-      <c r="M11" s="122"/>
-      <c r="N11" s="122"/>
-      <c r="O11" s="122"/>
-      <c r="P11" s="122"/>
-      <c r="Q11" s="122"/>
-      <c r="R11" s="123"/>
+      <c r="B12" s="117"/>
+      <c r="C12" s="114"/>
+      <c r="D12" s="116"/>
+      <c r="E12" s="115"/>
+      <c r="F12" s="114"/>
+      <c r="G12" s="113"/>
+      <c r="H12" s="112"/>
+      <c r="I12" s="120"/>
+      <c r="J12" s="121"/>
+      <c r="K12" s="121"/>
+      <c r="L12" s="121"/>
+      <c r="M12" s="121"/>
+      <c r="N12" s="121"/>
+      <c r="O12" s="121"/>
+      <c r="P12" s="121"/>
+      <c r="Q12" s="121"/>
+      <c r="R12" s="122"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="I10:R10"/>
+  <mergeCells count="9">
     <mergeCell ref="I11:R11"/>
+    <mergeCell ref="I12:R12"/>
     <mergeCell ref="I4:R4"/>
-    <mergeCell ref="I5:R5"/>
     <mergeCell ref="I6:R6"/>
     <mergeCell ref="I7:R7"/>
     <mergeCell ref="I8:R8"/>
     <mergeCell ref="I9:R9"/>
+    <mergeCell ref="I10:R10"/>
+    <mergeCell ref="I5:R5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12816,10 +12906,10 @@
         <v>335</v>
       </c>
       <c r="J36" s="85"/>
-      <c r="K36" s="112" t="s">
+      <c r="K36" s="86" t="s">
         <v>287</v>
       </c>
-      <c r="L36" s="113"/>
+      <c r="L36" s="71"/>
       <c r="M36" s="73" t="s">
         <v>286</v>
       </c>
@@ -14032,24 +14122,24 @@
       <c r="C3" s="33"/>
     </row>
     <row r="5" spans="1:12">
-      <c r="B5" s="127" t="s">
+      <c r="B5" s="126" t="s">
         <v>129</v>
       </c>
-      <c r="C5" s="127"/>
-      <c r="D5" s="124"/>
-      <c r="E5" s="124" t="s">
+      <c r="C5" s="126"/>
+      <c r="D5" s="123"/>
+      <c r="E5" s="123" t="s">
         <v>126</v>
       </c>
-      <c r="F5" s="126"/>
-      <c r="G5" s="125"/>
-      <c r="H5" s="124" t="s">
+      <c r="F5" s="125"/>
+      <c r="G5" s="124"/>
+      <c r="H5" s="123" t="s">
         <v>136</v>
       </c>
-      <c r="I5" s="125"/>
-      <c r="J5" s="124" t="s">
+      <c r="I5" s="124"/>
+      <c r="J5" s="123" t="s">
         <v>141</v>
       </c>
-      <c r="K5" s="125"/>
+      <c r="K5" s="124"/>
     </row>
     <row r="6" spans="1:12">
       <c r="B6" s="25" t="s">
@@ -14119,27 +14209,27 @@
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="B9" s="124" t="s">
+      <c r="B9" s="123" t="s">
         <v>151</v>
       </c>
-      <c r="C9" s="125"/>
-      <c r="D9" s="124" t="s">
+      <c r="C9" s="124"/>
+      <c r="D9" s="123" t="s">
         <v>153</v>
       </c>
-      <c r="E9" s="126"/>
-      <c r="F9" s="125"/>
-      <c r="G9" s="124" t="s">
+      <c r="E9" s="125"/>
+      <c r="F9" s="124"/>
+      <c r="G9" s="123" t="s">
         <v>136</v>
       </c>
-      <c r="H9" s="125"/>
-      <c r="I9" s="124" t="s">
+      <c r="H9" s="124"/>
+      <c r="I9" s="123" t="s">
         <v>141</v>
       </c>
-      <c r="J9" s="125"/>
-      <c r="K9" s="124" t="s">
+      <c r="J9" s="124"/>
+      <c r="K9" s="123" t="s">
         <v>178</v>
       </c>
-      <c r="L9" s="125"/>
+      <c r="L9" s="124"/>
     </row>
     <row r="10" spans="1:12">
       <c r="B10" s="25" t="s">
@@ -14215,7 +14305,7 @@
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="128" t="s">
+      <c r="A14" s="127" t="s">
         <v>155</v>
       </c>
       <c r="D14" s="27" t="s">
@@ -14224,14 +14314,14 @@
       <c r="E14" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="F14" s="127" t="s">
+      <c r="F14" s="126" t="s">
         <v>165</v>
       </c>
-      <c r="G14" s="127"/>
-      <c r="H14" s="127"/>
+      <c r="G14" s="126"/>
+      <c r="H14" s="126"/>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="129"/>
+      <c r="A15" s="128"/>
       <c r="D15" s="34" t="s">
         <v>157</v>
       </c>
@@ -14243,7 +14333,7 @@
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="129"/>
+      <c r="A16" s="128"/>
       <c r="D16" s="35" t="s">
         <v>158</v>
       </c>
@@ -14252,7 +14342,7 @@
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="129"/>
+      <c r="A17" s="128"/>
       <c r="D17" s="23" t="s">
         <v>159</v>
       </c>
@@ -14264,73 +14354,73 @@
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="129"/>
+      <c r="A18" s="128"/>
       <c r="D18" s="13" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="129"/>
+      <c r="A19" s="128"/>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="129"/>
+      <c r="A20" s="128"/>
       <c r="E20" s="36" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="129"/>
+      <c r="A21" s="128"/>
       <c r="E21" s="13" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="129"/>
+      <c r="A22" s="128"/>
       <c r="E22" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="129"/>
+      <c r="A23" s="128"/>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="129"/>
+      <c r="A24" s="128"/>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="129"/>
+      <c r="A25" s="128"/>
       <c r="E25" s="11" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="129"/>
+      <c r="A26" s="128"/>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="129"/>
+      <c r="A27" s="128"/>
       <c r="E27" s="13" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="129"/>
+      <c r="A28" s="128"/>
       <c r="E28" s="13" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="29" spans="1:6">
-      <c r="A29" s="129"/>
+      <c r="A29" s="128"/>
       <c r="E29" s="11" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="30" spans="1:6">
-      <c r="A30" s="129"/>
+      <c r="A30" s="128"/>
       <c r="E30" s="13" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="130"/>
+      <c r="A31" s="129"/>
     </row>
     <row r="33" spans="1:7">
       <c r="B33" s="27" t="s">
@@ -14339,14 +14429,14 @@
       <c r="C33" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="D33" s="124" t="s">
+      <c r="D33" s="123" t="s">
         <v>189</v>
       </c>
-      <c r="E33" s="125"/>
-      <c r="F33" s="124" t="s">
+      <c r="E33" s="124"/>
+      <c r="F33" s="123" t="s">
         <v>178</v>
       </c>
-      <c r="G33" s="125"/>
+      <c r="G33" s="124"/>
     </row>
     <row r="34" spans="1:7">
       <c r="B34" s="26" t="s">

--- a/Document/정책문서.xlsx
+++ b/Document/정책문서.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git_fork\ProjectShoot\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DDE17B5-0E54-4BB8-A59B-DF68287F3E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C4AC7E-1646-425A-AE69-53F5803E57B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="711" firstSheet="1" activeTab="1" xr2:uid="{F9E8F865-F741-4425-897D-555A2E4B3EBE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="711" firstSheet="1" activeTab="6" xr2:uid="{F9E8F865-F741-4425-897D-555A2E4B3EBE}"/>
   </bookViews>
   <sheets>
     <sheet name="깃포크 공부" sheetId="11" state="hidden" r:id="rId1"/>
@@ -277,7 +277,103 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>???</t>
+          <t xml:space="preserve">??? 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>유진님</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>완전</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>됩니다</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>이걸로</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>개발하겠습니다</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">. </t>
         </r>
       </text>
     </comment>
@@ -291,7 +387,7 @@
     <author>user</author>
   </authors>
   <commentList>
-    <comment ref="D14" authorId="0" shapeId="0" xr:uid="{17B81B10-DFF1-4D44-B5B0-6A2782D16F0A}">
+    <comment ref="E17" authorId="0" shapeId="0" xr:uid="{42AAC616-7FC8-4B54-9933-9D724E707105}">
       <text>
         <r>
           <rPr>
@@ -311,6 +407,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
+user:
 </t>
         </r>
         <r>
@@ -672,7 +769,8 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>.</t>
+          <t xml:space="preserve">.
+</t>
         </r>
       </text>
     </comment>
@@ -681,7 +779,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="417">
   <si>
     <t>설명</t>
   </si>
@@ -2322,6 +2420,94 @@
   </si>
   <si>
     <t>- 포매이션의 경우 별도의 코딩이 아닌 기획적 작성임을 회의를 통해 합의</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유니티</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">100픽셀=1칸 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">질문 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서로 다른 움직임을 조합하여 자연스러운 적의 움직임을 구현</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조합의 개수는 현재 제한없이 많이 가능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>행동 유형</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STAY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정 Y비율에 멈춤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RUSH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC가 있는 방향을 향해 돌진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다른 이동과 조합시에만 사용 (해당 초만큼만 머뭄)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RETREAT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">U자 형태로 이탈 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATTACK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NONATTACK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격하지 않음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">애니메이션은 상태 머신으로 도입 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">행동 시퀀스 ( 확정) </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">스테이트 머신 (후보) </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3470,9 +3656,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
@@ -3497,6 +3680,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3506,18 +3701,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3525,6 +3708,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7939,15 +8125,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>598674</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>484009</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -8012,15 +8198,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>631514</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>535134</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -8036,7 +8222,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8384864" y="3495675"/>
+          <a:off x="11128064" y="3495675"/>
           <a:ext cx="1275220" cy="2343150"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -8085,15 +8271,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
+      <xdr:col>21</xdr:col>
       <xdr:colOff>545196</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
+      <xdr:col>21</xdr:col>
       <xdr:colOff>653112</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -8145,15 +8331,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -8202,15 +8388,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
+      <xdr:col>24</xdr:col>
       <xdr:colOff>250371</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -8291,15 +8477,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>561975</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>128588</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -8346,15 +8532,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>161925</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
+      <xdr:col>24</xdr:col>
       <xdr:colOff>212271</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -8426,7 +8612,7 @@
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>100</a:t>
+            <a:t>100%</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -8435,15 +8621,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>523875</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>161925</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>90488</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -8490,15 +8676,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>647700</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
+      <xdr:col>27</xdr:col>
       <xdr:colOff>247650</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -10732,7 +10918,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="33.75">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="117" t="s">
         <v>387</v>
       </c>
     </row>
@@ -10769,238 +10955,238 @@
       <c r="R3" s="51"/>
     </row>
     <row r="4" spans="1:18">
-      <c r="A4" s="116"/>
-      <c r="B4" s="117"/>
-      <c r="C4" s="114"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="121"/>
-      <c r="L4" s="121"/>
-      <c r="M4" s="121"/>
-      <c r="N4" s="121"/>
-      <c r="O4" s="121"/>
-      <c r="P4" s="121"/>
-      <c r="Q4" s="121"/>
-      <c r="R4" s="122"/>
+      <c r="A4" s="115"/>
+      <c r="B4" s="116"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="123"/>
+      <c r="J4" s="124"/>
+      <c r="K4" s="124"/>
+      <c r="L4" s="124"/>
+      <c r="M4" s="124"/>
+      <c r="N4" s="124"/>
+      <c r="O4" s="124"/>
+      <c r="P4" s="124"/>
+      <c r="Q4" s="124"/>
+      <c r="R4" s="125"/>
     </row>
     <row r="5" spans="1:18" ht="50.25" customHeight="1">
-      <c r="A5" s="116">
+      <c r="A5" s="115">
         <f t="shared" ref="A5:A12" si="0">ROW()-ROW($A$4)</f>
         <v>1</v>
       </c>
-      <c r="B5" s="117">
+      <c r="B5" s="116">
         <v>46185</v>
       </c>
-      <c r="C5" s="114"/>
-      <c r="D5" s="116" t="s">
+      <c r="C5" s="113"/>
+      <c r="D5" s="115" t="s">
         <v>380</v>
       </c>
-      <c r="E5" s="115" t="s">
+      <c r="E5" s="114" t="s">
         <v>390</v>
       </c>
-      <c r="F5" s="114"/>
-      <c r="G5" s="119" t="s">
+      <c r="F5" s="113"/>
+      <c r="G5" s="118" t="s">
         <v>393</v>
       </c>
-      <c r="H5" s="112"/>
-      <c r="I5" s="120" t="s">
+      <c r="H5" s="111"/>
+      <c r="I5" s="123" t="s">
         <v>394</v>
       </c>
-      <c r="J5" s="121"/>
-      <c r="K5" s="121"/>
-      <c r="L5" s="121"/>
-      <c r="M5" s="121"/>
-      <c r="N5" s="121"/>
-      <c r="O5" s="121"/>
-      <c r="P5" s="121"/>
-      <c r="Q5" s="121"/>
-      <c r="R5" s="122"/>
+      <c r="J5" s="124"/>
+      <c r="K5" s="124"/>
+      <c r="L5" s="124"/>
+      <c r="M5" s="124"/>
+      <c r="N5" s="124"/>
+      <c r="O5" s="124"/>
+      <c r="P5" s="124"/>
+      <c r="Q5" s="124"/>
+      <c r="R5" s="125"/>
     </row>
     <row r="6" spans="1:18" ht="50.25" customHeight="1">
-      <c r="A6" s="116">
+      <c r="A6" s="115">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="B6" s="117">
+      <c r="B6" s="116">
         <v>46185</v>
       </c>
-      <c r="C6" s="114"/>
-      <c r="D6" s="116" t="s">
+      <c r="C6" s="113"/>
+      <c r="D6" s="115" t="s">
         <v>380</v>
       </c>
-      <c r="E6" s="115" t="s">
+      <c r="E6" s="114" t="s">
         <v>390</v>
       </c>
-      <c r="F6" s="114"/>
-      <c r="G6" s="119" t="s">
+      <c r="F6" s="113"/>
+      <c r="G6" s="118" t="s">
         <v>391</v>
       </c>
-      <c r="H6" s="112"/>
-      <c r="I6" s="120" t="s">
+      <c r="H6" s="111"/>
+      <c r="I6" s="123" t="s">
         <v>392</v>
       </c>
-      <c r="J6" s="121"/>
-      <c r="K6" s="121"/>
-      <c r="L6" s="121"/>
-      <c r="M6" s="121"/>
-      <c r="N6" s="121"/>
-      <c r="O6" s="121"/>
-      <c r="P6" s="121"/>
-      <c r="Q6" s="121"/>
-      <c r="R6" s="122"/>
+      <c r="J6" s="124"/>
+      <c r="K6" s="124"/>
+      <c r="L6" s="124"/>
+      <c r="M6" s="124"/>
+      <c r="N6" s="124"/>
+      <c r="O6" s="124"/>
+      <c r="P6" s="124"/>
+      <c r="Q6" s="124"/>
+      <c r="R6" s="125"/>
     </row>
     <row r="7" spans="1:18">
-      <c r="A7" s="116">
+      <c r="A7" s="115">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B7" s="117">
+      <c r="B7" s="116">
         <v>46185</v>
       </c>
-      <c r="C7" s="114"/>
-      <c r="D7" s="116" t="s">
+      <c r="C7" s="113"/>
+      <c r="D7" s="115" t="s">
         <v>380</v>
       </c>
-      <c r="E7" s="115" t="s">
+      <c r="E7" s="114" t="s">
         <v>388</v>
       </c>
-      <c r="F7" s="114"/>
-      <c r="G7" s="113" t="s">
+      <c r="F7" s="113"/>
+      <c r="G7" s="112" t="s">
         <v>387</v>
       </c>
-      <c r="H7" s="112"/>
-      <c r="I7" s="120" t="s">
+      <c r="H7" s="111"/>
+      <c r="I7" s="123" t="s">
         <v>389</v>
       </c>
-      <c r="J7" s="121"/>
-      <c r="K7" s="121"/>
-      <c r="L7" s="121"/>
-      <c r="M7" s="121"/>
-      <c r="N7" s="121"/>
-      <c r="O7" s="121"/>
-      <c r="P7" s="121"/>
-      <c r="Q7" s="121"/>
-      <c r="R7" s="122"/>
+      <c r="J7" s="124"/>
+      <c r="K7" s="124"/>
+      <c r="L7" s="124"/>
+      <c r="M7" s="124"/>
+      <c r="N7" s="124"/>
+      <c r="O7" s="124"/>
+      <c r="P7" s="124"/>
+      <c r="Q7" s="124"/>
+      <c r="R7" s="125"/>
     </row>
     <row r="8" spans="1:18">
-      <c r="A8" s="116">
+      <c r="A8" s="115">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B8" s="117"/>
-      <c r="C8" s="114"/>
-      <c r="D8" s="116"/>
-      <c r="E8" s="115"/>
-      <c r="F8" s="114"/>
-      <c r="G8" s="113"/>
-      <c r="H8" s="112"/>
-      <c r="I8" s="120"/>
-      <c r="J8" s="121"/>
-      <c r="K8" s="121"/>
-      <c r="L8" s="121"/>
-      <c r="M8" s="121"/>
-      <c r="N8" s="121"/>
-      <c r="O8" s="121"/>
-      <c r="P8" s="121"/>
-      <c r="Q8" s="121"/>
-      <c r="R8" s="122"/>
+      <c r="B8" s="116"/>
+      <c r="C8" s="113"/>
+      <c r="D8" s="115"/>
+      <c r="E8" s="114"/>
+      <c r="F8" s="113"/>
+      <c r="G8" s="112"/>
+      <c r="H8" s="111"/>
+      <c r="I8" s="123"/>
+      <c r="J8" s="124"/>
+      <c r="K8" s="124"/>
+      <c r="L8" s="124"/>
+      <c r="M8" s="124"/>
+      <c r="N8" s="124"/>
+      <c r="O8" s="124"/>
+      <c r="P8" s="124"/>
+      <c r="Q8" s="124"/>
+      <c r="R8" s="125"/>
     </row>
     <row r="9" spans="1:18">
-      <c r="A9" s="116">
+      <c r="A9" s="115">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B9" s="117"/>
-      <c r="C9" s="114"/>
-      <c r="D9" s="116"/>
-      <c r="E9" s="115"/>
-      <c r="F9" s="114"/>
-      <c r="G9" s="113"/>
-      <c r="H9" s="112"/>
-      <c r="I9" s="120"/>
-      <c r="J9" s="121"/>
-      <c r="K9" s="121"/>
-      <c r="L9" s="121"/>
-      <c r="M9" s="121"/>
-      <c r="N9" s="121"/>
-      <c r="O9" s="121"/>
-      <c r="P9" s="121"/>
-      <c r="Q9" s="121"/>
-      <c r="R9" s="122"/>
+      <c r="B9" s="116"/>
+      <c r="C9" s="113"/>
+      <c r="D9" s="115"/>
+      <c r="E9" s="114"/>
+      <c r="F9" s="113"/>
+      <c r="G9" s="112"/>
+      <c r="H9" s="111"/>
+      <c r="I9" s="123"/>
+      <c r="J9" s="124"/>
+      <c r="K9" s="124"/>
+      <c r="L9" s="124"/>
+      <c r="M9" s="124"/>
+      <c r="N9" s="124"/>
+      <c r="O9" s="124"/>
+      <c r="P9" s="124"/>
+      <c r="Q9" s="124"/>
+      <c r="R9" s="125"/>
     </row>
     <row r="10" spans="1:18">
-      <c r="A10" s="116">
+      <c r="A10" s="115">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B10" s="117"/>
-      <c r="C10" s="114"/>
-      <c r="D10" s="116"/>
-      <c r="E10" s="115"/>
-      <c r="F10" s="114"/>
-      <c r="G10" s="113"/>
-      <c r="H10" s="112"/>
-      <c r="I10" s="120"/>
-      <c r="J10" s="121"/>
-      <c r="K10" s="121"/>
-      <c r="L10" s="121"/>
-      <c r="M10" s="121"/>
-      <c r="N10" s="121"/>
-      <c r="O10" s="121"/>
-      <c r="P10" s="121"/>
-      <c r="Q10" s="121"/>
-      <c r="R10" s="122"/>
+      <c r="B10" s="116"/>
+      <c r="C10" s="113"/>
+      <c r="D10" s="115"/>
+      <c r="E10" s="114"/>
+      <c r="F10" s="113"/>
+      <c r="G10" s="112"/>
+      <c r="H10" s="111"/>
+      <c r="I10" s="123"/>
+      <c r="J10" s="124"/>
+      <c r="K10" s="124"/>
+      <c r="L10" s="124"/>
+      <c r="M10" s="124"/>
+      <c r="N10" s="124"/>
+      <c r="O10" s="124"/>
+      <c r="P10" s="124"/>
+      <c r="Q10" s="124"/>
+      <c r="R10" s="125"/>
     </row>
     <row r="11" spans="1:18">
-      <c r="A11" s="116">
+      <c r="A11" s="115">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B11" s="117"/>
-      <c r="C11" s="114"/>
-      <c r="D11" s="116"/>
-      <c r="E11" s="115"/>
-      <c r="F11" s="114"/>
-      <c r="G11" s="113"/>
-      <c r="H11" s="112"/>
-      <c r="I11" s="120"/>
-      <c r="J11" s="121"/>
-      <c r="K11" s="121"/>
-      <c r="L11" s="121"/>
-      <c r="M11" s="121"/>
-      <c r="N11" s="121"/>
-      <c r="O11" s="121"/>
-      <c r="P11" s="121"/>
-      <c r="Q11" s="121"/>
-      <c r="R11" s="122"/>
+      <c r="B11" s="116"/>
+      <c r="C11" s="113"/>
+      <c r="D11" s="115"/>
+      <c r="E11" s="114"/>
+      <c r="F11" s="113"/>
+      <c r="G11" s="112"/>
+      <c r="H11" s="111"/>
+      <c r="I11" s="123"/>
+      <c r="J11" s="124"/>
+      <c r="K11" s="124"/>
+      <c r="L11" s="124"/>
+      <c r="M11" s="124"/>
+      <c r="N11" s="124"/>
+      <c r="O11" s="124"/>
+      <c r="P11" s="124"/>
+      <c r="Q11" s="124"/>
+      <c r="R11" s="125"/>
     </row>
     <row r="12" spans="1:18">
-      <c r="A12" s="116">
+      <c r="A12" s="115">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B12" s="117"/>
-      <c r="C12" s="114"/>
-      <c r="D12" s="116"/>
-      <c r="E12" s="115"/>
-      <c r="F12" s="114"/>
-      <c r="G12" s="113"/>
-      <c r="H12" s="112"/>
-      <c r="I12" s="120"/>
-      <c r="J12" s="121"/>
-      <c r="K12" s="121"/>
-      <c r="L12" s="121"/>
-      <c r="M12" s="121"/>
-      <c r="N12" s="121"/>
-      <c r="O12" s="121"/>
-      <c r="P12" s="121"/>
-      <c r="Q12" s="121"/>
-      <c r="R12" s="122"/>
+      <c r="B12" s="116"/>
+      <c r="C12" s="113"/>
+      <c r="D12" s="115"/>
+      <c r="E12" s="114"/>
+      <c r="F12" s="113"/>
+      <c r="G12" s="112"/>
+      <c r="H12" s="111"/>
+      <c r="I12" s="123"/>
+      <c r="J12" s="124"/>
+      <c r="K12" s="124"/>
+      <c r="L12" s="124"/>
+      <c r="M12" s="124"/>
+      <c r="N12" s="124"/>
+      <c r="O12" s="124"/>
+      <c r="P12" s="124"/>
+      <c r="Q12" s="124"/>
+      <c r="R12" s="125"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -12906,10 +13092,10 @@
         <v>335</v>
       </c>
       <c r="J36" s="85"/>
-      <c r="K36" s="86" t="s">
+      <c r="K36" s="67" t="s">
         <v>287</v>
       </c>
-      <c r="L36" s="71"/>
+      <c r="L36" s="73"/>
       <c r="M36" s="73" t="s">
         <v>286</v>
       </c>
@@ -13289,7 +13475,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96B3948A-F2EB-4210-816C-FE29D536AFF8}">
-  <dimension ref="A1:X54"/>
+  <dimension ref="A1:Y69"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="3" width="3.375" customWidth="1"/>
@@ -13299,786 +13485,876 @@
     <col min="24" max="26" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="26.25">
+    <row r="1" spans="1:25" ht="26.25">
       <c r="A1" s="47" t="s">
         <v>321</v>
       </c>
       <c r="B1" s="8"/>
     </row>
-    <row r="2" spans="1:22" ht="15.75" customHeight="1">
+    <row r="2" spans="1:25" ht="15.75" customHeight="1">
       <c r="A2" s="47"/>
       <c r="B2" s="8"/>
     </row>
-    <row r="3" spans="1:22" ht="15.75" customHeight="1">
+    <row r="3" spans="1:25" ht="15.75" customHeight="1">
       <c r="A3" s="47"/>
       <c r="B3" s="8" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="4" spans="1:22" ht="15.75" customHeight="1">
+    <row r="4" spans="1:25" ht="15.75" customHeight="1">
       <c r="A4" s="47"/>
       <c r="B4" s="8"/>
       <c r="C4" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="5" spans="1:22" ht="15.75" customHeight="1">
+    <row r="5" spans="1:25" ht="15.75" customHeight="1">
       <c r="A5" s="47"/>
       <c r="B5" s="8"/>
     </row>
-    <row r="6" spans="1:22" ht="15.75" customHeight="1">
-      <c r="B6" s="8" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" ht="15.75" customHeight="1">
+    <row r="6" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A6" s="47"/>
+      <c r="B6" s="8"/>
+      <c r="C6" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A7" s="47"/>
       <c r="B7" s="8"/>
       <c r="C7" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A8" s="47"/>
+      <c r="B8" s="8"/>
+    </row>
+    <row r="9" spans="1:25" ht="15.75" customHeight="1">
+      <c r="B9" s="8" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" ht="15.75" customHeight="1">
+      <c r="B10" s="8"/>
+      <c r="C10" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="8" spans="1:22" ht="15.75" customHeight="1">
-      <c r="B8" s="8"/>
-    </row>
-    <row r="9" spans="1:22">
-      <c r="B9" s="8" t="s">
+    <row r="11" spans="1:25" ht="15.75" customHeight="1">
+      <c r="B11" s="8"/>
+    </row>
+    <row r="12" spans="1:25">
+      <c r="B12" s="8" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="10" spans="1:22">
-      <c r="C10" s="8"/>
-    </row>
-    <row r="11" spans="1:22">
-      <c r="C11" s="14" t="s">
+    <row r="13" spans="1:25">
+      <c r="C13" s="8"/>
+    </row>
+    <row r="14" spans="1:25">
+      <c r="C14" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="48" t="s">
+      <c r="D14" s="119" t="s">
+        <v>400</v>
+      </c>
+      <c r="E14" s="50" t="s">
         <v>355</v>
       </c>
-      <c r="E11" s="48"/>
-      <c r="F11" s="48" t="s">
+      <c r="F14" s="51"/>
+      <c r="G14" s="50" t="s">
         <v>359</v>
       </c>
-      <c r="G11" s="48"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="48"/>
-      <c r="J11" s="48" t="s">
+      <c r="H14" s="52"/>
+      <c r="I14" s="52"/>
+      <c r="J14" s="51"/>
+      <c r="K14" s="50" t="s">
         <v>377</v>
       </c>
-      <c r="K11" s="48"/>
-      <c r="L11" s="48"/>
-      <c r="M11" s="48" t="s">
+      <c r="L14" s="52"/>
+      <c r="M14" s="51"/>
+      <c r="N14" s="50" t="s">
         <v>378</v>
       </c>
-      <c r="N11" s="48"/>
-      <c r="O11" s="48"/>
-      <c r="Q11" s="50" t="s">
+      <c r="O14" s="52"/>
+      <c r="P14" s="52"/>
+      <c r="Q14" s="52"/>
+      <c r="R14" s="51"/>
+      <c r="T14" s="50" t="s">
         <v>341</v>
       </c>
-      <c r="R11" s="52"/>
-      <c r="S11" s="52"/>
-      <c r="T11" s="52"/>
-      <c r="U11" s="51"/>
-      <c r="V11" s="51"/>
-    </row>
-    <row r="12" spans="1:22">
-      <c r="C12" s="11">
-        <f t="shared" ref="C12:C20" si="0">ROW()-ROW($C$11)</f>
+      <c r="U14" s="52"/>
+      <c r="V14" s="52"/>
+      <c r="W14" s="52"/>
+      <c r="X14" s="51"/>
+      <c r="Y14" s="51"/>
+    </row>
+    <row r="15" spans="1:25">
+      <c r="C15" s="11">
+        <f t="shared" ref="C15:C21" si="0">ROW()-ROW($C$14)</f>
         <v>1</v>
       </c>
-      <c r="D12" t="s">
-        <v>356</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>367</v>
-      </c>
-      <c r="G12" s="70"/>
-      <c r="H12" s="70"/>
-      <c r="I12" s="70"/>
-      <c r="J12" s="70" t="s">
+      <c r="D15" t="s">
+        <v>401</v>
+      </c>
+      <c r="E15" t="s">
+        <v>403</v>
+      </c>
+      <c r="G15" t="s">
+        <v>404</v>
+      </c>
+      <c r="K15" s="70" t="s">
         <v>357</v>
       </c>
-      <c r="K12" s="70"/>
-      <c r="L12" s="70"/>
-      <c r="M12" s="70" t="s">
-        <v>358</v>
-      </c>
-      <c r="N12" s="70"/>
-      <c r="O12" s="70"/>
-      <c r="Q12" s="64"/>
-      <c r="R12" s="65"/>
-      <c r="S12" s="65"/>
-      <c r="T12" s="65"/>
-      <c r="U12" s="65"/>
-      <c r="V12" s="66"/>
-    </row>
-    <row r="13" spans="1:22">
-      <c r="C13" s="11">
+      <c r="L15" s="70"/>
+      <c r="M15" s="70"/>
+      <c r="N15" s="13" t="s">
+        <v>407</v>
+      </c>
+      <c r="O15" s="70"/>
+      <c r="P15" s="70"/>
+      <c r="T15" s="64"/>
+      <c r="U15" s="65"/>
+      <c r="V15" s="65"/>
+      <c r="W15" s="65"/>
+      <c r="X15" s="65"/>
+      <c r="Y15" s="66"/>
+    </row>
+    <row r="16" spans="1:25">
+      <c r="C16" s="11">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="D13" t="s">
-        <v>366</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>363</v>
-      </c>
-      <c r="G13" s="70"/>
-      <c r="H13" s="70"/>
-      <c r="I13" s="70"/>
-      <c r="J13" s="70" t="s">
-        <v>357</v>
-      </c>
-      <c r="K13" s="70"/>
-      <c r="L13" s="70"/>
-      <c r="M13" s="70" t="s">
-        <v>357</v>
-      </c>
-      <c r="N13" s="70"/>
-      <c r="O13" s="70"/>
-      <c r="Q13" s="58"/>
-      <c r="R13" s="59"/>
-      <c r="S13" s="59"/>
-      <c r="T13" s="59"/>
-      <c r="U13" s="59"/>
-      <c r="V13" s="60"/>
-    </row>
-    <row r="14" spans="1:22">
-      <c r="C14" s="11">
+      <c r="D16" t="s">
+        <v>401</v>
+      </c>
+      <c r="E16" t="s">
+        <v>405</v>
+      </c>
+      <c r="G16" t="s">
+        <v>406</v>
+      </c>
+      <c r="K16" t="s">
+        <v>358</v>
+      </c>
+      <c r="N16" t="s">
+        <v>358</v>
+      </c>
+      <c r="T16" s="58"/>
+      <c r="U16" s="59"/>
+      <c r="V16" s="59"/>
+      <c r="W16" s="59"/>
+      <c r="X16" s="59"/>
+      <c r="Y16" s="60"/>
+    </row>
+    <row r="17" spans="2:25">
+      <c r="C17" s="11">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D14" t="s">
-        <v>364</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>365</v>
-      </c>
-      <c r="G14" s="70"/>
-      <c r="H14" s="70"/>
-      <c r="I14" s="70"/>
-      <c r="J14" s="70" t="s">
-        <v>357</v>
-      </c>
-      <c r="K14" s="70"/>
-      <c r="L14" s="70"/>
-      <c r="M14" s="70" t="s">
-        <v>357</v>
-      </c>
-      <c r="N14" s="70"/>
-      <c r="O14" s="70"/>
-      <c r="Q14" s="58"/>
-      <c r="R14" s="59"/>
-      <c r="S14" s="59"/>
-      <c r="T14" s="59"/>
-      <c r="U14" s="59"/>
-      <c r="V14" s="60"/>
-    </row>
-    <row r="15" spans="1:22">
-      <c r="C15" s="11">
+      <c r="E17" t="s">
+        <v>408</v>
+      </c>
+      <c r="G17" t="s">
+        <v>409</v>
+      </c>
+      <c r="T17" s="58"/>
+      <c r="U17" s="59"/>
+      <c r="V17" s="59"/>
+      <c r="W17" s="59"/>
+      <c r="X17" s="59"/>
+      <c r="Y17" s="60"/>
+    </row>
+    <row r="18" spans="2:25">
+      <c r="C18" s="11">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="D15" t="s">
-        <v>360</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>361</v>
-      </c>
-      <c r="G15" s="70"/>
-      <c r="H15" s="70"/>
-      <c r="I15" s="70"/>
-      <c r="J15" s="70" t="s">
-        <v>358</v>
-      </c>
-      <c r="K15" s="70"/>
-      <c r="L15" s="70"/>
-      <c r="M15" s="70" t="s">
-        <v>358</v>
-      </c>
-      <c r="N15" s="70"/>
-      <c r="O15" s="70"/>
-      <c r="Q15" s="58"/>
-      <c r="R15" s="59"/>
-      <c r="S15" s="59"/>
-      <c r="T15" s="59"/>
-      <c r="U15" s="59"/>
-      <c r="V15" s="60"/>
-    </row>
-    <row r="16" spans="1:22">
-      <c r="C16" s="11">
+      <c r="D18" t="s">
+        <v>402</v>
+      </c>
+      <c r="E18" t="s">
+        <v>410</v>
+      </c>
+      <c r="G18" t="s">
+        <v>412</v>
+      </c>
+      <c r="T18" s="58"/>
+      <c r="U18" s="59"/>
+      <c r="V18" s="59"/>
+      <c r="W18" s="59"/>
+      <c r="X18" s="59"/>
+      <c r="Y18" s="60"/>
+    </row>
+    <row r="19" spans="2:25">
+      <c r="C19" s="11">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="D16" t="s">
-        <v>379</v>
-      </c>
-      <c r="F16" s="13"/>
-      <c r="G16" s="70"/>
-      <c r="H16" s="70"/>
-      <c r="I16" s="70"/>
-      <c r="J16" s="70"/>
-      <c r="K16" s="70"/>
-      <c r="L16" s="70"/>
-      <c r="M16" s="70"/>
-      <c r="N16" s="70"/>
-      <c r="O16" s="70"/>
-      <c r="Q16" s="58"/>
-      <c r="R16" s="59"/>
-      <c r="S16" s="59"/>
-      <c r="T16" s="59"/>
-      <c r="U16" s="59"/>
-      <c r="V16" s="60"/>
-    </row>
-    <row r="17" spans="2:22">
-      <c r="C17" s="11">
+      <c r="E19" t="s">
+        <v>411</v>
+      </c>
+      <c r="G19" t="s">
+        <v>413</v>
+      </c>
+      <c r="T19" s="58"/>
+      <c r="U19" s="59"/>
+      <c r="V19" s="59"/>
+      <c r="W19" s="59"/>
+      <c r="X19" s="59"/>
+      <c r="Y19" s="60"/>
+    </row>
+    <row r="20" spans="2:25">
+      <c r="C20" s="11">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="Q17" s="58"/>
-      <c r="R17" s="59"/>
-      <c r="S17" s="59"/>
-      <c r="T17" s="59"/>
-      <c r="U17" s="59"/>
-      <c r="V17" s="60"/>
-    </row>
-    <row r="18" spans="2:22">
-      <c r="C18" s="11">
+      <c r="T20" s="58"/>
+      <c r="U20" s="59"/>
+      <c r="V20" s="59"/>
+      <c r="W20" s="59"/>
+      <c r="X20" s="59"/>
+      <c r="Y20" s="60"/>
+    </row>
+    <row r="21" spans="2:25">
+      <c r="C21" s="11">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="Q18" s="58"/>
-      <c r="R18" s="59"/>
-      <c r="S18" s="59"/>
-      <c r="T18" s="59"/>
-      <c r="U18" s="59"/>
-      <c r="V18" s="60"/>
-    </row>
-    <row r="19" spans="2:22">
-      <c r="C19" s="11">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="Q19" s="58"/>
-      <c r="R19" s="59"/>
-      <c r="S19" s="59"/>
-      <c r="T19" s="59"/>
-      <c r="U19" s="59"/>
-      <c r="V19" s="60"/>
-    </row>
-    <row r="20" spans="2:22">
-      <c r="C20" s="11">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="Q20" s="58"/>
-      <c r="R20" s="59"/>
-      <c r="S20" s="59"/>
-      <c r="T20" s="59"/>
-      <c r="U20" s="59"/>
-      <c r="V20" s="60"/>
-    </row>
-    <row r="21" spans="2:22">
-      <c r="Q21" s="58"/>
-      <c r="R21" s="59"/>
-      <c r="S21" s="59"/>
-      <c r="T21" s="59"/>
+      <c r="D21" t="s">
+        <v>379</v>
+      </c>
+      <c r="T21" s="58"/>
       <c r="U21" s="59"/>
-      <c r="V21" s="60"/>
-    </row>
-    <row r="22" spans="2:22">
-      <c r="Q22" s="58"/>
-      <c r="R22" s="59"/>
-      <c r="S22" s="59"/>
-      <c r="T22" s="59"/>
+      <c r="V21" s="59"/>
+      <c r="W21" s="59"/>
+      <c r="X21" s="59"/>
+      <c r="Y21" s="60"/>
+    </row>
+    <row r="22" spans="2:25">
+      <c r="C22" s="11"/>
+      <c r="T22" s="58"/>
       <c r="U22" s="59"/>
-      <c r="V22" s="60"/>
-    </row>
-    <row r="23" spans="2:22">
-      <c r="Q23" s="58"/>
-      <c r="R23" s="59"/>
-      <c r="S23" s="59"/>
-      <c r="T23" s="59"/>
+      <c r="V22" s="59"/>
+      <c r="W22" s="59"/>
+      <c r="X22" s="59"/>
+      <c r="Y22" s="60"/>
+    </row>
+    <row r="23" spans="2:25">
+      <c r="C23" s="11"/>
+      <c r="T23" s="58"/>
       <c r="U23" s="59"/>
-      <c r="V23" s="60"/>
-    </row>
-    <row r="24" spans="2:22">
-      <c r="H24" s="111"/>
-      <c r="Q24" s="58"/>
-      <c r="R24" s="59"/>
-      <c r="S24" s="59"/>
-      <c r="T24" s="59"/>
+      <c r="V23" s="59"/>
+      <c r="W23" s="59"/>
+      <c r="X23" s="59"/>
+      <c r="Y23" s="60"/>
+    </row>
+    <row r="24" spans="2:25">
+      <c r="D24" s="48" t="s">
+        <v>355</v>
+      </c>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48" t="s">
+        <v>359</v>
+      </c>
+      <c r="G24" s="48"/>
+      <c r="H24" s="48"/>
+      <c r="I24" s="48"/>
+      <c r="J24" s="48" t="s">
+        <v>377</v>
+      </c>
+      <c r="K24" s="48"/>
+      <c r="L24" s="48"/>
+      <c r="M24" s="48" t="s">
+        <v>378</v>
+      </c>
+      <c r="N24" s="48"/>
+      <c r="O24" s="48"/>
+      <c r="T24" s="58"/>
       <c r="U24" s="59"/>
-      <c r="V24" s="60"/>
-    </row>
-    <row r="25" spans="2:22">
-      <c r="Q25" s="58"/>
-      <c r="R25" s="59"/>
-      <c r="S25" s="59"/>
-      <c r="T25" s="59"/>
+      <c r="V24" s="59"/>
+      <c r="W24" s="59"/>
+      <c r="X24" s="59"/>
+      <c r="Y24" s="60"/>
+    </row>
+    <row r="25" spans="2:25">
+      <c r="D25" t="s">
+        <v>356</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>367</v>
+      </c>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70"/>
+      <c r="T25" s="58"/>
       <c r="U25" s="59"/>
-      <c r="V25" s="60"/>
-    </row>
-    <row r="26" spans="2:22">
-      <c r="Q26" s="58"/>
-      <c r="R26" s="59"/>
-      <c r="S26" s="59"/>
-      <c r="T26" s="59"/>
+      <c r="V25" s="59"/>
+      <c r="W25" s="59"/>
+      <c r="X25" s="59"/>
+      <c r="Y25" s="60"/>
+    </row>
+    <row r="26" spans="2:25">
+      <c r="D26" t="s">
+        <v>366</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>363</v>
+      </c>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="70" t="s">
+        <v>357</v>
+      </c>
+      <c r="K26" s="70"/>
+      <c r="L26" s="70"/>
+      <c r="M26" s="70" t="s">
+        <v>357</v>
+      </c>
+      <c r="N26" s="70"/>
+      <c r="O26" s="70"/>
+      <c r="T26" s="58"/>
       <c r="U26" s="59"/>
-      <c r="V26" s="60"/>
-    </row>
-    <row r="27" spans="2:22">
-      <c r="Q27" s="58"/>
-      <c r="R27" s="59"/>
-      <c r="S27" s="59"/>
-      <c r="T27" s="59"/>
+      <c r="V26" s="59"/>
+      <c r="W26" s="59"/>
+      <c r="X26" s="59"/>
+      <c r="Y26" s="60"/>
+    </row>
+    <row r="27" spans="2:25">
+      <c r="D27" t="s">
+        <v>364</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="70" t="s">
+        <v>357</v>
+      </c>
+      <c r="K27" s="70"/>
+      <c r="L27" s="70"/>
+      <c r="M27" s="70" t="s">
+        <v>357</v>
+      </c>
+      <c r="N27" s="70"/>
+      <c r="O27" s="70"/>
+      <c r="T27" s="58"/>
       <c r="U27" s="59"/>
-      <c r="V27" s="60"/>
-    </row>
-    <row r="28" spans="2:22">
-      <c r="Q28" s="58"/>
-      <c r="R28" s="59"/>
-      <c r="S28" s="59"/>
-      <c r="T28" s="59"/>
+      <c r="V27" s="59"/>
+      <c r="W27" s="59"/>
+      <c r="X27" s="59"/>
+      <c r="Y27" s="60"/>
+    </row>
+    <row r="28" spans="2:25">
+      <c r="D28" t="s">
+        <v>360</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="70" t="s">
+        <v>358</v>
+      </c>
+      <c r="K28" s="70"/>
+      <c r="L28" s="70"/>
+      <c r="M28" s="70" t="s">
+        <v>358</v>
+      </c>
+      <c r="N28" s="70"/>
+      <c r="O28" s="70"/>
+      <c r="T28" s="58"/>
       <c r="U28" s="59"/>
-      <c r="V28" s="60"/>
-    </row>
-    <row r="29" spans="2:22">
-      <c r="B29" s="8"/>
-      <c r="Q29" s="58"/>
-      <c r="R29" s="59"/>
-      <c r="S29" s="59"/>
-      <c r="T29" s="59"/>
+      <c r="V28" s="59"/>
+      <c r="W28" s="59"/>
+      <c r="X28" s="59"/>
+      <c r="Y28" s="60"/>
+    </row>
+    <row r="29" spans="2:25">
+      <c r="F29" s="13"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70"/>
+      <c r="J29" s="70"/>
+      <c r="K29" s="70"/>
+      <c r="L29" s="70"/>
+      <c r="M29" s="70"/>
+      <c r="N29" s="70"/>
+      <c r="O29" s="70"/>
+      <c r="T29" s="58"/>
       <c r="U29" s="59"/>
-      <c r="V29" s="60"/>
-    </row>
-    <row r="30" spans="2:22">
-      <c r="Q30" s="58"/>
-      <c r="R30" s="59"/>
-      <c r="S30" s="59"/>
-      <c r="T30" s="59"/>
+      <c r="V29" s="59"/>
+      <c r="W29" s="59"/>
+      <c r="X29" s="59"/>
+      <c r="Y29" s="60"/>
+    </row>
+    <row r="30" spans="2:25">
+      <c r="T30" s="58"/>
       <c r="U30" s="59"/>
-      <c r="V30" s="60"/>
-    </row>
-    <row r="31" spans="2:22">
-      <c r="Q31" s="61"/>
-      <c r="R31" s="62"/>
-      <c r="S31" s="62"/>
-      <c r="T31" s="62"/>
-      <c r="U31" s="62"/>
-      <c r="V31" s="63"/>
-    </row>
-    <row r="33" spans="2:24">
-      <c r="B33" s="8" t="s">
+      <c r="V30" s="59"/>
+      <c r="W30" s="59"/>
+      <c r="X30" s="59"/>
+      <c r="Y30" s="60"/>
+    </row>
+    <row r="31" spans="2:25">
+      <c r="D31" t="s">
+        <v>416</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>415</v>
+      </c>
+      <c r="T31" s="58"/>
+      <c r="U31" s="59"/>
+      <c r="V31" s="59"/>
+      <c r="W31" s="59"/>
+      <c r="X31" s="59"/>
+      <c r="Y31" s="60"/>
+    </row>
+    <row r="32" spans="2:25">
+      <c r="B32" s="8"/>
+      <c r="T32" s="58"/>
+      <c r="U32" s="59"/>
+      <c r="V32" s="59"/>
+      <c r="W32" s="59"/>
+      <c r="X32" s="59"/>
+      <c r="Y32" s="60"/>
+    </row>
+    <row r="33" spans="2:25">
+      <c r="G33" t="s">
+        <v>414</v>
+      </c>
+      <c r="T33" s="58"/>
+      <c r="U33" s="59"/>
+      <c r="V33" s="59"/>
+      <c r="W33" s="59"/>
+      <c r="X33" s="59"/>
+      <c r="Y33" s="60"/>
+    </row>
+    <row r="34" spans="2:25">
+      <c r="T34" s="61"/>
+      <c r="U34" s="62"/>
+      <c r="V34" s="62"/>
+      <c r="W34" s="62"/>
+      <c r="X34" s="62"/>
+      <c r="Y34" s="63"/>
+    </row>
+    <row r="48" spans="2:25">
+      <c r="B48" s="8" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="34" spans="2:24">
-      <c r="B34" s="8"/>
-      <c r="C34" t="s">
+    <row r="49" spans="2:24">
+      <c r="B49" s="8"/>
+      <c r="C49" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="35" spans="2:24" ht="17.25" thickBot="1">
-      <c r="B35" s="8"/>
-    </row>
-    <row r="36" spans="2:24">
-      <c r="B36" s="8"/>
-      <c r="D36" s="79" t="s">
+    <row r="50" spans="2:24" ht="17.25" thickBot="1">
+      <c r="B50" s="8"/>
+    </row>
+    <row r="51" spans="2:24">
+      <c r="B51" s="8"/>
+      <c r="D51" s="79" t="s">
         <v>304</v>
       </c>
-      <c r="E36" s="75" t="s">
+      <c r="E51" s="75" t="s">
         <v>284</v>
       </c>
-      <c r="F36" s="76"/>
-      <c r="G36" s="75" t="s">
+      <c r="F51" s="76"/>
+      <c r="G51" s="75" t="s">
         <v>285</v>
       </c>
-      <c r="H36" s="76"/>
-      <c r="I36" s="85" t="s">
+      <c r="H51" s="76"/>
+      <c r="I51" s="85" t="s">
         <v>335</v>
       </c>
-      <c r="J36" s="85"/>
-      <c r="K36" s="75" t="s">
+      <c r="J51" s="85"/>
+      <c r="K51" s="75" t="s">
         <v>287</v>
       </c>
-      <c r="L36" s="76"/>
-      <c r="M36" s="75" t="s">
+      <c r="L51" s="76"/>
+      <c r="M51" s="75" t="s">
         <v>286</v>
       </c>
-      <c r="N36" s="76"/>
-      <c r="O36" s="75" t="s">
+      <c r="N51" s="76"/>
+      <c r="O51" s="75" t="s">
         <v>288</v>
       </c>
-      <c r="P36" s="76"/>
-      <c r="Q36" s="75" t="s">
+      <c r="P51" s="76"/>
+      <c r="Q51" s="75" t="s">
         <v>289</v>
       </c>
-      <c r="R36" s="76"/>
-      <c r="S36" s="67" t="s">
+      <c r="R51" s="76"/>
+      <c r="S51" s="67" t="s">
         <v>290</v>
       </c>
-      <c r="T36" s="73"/>
-      <c r="U36" s="102" t="s">
+      <c r="T51" s="73"/>
+      <c r="U51" s="102" t="s">
         <v>370</v>
       </c>
-      <c r="V36" s="102"/>
-      <c r="W36" s="103" t="s">
+      <c r="V51" s="102"/>
+      <c r="W51" s="103" t="s">
         <v>372</v>
       </c>
-      <c r="X36" s="104"/>
-    </row>
-    <row r="37" spans="2:24">
-      <c r="B37" s="8"/>
-      <c r="D37" s="79" t="s">
+      <c r="X51" s="104"/>
+    </row>
+    <row r="52" spans="2:24">
+      <c r="B52" s="8"/>
+      <c r="D52" s="79" t="s">
         <v>300</v>
       </c>
-      <c r="E37" s="75" t="s">
+      <c r="E52" s="75" t="s">
         <v>301</v>
       </c>
-      <c r="F37" s="76"/>
-      <c r="G37" s="75" t="s">
+      <c r="F52" s="76"/>
+      <c r="G52" s="75" t="s">
         <v>316</v>
       </c>
-      <c r="H37" s="76"/>
-      <c r="I37" s="85" t="s">
+      <c r="H52" s="76"/>
+      <c r="I52" s="85" t="s">
         <v>316</v>
       </c>
-      <c r="J37" s="85"/>
-      <c r="K37" s="75" t="s">
+      <c r="J52" s="85"/>
+      <c r="K52" s="75" t="s">
         <v>303</v>
       </c>
-      <c r="L37" s="76"/>
-      <c r="M37" s="75" t="s">
+      <c r="L52" s="76"/>
+      <c r="M52" s="75" t="s">
         <v>300</v>
       </c>
-      <c r="N37" s="76"/>
-      <c r="O37" s="75" t="s">
+      <c r="N52" s="76"/>
+      <c r="O52" s="75" t="s">
         <v>301</v>
       </c>
-      <c r="P37" s="76"/>
-      <c r="Q37" s="75" t="s">
+      <c r="P52" s="76"/>
+      <c r="Q52" s="75" t="s">
         <v>301</v>
       </c>
-      <c r="R37" s="76"/>
-      <c r="S37" s="86" t="s">
+      <c r="R52" s="76"/>
+      <c r="S52" s="86" t="s">
         <v>368</v>
       </c>
-      <c r="T37" s="71"/>
-      <c r="U37" s="105" t="s">
+      <c r="T52" s="71"/>
+      <c r="U52" s="105" t="s">
         <v>301</v>
       </c>
-      <c r="V37" s="105"/>
-      <c r="W37" s="106" t="s">
+      <c r="V52" s="105"/>
+      <c r="W52" s="106" t="s">
         <v>301</v>
       </c>
-      <c r="X37" s="107"/>
-    </row>
-    <row r="38" spans="2:24">
-      <c r="B38" s="8"/>
-      <c r="D38" s="79" t="s">
+      <c r="X52" s="107"/>
+    </row>
+    <row r="53" spans="2:24">
+      <c r="B53" s="8"/>
+      <c r="D53" s="79" t="s">
         <v>291</v>
       </c>
-      <c r="E38" s="78" t="s">
+      <c r="E53" s="78" t="s">
         <v>292</v>
       </c>
-      <c r="F38" s="76"/>
-      <c r="G38" s="78" t="s">
+      <c r="F53" s="76"/>
+      <c r="G53" s="78" t="s">
         <v>309</v>
       </c>
-      <c r="H38" s="76"/>
-      <c r="I38" s="85" t="s">
+      <c r="H53" s="76"/>
+      <c r="I53" s="85" t="s">
         <v>336</v>
       </c>
-      <c r="J38" s="85"/>
-      <c r="K38" s="78" t="s">
+      <c r="J53" s="85"/>
+      <c r="K53" s="78" t="s">
         <v>294</v>
       </c>
-      <c r="L38" s="76"/>
-      <c r="M38" s="78" t="s">
+      <c r="L53" s="76"/>
+      <c r="M53" s="78" t="s">
         <v>293</v>
       </c>
-      <c r="N38" s="76"/>
-      <c r="O38" s="78" t="s">
+      <c r="N53" s="76"/>
+      <c r="O53" s="78" t="s">
         <v>295</v>
       </c>
-      <c r="P38" s="76"/>
-      <c r="Q38" s="78" t="s">
+      <c r="P53" s="76"/>
+      <c r="Q53" s="78" t="s">
         <v>296</v>
       </c>
-      <c r="R38" s="76"/>
-      <c r="S38" s="86" t="s">
+      <c r="R53" s="76"/>
+      <c r="S53" s="86" t="s">
         <v>297</v>
       </c>
-      <c r="T38" s="71"/>
-      <c r="U38" s="108" t="s">
+      <c r="T53" s="71"/>
+      <c r="U53" s="108" t="s">
         <v>369</v>
       </c>
-      <c r="V38" s="105"/>
-      <c r="W38" s="109" t="s">
+      <c r="V53" s="105"/>
+      <c r="W53" s="109" t="s">
         <v>371</v>
       </c>
-      <c r="X38" s="107"/>
-    </row>
-    <row r="39" spans="2:24">
-      <c r="B39" s="8"/>
-      <c r="D39" s="80">
-        <f>ROW()-ROW($D$38)</f>
+      <c r="X53" s="107"/>
+    </row>
+    <row r="54" spans="2:24">
+      <c r="B54" s="8"/>
+      <c r="D54" s="80">
+        <f>ROW()-ROW($D$53)</f>
         <v>1</v>
       </c>
-      <c r="E39" s="92">
+      <c r="E54" s="92">
         <v>3</v>
       </c>
-      <c r="F39" s="93"/>
-      <c r="G39" s="93" t="s">
+      <c r="F54" s="93"/>
+      <c r="G54" s="93" t="s">
         <v>298</v>
       </c>
-      <c r="H39" s="93"/>
-      <c r="I39" s="93" t="s">
+      <c r="H54" s="93"/>
+      <c r="I54" s="93" t="s">
         <v>338</v>
       </c>
-      <c r="J39" s="93"/>
-      <c r="K39" s="93" t="s">
+      <c r="J54" s="93"/>
+      <c r="K54" s="93" t="s">
         <v>299</v>
       </c>
-      <c r="L39" s="93"/>
-      <c r="M39" s="93">
+      <c r="L54" s="93"/>
+      <c r="M54" s="93">
         <v>5</v>
       </c>
-      <c r="N39" s="93"/>
-      <c r="O39" s="93">
+      <c r="N54" s="93"/>
+      <c r="O54" s="93">
         <v>30</v>
       </c>
-      <c r="P39" s="93"/>
-      <c r="Q39" s="93">
+      <c r="P54" s="93"/>
+      <c r="Q54" s="93">
         <v>30</v>
       </c>
-      <c r="R39" s="93"/>
-      <c r="S39" s="95" t="s">
+      <c r="R54" s="93"/>
+      <c r="S54" s="95" t="s">
         <v>373</v>
       </c>
-      <c r="T39" s="93"/>
-      <c r="U39" s="92">
+      <c r="T54" s="93"/>
+      <c r="U54" s="92">
         <v>75</v>
       </c>
-      <c r="V39" s="93"/>
-      <c r="W39" s="92">
+      <c r="V54" s="93"/>
+      <c r="W54" s="92">
         <v>30</v>
       </c>
-      <c r="X39" s="96"/>
-    </row>
-    <row r="40" spans="2:24">
-      <c r="B40" s="8"/>
-      <c r="D40" s="80">
-        <f t="shared" ref="D40:D42" si="1">ROW()-ROW($D$38)</f>
+      <c r="X54" s="96"/>
+    </row>
+    <row r="55" spans="2:24">
+      <c r="B55" s="8"/>
+      <c r="D55" s="80">
+        <f t="shared" ref="D55:D57" si="1">ROW()-ROW($D$53)</f>
         <v>2</v>
       </c>
-      <c r="E40" s="93" t="s">
+      <c r="E55" s="93" t="s">
         <v>302</v>
       </c>
-      <c r="F40" s="93"/>
-      <c r="G40" s="93" t="s">
+      <c r="F55" s="93"/>
+      <c r="G55" s="93" t="s">
         <v>302</v>
       </c>
-      <c r="H40" s="93"/>
-      <c r="I40" s="93" t="s">
+      <c r="H55" s="93"/>
+      <c r="I55" s="93" t="s">
         <v>339</v>
       </c>
-      <c r="J40" s="93"/>
-      <c r="K40" s="93" t="s">
+      <c r="J55" s="93"/>
+      <c r="K55" s="93" t="s">
         <v>302</v>
       </c>
-      <c r="L40" s="93"/>
-      <c r="M40" s="94"/>
-      <c r="N40" s="18"/>
-      <c r="O40" s="94"/>
-      <c r="P40" s="18"/>
-      <c r="Q40" s="94"/>
-      <c r="R40" s="18"/>
-      <c r="S40" s="97"/>
-      <c r="T40" s="18"/>
-      <c r="U40" s="94"/>
-      <c r="V40" s="18"/>
-      <c r="W40" s="94"/>
-      <c r="X40" s="98"/>
-    </row>
-    <row r="41" spans="2:24">
-      <c r="B41" s="8"/>
-      <c r="D41" s="80">
+      <c r="L55" s="93"/>
+      <c r="M55" s="94"/>
+      <c r="N55" s="18"/>
+      <c r="O55" s="94"/>
+      <c r="P55" s="18"/>
+      <c r="Q55" s="94"/>
+      <c r="R55" s="18"/>
+      <c r="S55" s="97"/>
+      <c r="T55" s="18"/>
+      <c r="U55" s="94"/>
+      <c r="V55" s="18"/>
+      <c r="W55" s="94"/>
+      <c r="X55" s="98"/>
+    </row>
+    <row r="56" spans="2:24">
+      <c r="B56" s="8"/>
+      <c r="D56" s="80">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="E41" s="93" t="s">
+      <c r="E56" s="93" t="s">
         <v>302</v>
       </c>
-      <c r="F41" s="93"/>
-      <c r="G41" s="93" t="s">
+      <c r="F56" s="93"/>
+      <c r="G56" s="93" t="s">
         <v>302</v>
       </c>
-      <c r="H41" s="93"/>
-      <c r="I41" s="93" t="s">
+      <c r="H56" s="93"/>
+      <c r="I56" s="93" t="s">
         <v>348</v>
       </c>
-      <c r="J41" s="93"/>
-      <c r="K41" s="93" t="s">
+      <c r="J56" s="93"/>
+      <c r="K56" s="93" t="s">
         <v>302</v>
       </c>
-      <c r="L41" s="93"/>
-      <c r="M41" s="94"/>
-      <c r="N41" s="18"/>
-      <c r="O41" s="94"/>
-      <c r="P41" s="18"/>
-      <c r="Q41" s="94"/>
-      <c r="R41" s="18"/>
-      <c r="S41" s="97"/>
-      <c r="T41" s="18"/>
-      <c r="U41" s="94"/>
-      <c r="V41" s="18"/>
-      <c r="W41" s="94"/>
-      <c r="X41" s="98"/>
-    </row>
-    <row r="42" spans="2:24" ht="17.25" thickBot="1">
-      <c r="B42" s="8"/>
-      <c r="D42" s="82">
+      <c r="L56" s="93"/>
+      <c r="M56" s="94"/>
+      <c r="N56" s="18"/>
+      <c r="O56" s="94"/>
+      <c r="P56" s="18"/>
+      <c r="Q56" s="94"/>
+      <c r="R56" s="18"/>
+      <c r="S56" s="97"/>
+      <c r="T56" s="18"/>
+      <c r="U56" s="94"/>
+      <c r="V56" s="18"/>
+      <c r="W56" s="94"/>
+      <c r="X56" s="98"/>
+    </row>
+    <row r="57" spans="2:24" ht="17.25" thickBot="1">
+      <c r="B57" s="8"/>
+      <c r="D57" s="82">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="E42" s="83" t="s">
+      <c r="E57" s="83" t="s">
         <v>302</v>
       </c>
-      <c r="F42" s="83"/>
-      <c r="G42" s="83" t="s">
+      <c r="F57" s="83"/>
+      <c r="G57" s="83" t="s">
         <v>302</v>
       </c>
-      <c r="H42" s="83"/>
-      <c r="I42" s="83" t="s">
+      <c r="H57" s="83"/>
+      <c r="I57" s="83" t="s">
         <v>302</v>
       </c>
-      <c r="J42" s="83"/>
-      <c r="K42" s="84" t="s">
+      <c r="J57" s="83"/>
+      <c r="K57" s="84" t="s">
         <v>349</v>
       </c>
-      <c r="L42" s="84"/>
-      <c r="M42" s="84"/>
-      <c r="N42" s="84"/>
-      <c r="O42" s="84"/>
-      <c r="P42" s="84"/>
-      <c r="Q42" s="84"/>
-      <c r="R42" s="84"/>
-      <c r="S42" s="99"/>
-      <c r="T42" s="100"/>
-      <c r="U42" s="100"/>
-      <c r="V42" s="100"/>
-      <c r="W42" s="100"/>
-      <c r="X42" s="101"/>
-    </row>
-    <row r="43" spans="2:24">
-      <c r="B43" s="8"/>
-    </row>
-    <row r="44" spans="2:24">
-      <c r="B44" s="8"/>
-      <c r="D44" s="18" t="s">
+      <c r="L57" s="84"/>
+      <c r="M57" s="84"/>
+      <c r="N57" s="84"/>
+      <c r="O57" s="84"/>
+      <c r="P57" s="84"/>
+      <c r="Q57" s="84"/>
+      <c r="R57" s="84"/>
+      <c r="S57" s="99"/>
+      <c r="T57" s="100"/>
+      <c r="U57" s="100"/>
+      <c r="V57" s="100"/>
+      <c r="W57" s="100"/>
+      <c r="X57" s="101"/>
+    </row>
+    <row r="58" spans="2:24">
+      <c r="B58" s="8"/>
+    </row>
+    <row r="59" spans="2:24">
+      <c r="B59" s="8"/>
+      <c r="D59" s="18" t="s">
         <v>306</v>
       </c>
-      <c r="G44" t="s">
+      <c r="G59" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="45" spans="2:24">
-      <c r="B45" s="8"/>
-      <c r="D45" s="18" t="s">
+    <row r="60" spans="2:24">
+      <c r="B60" s="8"/>
+      <c r="D60" s="18" t="s">
         <v>307</v>
       </c>
-      <c r="G45" t="s">
+      <c r="G60" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="46" spans="2:24">
-      <c r="B46" s="8"/>
-      <c r="D46" s="18" t="s">
+    <row r="61" spans="2:24">
+      <c r="B61" s="8"/>
+      <c r="D61" s="18" t="s">
         <v>315</v>
       </c>
-      <c r="G46" t="s">
+      <c r="G61" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="47" spans="2:24">
-      <c r="B47" s="8"/>
-      <c r="D47" s="18" t="s">
+    <row r="62" spans="2:24">
+      <c r="B62" s="8"/>
+      <c r="D62" s="18" t="s">
         <v>337</v>
       </c>
-      <c r="G47" s="18" t="s">
+      <c r="G62" s="18" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="48" spans="2:24">
-      <c r="B48" s="8"/>
-      <c r="D48" s="18" t="s">
+    <row r="63" spans="2:24">
+      <c r="B63" s="8"/>
+      <c r="D63" s="18" t="s">
         <v>313</v>
       </c>
-      <c r="G48" s="18" t="s">
+      <c r="G63" s="18" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="49" spans="2:23">
-      <c r="B49" s="8"/>
-      <c r="D49" s="18" t="s">
+    <row r="64" spans="2:24">
+      <c r="B64" s="8"/>
+      <c r="D64" s="18" t="s">
         <v>311</v>
       </c>
-      <c r="G49" s="18" t="s">
+      <c r="G64" s="18" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="50" spans="2:23">
-      <c r="B50" s="8"/>
-      <c r="D50" s="18" t="s">
+    <row r="65" spans="2:23">
+      <c r="B65" s="8"/>
+      <c r="D65" s="18" t="s">
         <v>323</v>
       </c>
-      <c r="E50" s="18"/>
-      <c r="F50" s="18"/>
-      <c r="G50" s="18" t="s">
+      <c r="E65" s="18"/>
+      <c r="F65" s="18"/>
+      <c r="G65" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="H50" s="18"/>
-    </row>
-    <row r="51" spans="2:23">
-      <c r="B51" s="8"/>
-      <c r="D51" s="18" t="s">
+      <c r="H65" s="18"/>
+    </row>
+    <row r="66" spans="2:23">
+      <c r="B66" s="8"/>
+      <c r="D66" s="18" t="s">
         <v>326</v>
       </c>
-      <c r="E51" s="18"/>
-      <c r="F51" s="18"/>
-      <c r="G51" s="18" t="s">
+      <c r="E66" s="18"/>
+      <c r="F66" s="18"/>
+      <c r="G66" s="18" t="s">
         <v>327</v>
       </c>
-      <c r="H51" s="18"/>
-      <c r="S51" s="18"/>
-      <c r="T51" s="18"/>
-      <c r="U51" s="18"/>
-      <c r="V51" s="18"/>
-      <c r="W51" s="18"/>
-    </row>
-    <row r="52" spans="2:23">
-      <c r="D52" s="8" t="s">
+      <c r="H66" s="18"/>
+      <c r="S66" s="18"/>
+      <c r="T66" s="18"/>
+      <c r="U66" s="18"/>
+      <c r="V66" s="18"/>
+      <c r="W66" s="18"/>
+    </row>
+    <row r="67" spans="2:23">
+      <c r="D67" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="G52" s="8" t="s">
+      <c r="G67" s="8" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="53" spans="2:23">
-      <c r="D53" s="8" t="s">
+    <row r="68" spans="2:23">
+      <c r="D68" s="8" t="s">
         <v>369</v>
       </c>
-      <c r="G53" s="8" t="s">
+      <c r="G68" s="8" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="54" spans="2:23">
-      <c r="D54" s="8" t="s">
+    <row r="69" spans="2:23">
+      <c r="D69" s="8" t="s">
         <v>371</v>
       </c>
-      <c r="G54" s="8" t="s">
+      <c r="G69" s="8" t="s">
         <v>376</v>
       </c>
     </row>
@@ -14122,24 +14398,24 @@
       <c r="C3" s="33"/>
     </row>
     <row r="5" spans="1:12">
-      <c r="B5" s="126" t="s">
+      <c r="B5" s="129" t="s">
         <v>129</v>
       </c>
-      <c r="C5" s="126"/>
-      <c r="D5" s="123"/>
-      <c r="E5" s="123" t="s">
+      <c r="C5" s="129"/>
+      <c r="D5" s="120"/>
+      <c r="E5" s="120" t="s">
         <v>126</v>
       </c>
-      <c r="F5" s="125"/>
-      <c r="G5" s="124"/>
-      <c r="H5" s="123" t="s">
+      <c r="F5" s="121"/>
+      <c r="G5" s="122"/>
+      <c r="H5" s="120" t="s">
         <v>136</v>
       </c>
-      <c r="I5" s="124"/>
-      <c r="J5" s="123" t="s">
+      <c r="I5" s="122"/>
+      <c r="J5" s="120" t="s">
         <v>141</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="122"/>
     </row>
     <row r="6" spans="1:12">
       <c r="B6" s="25" t="s">
@@ -14209,27 +14485,27 @@
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="B9" s="123" t="s">
+      <c r="B9" s="120" t="s">
         <v>151</v>
       </c>
-      <c r="C9" s="124"/>
-      <c r="D9" s="123" t="s">
+      <c r="C9" s="122"/>
+      <c r="D9" s="120" t="s">
         <v>153</v>
       </c>
-      <c r="E9" s="125"/>
-      <c r="F9" s="124"/>
-      <c r="G9" s="123" t="s">
+      <c r="E9" s="121"/>
+      <c r="F9" s="122"/>
+      <c r="G9" s="120" t="s">
         <v>136</v>
       </c>
-      <c r="H9" s="124"/>
-      <c r="I9" s="123" t="s">
+      <c r="H9" s="122"/>
+      <c r="I9" s="120" t="s">
         <v>141</v>
       </c>
-      <c r="J9" s="124"/>
-      <c r="K9" s="123" t="s">
+      <c r="J9" s="122"/>
+      <c r="K9" s="120" t="s">
         <v>178</v>
       </c>
-      <c r="L9" s="124"/>
+      <c r="L9" s="122"/>
     </row>
     <row r="10" spans="1:12">
       <c r="B10" s="25" t="s">
@@ -14305,7 +14581,7 @@
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="127" t="s">
+      <c r="A14" s="126" t="s">
         <v>155</v>
       </c>
       <c r="D14" s="27" t="s">
@@ -14314,14 +14590,14 @@
       <c r="E14" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="F14" s="126" t="s">
+      <c r="F14" s="129" t="s">
         <v>165</v>
       </c>
-      <c r="G14" s="126"/>
-      <c r="H14" s="126"/>
+      <c r="G14" s="129"/>
+      <c r="H14" s="129"/>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="128"/>
+      <c r="A15" s="127"/>
       <c r="D15" s="34" t="s">
         <v>157</v>
       </c>
@@ -14333,7 +14609,7 @@
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="128"/>
+      <c r="A16" s="127"/>
       <c r="D16" s="35" t="s">
         <v>158</v>
       </c>
@@ -14342,7 +14618,7 @@
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="128"/>
+      <c r="A17" s="127"/>
       <c r="D17" s="23" t="s">
         <v>159</v>
       </c>
@@ -14354,73 +14630,73 @@
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="128"/>
+      <c r="A18" s="127"/>
       <c r="D18" s="13" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="128"/>
+      <c r="A19" s="127"/>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="128"/>
+      <c r="A20" s="127"/>
       <c r="E20" s="36" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="128"/>
+      <c r="A21" s="127"/>
       <c r="E21" s="13" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="128"/>
+      <c r="A22" s="127"/>
       <c r="E22" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="128"/>
+      <c r="A23" s="127"/>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="128"/>
+      <c r="A24" s="127"/>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="128"/>
+      <c r="A25" s="127"/>
       <c r="E25" s="11" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="128"/>
+      <c r="A26" s="127"/>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="128"/>
+      <c r="A27" s="127"/>
       <c r="E27" s="13" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="128"/>
+      <c r="A28" s="127"/>
       <c r="E28" s="13" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="29" spans="1:6">
-      <c r="A29" s="128"/>
+      <c r="A29" s="127"/>
       <c r="E29" s="11" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="30" spans="1:6">
-      <c r="A30" s="128"/>
+      <c r="A30" s="127"/>
       <c r="E30" s="13" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="129"/>
+      <c r="A31" s="128"/>
     </row>
     <row r="33" spans="1:7">
       <c r="B33" s="27" t="s">
@@ -14429,14 +14705,14 @@
       <c r="C33" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="D33" s="123" t="s">
+      <c r="D33" s="120" t="s">
         <v>189</v>
       </c>
-      <c r="E33" s="124"/>
-      <c r="F33" s="123" t="s">
+      <c r="E33" s="122"/>
+      <c r="F33" s="120" t="s">
         <v>178</v>
       </c>
-      <c r="G33" s="124"/>
+      <c r="G33" s="122"/>
     </row>
     <row r="34" spans="1:7">
       <c r="B34" s="26" t="s">
@@ -14555,11 +14831,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="A14:A31"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="B9:C9"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="G9:H9"/>
     <mergeCell ref="K9:L9"/>
@@ -14568,6 +14839,11 @@
     <mergeCell ref="E5:G5"/>
     <mergeCell ref="J5:K5"/>
     <mergeCell ref="H5:I5"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="A14:A31"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="B9:C9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14760,6 +15036,9 @@
       <c r="C14" t="s">
         <v>242</v>
       </c>
+      <c r="N14" t="s">
+        <v>397</v>
+      </c>
     </row>
     <row r="15" spans="1:25">
       <c r="C15" t="s">
@@ -14771,7 +15050,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="18" spans="2:3">
+    <row r="18" spans="2:5">
       <c r="B18">
         <v>4</v>
       </c>
@@ -14779,17 +15058,23 @@
         <v>240</v>
       </c>
     </row>
-    <row r="20" spans="2:3">
+    <row r="20" spans="2:5">
       <c r="B20" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="22" spans="2:3">
+    <row r="22" spans="2:5">
       <c r="B22" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="24" spans="2:3">
+      <c r="D22" t="s">
+        <v>395</v>
+      </c>
+      <c r="E22" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5">
       <c r="B24" s="57">
         <f>1920/3</f>
         <v>640</v>

--- a/Document/정책문서.xlsx
+++ b/Document/정책문서.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git_fork\ProjectShoot\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C4AC7E-1646-425A-AE69-53F5803E57B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55192451-B866-4347-88B1-C4C8DB65536B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="711" firstSheet="1" activeTab="6" xr2:uid="{F9E8F865-F741-4425-897D-555A2E4B3EBE}"/>
   </bookViews>
@@ -779,7 +779,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="425">
   <si>
     <t>설명</t>
   </si>
@@ -2508,6 +2508,38 @@
   </si>
   <si>
     <t xml:space="preserve">스테이트 머신 (후보) </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">있어도 없어도 되고 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>움직임 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">움직임 1 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>움직임 단일의 경우 루프</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>복수의 움직임의 경우 순서대로 루프</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>움직임에 조건 설정 할 수 있어야함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">움직임끼리의 순서 변경 가능 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>움직임 이름 수정 가능</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3322,7 +3354,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3683,15 +3715,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3700,6 +3723,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3710,7 +3745,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -10963,16 +10998,16 @@
       <c r="F4" s="113"/>
       <c r="G4" s="112"/>
       <c r="H4" s="111"/>
-      <c r="I4" s="123"/>
-      <c r="J4" s="124"/>
-      <c r="K4" s="124"/>
-      <c r="L4" s="124"/>
-      <c r="M4" s="124"/>
-      <c r="N4" s="124"/>
-      <c r="O4" s="124"/>
-      <c r="P4" s="124"/>
-      <c r="Q4" s="124"/>
-      <c r="R4" s="125"/>
+      <c r="I4" s="120"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="121"/>
+      <c r="L4" s="121"/>
+      <c r="M4" s="121"/>
+      <c r="N4" s="121"/>
+      <c r="O4" s="121"/>
+      <c r="P4" s="121"/>
+      <c r="Q4" s="121"/>
+      <c r="R4" s="122"/>
     </row>
     <row r="5" spans="1:18" ht="50.25" customHeight="1">
       <c r="A5" s="115">
@@ -10994,18 +11029,18 @@
         <v>393</v>
       </c>
       <c r="H5" s="111"/>
-      <c r="I5" s="123" t="s">
+      <c r="I5" s="120" t="s">
         <v>394</v>
       </c>
-      <c r="J5" s="124"/>
-      <c r="K5" s="124"/>
-      <c r="L5" s="124"/>
-      <c r="M5" s="124"/>
-      <c r="N5" s="124"/>
-      <c r="O5" s="124"/>
-      <c r="P5" s="124"/>
-      <c r="Q5" s="124"/>
-      <c r="R5" s="125"/>
+      <c r="J5" s="121"/>
+      <c r="K5" s="121"/>
+      <c r="L5" s="121"/>
+      <c r="M5" s="121"/>
+      <c r="N5" s="121"/>
+      <c r="O5" s="121"/>
+      <c r="P5" s="121"/>
+      <c r="Q5" s="121"/>
+      <c r="R5" s="122"/>
     </row>
     <row r="6" spans="1:18" ht="50.25" customHeight="1">
       <c r="A6" s="115">
@@ -11027,18 +11062,18 @@
         <v>391</v>
       </c>
       <c r="H6" s="111"/>
-      <c r="I6" s="123" t="s">
+      <c r="I6" s="120" t="s">
         <v>392</v>
       </c>
-      <c r="J6" s="124"/>
-      <c r="K6" s="124"/>
-      <c r="L6" s="124"/>
-      <c r="M6" s="124"/>
-      <c r="N6" s="124"/>
-      <c r="O6" s="124"/>
-      <c r="P6" s="124"/>
-      <c r="Q6" s="124"/>
-      <c r="R6" s="125"/>
+      <c r="J6" s="121"/>
+      <c r="K6" s="121"/>
+      <c r="L6" s="121"/>
+      <c r="M6" s="121"/>
+      <c r="N6" s="121"/>
+      <c r="O6" s="121"/>
+      <c r="P6" s="121"/>
+      <c r="Q6" s="121"/>
+      <c r="R6" s="122"/>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="115">
@@ -11060,18 +11095,18 @@
         <v>387</v>
       </c>
       <c r="H7" s="111"/>
-      <c r="I7" s="123" t="s">
+      <c r="I7" s="120" t="s">
         <v>389</v>
       </c>
-      <c r="J7" s="124"/>
-      <c r="K7" s="124"/>
-      <c r="L7" s="124"/>
-      <c r="M7" s="124"/>
-      <c r="N7" s="124"/>
-      <c r="O7" s="124"/>
-      <c r="P7" s="124"/>
-      <c r="Q7" s="124"/>
-      <c r="R7" s="125"/>
+      <c r="J7" s="121"/>
+      <c r="K7" s="121"/>
+      <c r="L7" s="121"/>
+      <c r="M7" s="121"/>
+      <c r="N7" s="121"/>
+      <c r="O7" s="121"/>
+      <c r="P7" s="121"/>
+      <c r="Q7" s="121"/>
+      <c r="R7" s="122"/>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="115">
@@ -11085,16 +11120,16 @@
       <c r="F8" s="113"/>
       <c r="G8" s="112"/>
       <c r="H8" s="111"/>
-      <c r="I8" s="123"/>
-      <c r="J8" s="124"/>
-      <c r="K8" s="124"/>
-      <c r="L8" s="124"/>
-      <c r="M8" s="124"/>
-      <c r="N8" s="124"/>
-      <c r="O8" s="124"/>
-      <c r="P8" s="124"/>
-      <c r="Q8" s="124"/>
-      <c r="R8" s="125"/>
+      <c r="I8" s="120"/>
+      <c r="J8" s="121"/>
+      <c r="K8" s="121"/>
+      <c r="L8" s="121"/>
+      <c r="M8" s="121"/>
+      <c r="N8" s="121"/>
+      <c r="O8" s="121"/>
+      <c r="P8" s="121"/>
+      <c r="Q8" s="121"/>
+      <c r="R8" s="122"/>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="115">
@@ -11108,16 +11143,16 @@
       <c r="F9" s="113"/>
       <c r="G9" s="112"/>
       <c r="H9" s="111"/>
-      <c r="I9" s="123"/>
-      <c r="J9" s="124"/>
-      <c r="K9" s="124"/>
-      <c r="L9" s="124"/>
-      <c r="M9" s="124"/>
-      <c r="N9" s="124"/>
-      <c r="O9" s="124"/>
-      <c r="P9" s="124"/>
-      <c r="Q9" s="124"/>
-      <c r="R9" s="125"/>
+      <c r="I9" s="120"/>
+      <c r="J9" s="121"/>
+      <c r="K9" s="121"/>
+      <c r="L9" s="121"/>
+      <c r="M9" s="121"/>
+      <c r="N9" s="121"/>
+      <c r="O9" s="121"/>
+      <c r="P9" s="121"/>
+      <c r="Q9" s="121"/>
+      <c r="R9" s="122"/>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="115">
@@ -11131,16 +11166,16 @@
       <c r="F10" s="113"/>
       <c r="G10" s="112"/>
       <c r="H10" s="111"/>
-      <c r="I10" s="123"/>
-      <c r="J10" s="124"/>
-      <c r="K10" s="124"/>
-      <c r="L10" s="124"/>
-      <c r="M10" s="124"/>
-      <c r="N10" s="124"/>
-      <c r="O10" s="124"/>
-      <c r="P10" s="124"/>
-      <c r="Q10" s="124"/>
-      <c r="R10" s="125"/>
+      <c r="I10" s="120"/>
+      <c r="J10" s="121"/>
+      <c r="K10" s="121"/>
+      <c r="L10" s="121"/>
+      <c r="M10" s="121"/>
+      <c r="N10" s="121"/>
+      <c r="O10" s="121"/>
+      <c r="P10" s="121"/>
+      <c r="Q10" s="121"/>
+      <c r="R10" s="122"/>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="115">
@@ -11154,16 +11189,16 @@
       <c r="F11" s="113"/>
       <c r="G11" s="112"/>
       <c r="H11" s="111"/>
-      <c r="I11" s="123"/>
-      <c r="J11" s="124"/>
-      <c r="K11" s="124"/>
-      <c r="L11" s="124"/>
-      <c r="M11" s="124"/>
-      <c r="N11" s="124"/>
-      <c r="O11" s="124"/>
-      <c r="P11" s="124"/>
-      <c r="Q11" s="124"/>
-      <c r="R11" s="125"/>
+      <c r="I11" s="120"/>
+      <c r="J11" s="121"/>
+      <c r="K11" s="121"/>
+      <c r="L11" s="121"/>
+      <c r="M11" s="121"/>
+      <c r="N11" s="121"/>
+      <c r="O11" s="121"/>
+      <c r="P11" s="121"/>
+      <c r="Q11" s="121"/>
+      <c r="R11" s="122"/>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="115">
@@ -11177,16 +11212,16 @@
       <c r="F12" s="113"/>
       <c r="G12" s="112"/>
       <c r="H12" s="111"/>
-      <c r="I12" s="123"/>
-      <c r="J12" s="124"/>
-      <c r="K12" s="124"/>
-      <c r="L12" s="124"/>
-      <c r="M12" s="124"/>
-      <c r="N12" s="124"/>
-      <c r="O12" s="124"/>
-      <c r="P12" s="124"/>
-      <c r="Q12" s="124"/>
-      <c r="R12" s="125"/>
+      <c r="I12" s="120"/>
+      <c r="J12" s="121"/>
+      <c r="K12" s="121"/>
+      <c r="L12" s="121"/>
+      <c r="M12" s="121"/>
+      <c r="N12" s="121"/>
+      <c r="O12" s="121"/>
+      <c r="P12" s="121"/>
+      <c r="Q12" s="121"/>
+      <c r="R12" s="122"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -13944,6 +13979,70 @@
       <c r="X34" s="62"/>
       <c r="Y34" s="63"/>
     </row>
+    <row r="36" spans="2:25">
+      <c r="B36" t="s">
+        <v>84</v>
+      </c>
+      <c r="D36" s="130" t="s">
+        <v>419</v>
+      </c>
+      <c r="E36" s="130"/>
+      <c r="H36" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25">
+      <c r="D37" t="s">
+        <v>401</v>
+      </c>
+      <c r="E37" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="38" spans="2:25">
+      <c r="D38" t="s">
+        <v>181</v>
+      </c>
+      <c r="E38" t="s">
+        <v>417</v>
+      </c>
+      <c r="H38" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="40" spans="2:25">
+      <c r="D40" s="130" t="s">
+        <v>418</v>
+      </c>
+      <c r="E40" s="130"/>
+      <c r="H40" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="41" spans="2:25">
+      <c r="D41" t="s">
+        <v>401</v>
+      </c>
+      <c r="E41" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25">
+      <c r="D42" t="s">
+        <v>181</v>
+      </c>
+      <c r="E42" t="s">
+        <v>417</v>
+      </c>
+      <c r="H42" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25">
+      <c r="H44" t="s">
+        <v>424</v>
+      </c>
+    </row>
     <row r="48" spans="2:25">
       <c r="B48" s="8" t="s">
         <v>282</v>
@@ -14359,6 +14458,10 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D40:E40"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -14398,24 +14501,24 @@
       <c r="C3" s="33"/>
     </row>
     <row r="5" spans="1:12">
-      <c r="B5" s="129" t="s">
+      <c r="B5" s="126" t="s">
         <v>129</v>
       </c>
-      <c r="C5" s="129"/>
-      <c r="D5" s="120"/>
-      <c r="E5" s="120" t="s">
+      <c r="C5" s="126"/>
+      <c r="D5" s="123"/>
+      <c r="E5" s="123" t="s">
         <v>126</v>
       </c>
-      <c r="F5" s="121"/>
-      <c r="G5" s="122"/>
-      <c r="H5" s="120" t="s">
+      <c r="F5" s="125"/>
+      <c r="G5" s="124"/>
+      <c r="H5" s="123" t="s">
         <v>136</v>
       </c>
-      <c r="I5" s="122"/>
-      <c r="J5" s="120" t="s">
+      <c r="I5" s="124"/>
+      <c r="J5" s="123" t="s">
         <v>141</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="124"/>
     </row>
     <row r="6" spans="1:12">
       <c r="B6" s="25" t="s">
@@ -14485,27 +14588,27 @@
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="B9" s="120" t="s">
+      <c r="B9" s="123" t="s">
         <v>151</v>
       </c>
-      <c r="C9" s="122"/>
-      <c r="D9" s="120" t="s">
+      <c r="C9" s="124"/>
+      <c r="D9" s="123" t="s">
         <v>153</v>
       </c>
-      <c r="E9" s="121"/>
-      <c r="F9" s="122"/>
-      <c r="G9" s="120" t="s">
+      <c r="E9" s="125"/>
+      <c r="F9" s="124"/>
+      <c r="G9" s="123" t="s">
         <v>136</v>
       </c>
-      <c r="H9" s="122"/>
-      <c r="I9" s="120" t="s">
+      <c r="H9" s="124"/>
+      <c r="I9" s="123" t="s">
         <v>141</v>
       </c>
-      <c r="J9" s="122"/>
-      <c r="K9" s="120" t="s">
+      <c r="J9" s="124"/>
+      <c r="K9" s="123" t="s">
         <v>178</v>
       </c>
-      <c r="L9" s="122"/>
+      <c r="L9" s="124"/>
     </row>
     <row r="10" spans="1:12">
       <c r="B10" s="25" t="s">
@@ -14581,7 +14684,7 @@
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="126" t="s">
+      <c r="A14" s="127" t="s">
         <v>155</v>
       </c>
       <c r="D14" s="27" t="s">
@@ -14590,14 +14693,14 @@
       <c r="E14" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="F14" s="129" t="s">
+      <c r="F14" s="126" t="s">
         <v>165</v>
       </c>
-      <c r="G14" s="129"/>
-      <c r="H14" s="129"/>
+      <c r="G14" s="126"/>
+      <c r="H14" s="126"/>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="127"/>
+      <c r="A15" s="128"/>
       <c r="D15" s="34" t="s">
         <v>157</v>
       </c>
@@ -14609,7 +14712,7 @@
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="127"/>
+      <c r="A16" s="128"/>
       <c r="D16" s="35" t="s">
         <v>158</v>
       </c>
@@ -14618,7 +14721,7 @@
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="127"/>
+      <c r="A17" s="128"/>
       <c r="D17" s="23" t="s">
         <v>159</v>
       </c>
@@ -14630,73 +14733,73 @@
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="127"/>
+      <c r="A18" s="128"/>
       <c r="D18" s="13" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="127"/>
+      <c r="A19" s="128"/>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="127"/>
+      <c r="A20" s="128"/>
       <c r="E20" s="36" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="127"/>
+      <c r="A21" s="128"/>
       <c r="E21" s="13" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="127"/>
+      <c r="A22" s="128"/>
       <c r="E22" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="127"/>
+      <c r="A23" s="128"/>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="127"/>
+      <c r="A24" s="128"/>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="127"/>
+      <c r="A25" s="128"/>
       <c r="E25" s="11" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="127"/>
+      <c r="A26" s="128"/>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="127"/>
+      <c r="A27" s="128"/>
       <c r="E27" s="13" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="127"/>
+      <c r="A28" s="128"/>
       <c r="E28" s="13" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="29" spans="1:6">
-      <c r="A29" s="127"/>
+      <c r="A29" s="128"/>
       <c r="E29" s="11" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="30" spans="1:6">
-      <c r="A30" s="127"/>
+      <c r="A30" s="128"/>
       <c r="E30" s="13" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="128"/>
+      <c r="A31" s="129"/>
     </row>
     <row r="33" spans="1:7">
       <c r="B33" s="27" t="s">
@@ -14705,14 +14808,14 @@
       <c r="C33" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="D33" s="120" t="s">
+      <c r="D33" s="123" t="s">
         <v>189</v>
       </c>
-      <c r="E33" s="122"/>
-      <c r="F33" s="120" t="s">
+      <c r="E33" s="124"/>
+      <c r="F33" s="123" t="s">
         <v>178</v>
       </c>
-      <c r="G33" s="122"/>
+      <c r="G33" s="124"/>
     </row>
     <row r="34" spans="1:7">
       <c r="B34" s="26" t="s">
@@ -14831,6 +14934,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="A14:A31"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="G9:H9"/>
     <mergeCell ref="K9:L9"/>
@@ -14839,11 +14947,6 @@
     <mergeCell ref="E5:G5"/>
     <mergeCell ref="J5:K5"/>
     <mergeCell ref="H5:I5"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="A14:A31"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="B9:C9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Document/정책문서.xlsx
+++ b/Document/정책문서.xlsx
@@ -1,28 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git_fork\ProjectShoot\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55192451-B866-4347-88B1-C4C8DB65536B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F107948-6E3A-4B78-AFF4-38BBC3A66C9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="711" firstSheet="1" activeTab="6" xr2:uid="{F9E8F865-F741-4425-897D-555A2E4B3EBE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="711" firstSheet="1" activeTab="4" xr2:uid="{F9E8F865-F741-4425-897D-555A2E4B3EBE}"/>
   </bookViews>
   <sheets>
     <sheet name="깃포크 공부" sheetId="11" state="hidden" r:id="rId1"/>
     <sheet name="History" sheetId="19" r:id="rId2"/>
     <sheet name="player" sheetId="3" r:id="rId3"/>
     <sheet name="enemy" sheetId="6" r:id="rId4"/>
-    <sheet name="Spawn" sheetId="18" r:id="rId5"/>
-    <sheet name="Formation" sheetId="16" r:id="rId6"/>
-    <sheet name="Move_Pattern" sheetId="17" r:id="rId7"/>
-    <sheet name="생애주기" sheetId="13" r:id="rId8"/>
-    <sheet name="카메라 " sheetId="15" r:id="rId9"/>
-    <sheet name="개발요청" sheetId="12" r:id="rId10"/>
+    <sheet name="skill" sheetId="20" r:id="rId5"/>
+    <sheet name="Spawn" sheetId="18" r:id="rId6"/>
+    <sheet name="Formation" sheetId="16" r:id="rId7"/>
+    <sheet name="Move_Pattern" sheetId="17" r:id="rId8"/>
+    <sheet name="생애주기" sheetId="13" r:id="rId9"/>
+    <sheet name="카메라 " sheetId="15" r:id="rId10"/>
+    <sheet name="개발요청" sheetId="12" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -779,7 +780,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="443">
   <si>
     <t>설명</t>
   </si>
@@ -962,10 +963,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>이 게임의 적의 경우 세가지 종류로 나뉩니다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>보스</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -987,10 +984,6 @@
   </si>
   <si>
     <t>일반적인 적입니다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">일정 시간이 되었을때 등장합니다. 플레이에 목표역할을 합니다. </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2540,6 +2533,84 @@
   </si>
   <si>
     <t>움직임 이름 수정 가능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 게임의 적의 경우 두가지 종류로 나뉩니다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정 시간이 되었을때 등장. 별도의 페이즈가 있음. 등장 시 주변 모든 몬스터 사망</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 (총기)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">정의 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">일반적인 슈팅게임에서의 총알,총기를 지칭 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 속성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">스킬의 이름 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">fire type </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">총알이 발사되는 형태 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>국문</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영문</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TARGET_PLAYER</t>
+  </si>
+  <si>
+    <t>직선</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조준</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TARGET_DOWN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부채꼴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FAN_SHAPE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CIRCLE_360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">원형 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3724,16 +3795,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3745,7 +3813,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5343,195 +5414,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>247650</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="47" name="사각형: 둥근 모서리 46">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FBD3319-F128-A6A6-552E-F848EA4DDDDD}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9525000" y="5181600"/>
-          <a:ext cx="914400" cy="133350"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="92D050"/>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>314325</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="48" name="사각형: 둥근 모서리 47">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{84720FD6-8B0B-595A-A850-6266F974842E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="13706475" y="5219700"/>
-          <a:ext cx="914400" cy="133350"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="92D050"/>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>581025</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="49" name="사각형: 둥근 모서리 48">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1A3A191-27A2-A82B-2284-9C204F762886}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14201775" y="3800475"/>
-          <a:ext cx="914400" cy="133350"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="92D050"/>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>20</xdr:col>
       <xdr:colOff>257175</xdr:colOff>
       <xdr:row>18</xdr:row>
@@ -5734,7 +5616,7 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>333375</xdr:rowOff>
     </xdr:from>
@@ -5757,8 +5639,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10801350" y="666750"/>
-          <a:ext cx="3400425" cy="5391150"/>
+          <a:off x="9629775" y="666750"/>
+          <a:ext cx="3438525" cy="5391150"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6328,51 +6210,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>352424</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>114299</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="그림 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A68EF345-6732-477C-8B5D-2D650E6B4BDC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:srcRect l="50648" t="67693" r="43829" b="15960"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="15125699" y="4743450"/>
-          <a:ext cx="447675" cy="742950"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>371476</xdr:colOff>
       <xdr:row>5</xdr:row>
@@ -6617,16 +6454,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>504824</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>304799</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>266699</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>66674</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6650,7 +6487,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15963899" y="4219575"/>
+          <a:off x="15078074" y="4552950"/>
           <a:ext cx="447675" cy="742950"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6664,6 +6501,79 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="직사각형 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60AE4B92-7203-CB77-0221-D1D53E724C14}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="809625" y="3381375"/>
+          <a:ext cx="2895600" cy="571500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            <a:t>혜인님</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0"/>
+            <a:t> 총기작업한거 보면서 더 쓰기 </a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -6795,12 +6705,12 @@
           </a:fontRef>
         </xdr:style>
         <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr"/>
             <a:r>
-              <a:rPr lang="ko-KR" altLang="en-US" sz="1050">
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1000">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -6808,7 +6718,7 @@
               <a:t>그룹</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" altLang="ko-KR" sz="1050">
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1000">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -6816,7 +6726,7 @@
               <a:t>1</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -6824,7 +6734,7 @@
               <a:t> </a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="ko-KR" altLang="en-US" sz="1050" baseline="0">
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -6832,7 +6742,7 @@
               <a:t>영역</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -6985,12 +6895,12 @@
           </a:fontRef>
         </xdr:style>
         <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr"/>
             <a:r>
-              <a:rPr lang="ko-KR" altLang="en-US" sz="1050">
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1000">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -6998,7 +6908,7 @@
               <a:t>그룹</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" altLang="ko-KR" sz="1050">
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1000">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -7006,7 +6916,7 @@
               <a:t>1</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -7014,7 +6924,7 @@
               <a:t> </a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="ko-KR" altLang="en-US" sz="1050" baseline="0">
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -7022,7 +6932,7 @@
               <a:t>영역</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -7072,12 +6982,12 @@
           </a:fontRef>
         </xdr:style>
         <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr"/>
             <a:r>
-              <a:rPr lang="ko-KR" altLang="en-US" sz="1050">
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1000">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -7085,7 +6995,7 @@
               <a:t>그룹</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" altLang="ko-KR" sz="1050">
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1000">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -7093,7 +7003,7 @@
               <a:t>1</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -7101,7 +7011,7 @@
               <a:t> </a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="ko-KR" altLang="en-US" sz="1050" baseline="0">
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -7109,7 +7019,7 @@
               <a:t>영역</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -7162,12 +7072,12 @@
           </a:fontRef>
         </xdr:style>
         <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr"/>
             <a:r>
-              <a:rPr lang="ko-KR" altLang="en-US" sz="1050">
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1000">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -7175,7 +7085,7 @@
               <a:t>그룹</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" altLang="ko-KR" sz="1050">
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1000">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -7183,7 +7093,7 @@
               <a:t>2</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -7191,7 +7101,7 @@
               <a:t> </a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="ko-KR" altLang="en-US" sz="1050" baseline="0">
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -7199,7 +7109,7 @@
               <a:t>영역</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -7252,12 +7162,12 @@
           </a:fontRef>
         </xdr:style>
         <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr"/>
             <a:r>
-              <a:rPr lang="ko-KR" altLang="en-US" sz="1050">
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1000">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -7265,7 +7175,7 @@
               <a:t>그룹</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" altLang="ko-KR" sz="1050">
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1000">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -7273,7 +7183,7 @@
               <a:t>2</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -7281,7 +7191,7 @@
               <a:t> </a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="ko-KR" altLang="en-US" sz="1050" baseline="0">
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -7289,7 +7199,7 @@
               <a:t>영역</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -7342,12 +7252,12 @@
           </a:fontRef>
         </xdr:style>
         <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr"/>
             <a:r>
-              <a:rPr lang="ko-KR" altLang="en-US" sz="1050">
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1000">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -7355,7 +7265,7 @@
               <a:t>그룹</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" altLang="ko-KR" sz="1050">
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1000">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -7363,7 +7273,7 @@
               <a:t>2</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -7371,7 +7281,7 @@
               <a:t> </a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="ko-KR" altLang="en-US" sz="1050" baseline="0">
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -7379,7 +7289,7 @@
               <a:t>영역</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -7516,12 +7426,12 @@
           </a:fontRef>
         </xdr:style>
         <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr"/>
             <a:r>
-              <a:rPr lang="ko-KR" altLang="en-US" sz="1050">
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1000">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -7529,7 +7439,7 @@
               <a:t>그룹</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" altLang="ko-KR" sz="1050">
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1000">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -7537,7 +7447,7 @@
               <a:t>1</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -7545,7 +7455,7 @@
               <a:t> </a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="ko-KR" altLang="en-US" sz="1050" baseline="0">
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -7553,7 +7463,7 @@
               <a:t>영역</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" altLang="ko-KR" sz="1050" baseline="0">
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -7768,7 +7678,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -8156,7 +8066,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -8591,7 +8501,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9972675" y="3343275"/>
+          <a:off x="14773275" y="3943350"/>
           <a:ext cx="736146" cy="314325"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -8735,7 +8645,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13201650" y="4095750"/>
+          <a:off x="15259050" y="4695825"/>
           <a:ext cx="2343150" cy="1028700"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartTerminator">
@@ -8899,7 +8809,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -9710,7 +9620,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -10601,7 +10511,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="38.25">
       <c r="A1" s="21" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -10609,26 +10519,26 @@
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="O3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="P3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="H4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="P4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="P5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -10636,7 +10546,7 @@
         <v>2</v>
       </c>
       <c r="G28" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -10647,6 +10557,244 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{511B7746-4A5E-454B-8602-7B4B353E7BEF}">
+  <dimension ref="A1:Y24"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="4.625" customWidth="1"/>
+    <col min="2" max="2" width="8.5" customWidth="1"/>
+    <col min="3" max="3" width="5.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25" ht="26.25">
+      <c r="A1" s="39" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25">
+      <c r="B3" t="s">
+        <v>199</v>
+      </c>
+      <c r="N3" s="40" t="s">
+        <v>243</v>
+      </c>
+      <c r="O3" s="40"/>
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="40"/>
+      <c r="S3" s="40"/>
+      <c r="T3" s="40"/>
+      <c r="U3" s="40"/>
+      <c r="V3" s="40"/>
+      <c r="W3" s="40"/>
+    </row>
+    <row r="4" spans="1:25">
+      <c r="B4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C4" t="s">
+        <v>231</v>
+      </c>
+      <c r="N4" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="O4" s="40"/>
+      <c r="P4" s="40"/>
+      <c r="Q4" s="40"/>
+      <c r="R4" s="40"/>
+      <c r="S4" s="40"/>
+      <c r="T4" s="40"/>
+      <c r="U4" s="40"/>
+      <c r="V4" s="40"/>
+      <c r="W4" s="40"/>
+    </row>
+    <row r="5" spans="1:25">
+      <c r="B5" t="s">
+        <v>201</v>
+      </c>
+      <c r="C5" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" ht="21.75">
+      <c r="B6" t="s">
+        <v>202</v>
+      </c>
+      <c r="C6" t="s">
+        <v>248</v>
+      </c>
+      <c r="N6" s="42" t="s">
+        <v>235</v>
+      </c>
+      <c r="O6" s="43"/>
+      <c r="P6" s="43"/>
+      <c r="Q6" s="43"/>
+      <c r="R6" s="43"/>
+      <c r="S6" s="43"/>
+      <c r="T6" s="43"/>
+      <c r="U6" s="43"/>
+      <c r="V6" s="43"/>
+      <c r="W6" s="43"/>
+      <c r="X6" s="43"/>
+      <c r="Y6" s="43"/>
+    </row>
+    <row r="7" spans="1:25">
+      <c r="N7" s="43"/>
+      <c r="O7" s="43"/>
+      <c r="P7" s="43"/>
+      <c r="Q7" s="43"/>
+      <c r="R7" s="43"/>
+      <c r="S7" s="43"/>
+      <c r="T7" s="43"/>
+      <c r="U7" s="43"/>
+      <c r="V7" s="43"/>
+      <c r="W7" s="43"/>
+      <c r="X7" s="43"/>
+      <c r="Y7" s="43"/>
+    </row>
+    <row r="8" spans="1:25">
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>239</v>
+      </c>
+      <c r="N8" s="43" t="s">
+        <v>236</v>
+      </c>
+      <c r="O8" s="43"/>
+      <c r="P8" s="43"/>
+      <c r="Q8" s="43"/>
+      <c r="R8" s="43"/>
+      <c r="S8" s="43"/>
+      <c r="T8" s="43"/>
+      <c r="U8" s="43"/>
+      <c r="V8" s="43"/>
+      <c r="W8" s="43"/>
+      <c r="X8" s="43"/>
+      <c r="Y8" s="43"/>
+    </row>
+    <row r="9" spans="1:25">
+      <c r="C9" t="s">
+        <v>232</v>
+      </c>
+      <c r="N9" s="44"/>
+      <c r="O9" s="43"/>
+      <c r="P9" s="43"/>
+      <c r="Q9" s="43"/>
+      <c r="R9" s="43"/>
+      <c r="S9" s="43"/>
+      <c r="T9" s="43"/>
+      <c r="U9" s="43"/>
+      <c r="V9" s="43"/>
+      <c r="W9" s="43"/>
+      <c r="X9" s="43"/>
+      <c r="Y9" s="43"/>
+    </row>
+    <row r="10" spans="1:25">
+      <c r="N10" s="45" t="s">
+        <v>246</v>
+      </c>
+      <c r="O10" s="43"/>
+      <c r="P10" s="43"/>
+      <c r="Q10" s="43"/>
+      <c r="R10" s="43"/>
+      <c r="S10" s="43"/>
+      <c r="T10" s="43"/>
+      <c r="U10" s="43"/>
+      <c r="V10" s="43"/>
+      <c r="W10" s="43"/>
+      <c r="X10" s="43"/>
+      <c r="Y10" s="43"/>
+    </row>
+    <row r="11" spans="1:25">
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11" t="s">
+        <v>237</v>
+      </c>
+      <c r="N11" s="45" t="s">
+        <v>247</v>
+      </c>
+      <c r="O11" s="43"/>
+      <c r="P11" s="43"/>
+      <c r="Q11" s="43"/>
+      <c r="R11" s="43"/>
+      <c r="S11" s="43"/>
+      <c r="T11" s="43"/>
+      <c r="U11" s="43"/>
+      <c r="V11" s="43"/>
+      <c r="W11" s="43"/>
+      <c r="X11" s="43"/>
+      <c r="Y11" s="43"/>
+    </row>
+    <row r="12" spans="1:25">
+      <c r="C12" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25">
+      <c r="B14">
+        <v>3</v>
+      </c>
+      <c r="C14" t="s">
+        <v>240</v>
+      </c>
+      <c r="N14" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25">
+      <c r="C15" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25">
+      <c r="C16" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5">
+      <c r="B18">
+        <v>4</v>
+      </c>
+      <c r="C18" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5">
+      <c r="B20" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5">
+      <c r="B22" t="s">
+        <v>318</v>
+      </c>
+      <c r="D22" t="s">
+        <v>393</v>
+      </c>
+      <c r="E22" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5">
+      <c r="B24" s="57">
+        <f>1920/3</f>
+        <v>640</v>
+      </c>
+      <c r="C24" t="s">
+        <v>317</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FEA1851-41A0-400A-9D42-CA24EB0A5B33}">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
@@ -10669,11 +10817,11 @@
         <v>7</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D2" s="16"/>
       <c r="H2" s="16" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="2:19">
@@ -10681,34 +10829,34 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F3" t="s">
         <v>83</v>
       </c>
-      <c r="F3" t="s">
-        <v>85</v>
-      </c>
       <c r="H3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="2:19">
       <c r="E4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F4" t="s">
         <v>84</v>
-      </c>
-      <c r="F4" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="5" spans="2:19">
       <c r="E5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="2:19">
       <c r="E6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8" spans="2:19">
@@ -10716,13 +10864,13 @@
         <v>2</v>
       </c>
       <c r="C8" t="s">
+        <v>85</v>
+      </c>
+      <c r="E8" s="37" t="s">
+        <v>205</v>
+      </c>
+      <c r="H8" t="s">
         <v>87</v>
-      </c>
-      <c r="E8" s="37" t="s">
-        <v>207</v>
-      </c>
-      <c r="H8" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="10" spans="2:19">
@@ -10730,13 +10878,13 @@
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H10" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="2:19">
@@ -10744,27 +10892,27 @@
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E12" t="s">
+        <v>91</v>
+      </c>
+      <c r="H12" t="s">
         <v>93</v>
       </c>
-      <c r="H12" t="s">
-        <v>95</v>
-      </c>
       <c r="J12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="2:19">
       <c r="C13" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E13" s="37" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="J13" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="2:19">
@@ -10772,13 +10920,13 @@
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="S15" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="2:19">
@@ -10789,18 +10937,18 @@
         <v>5.25</v>
       </c>
       <c r="C17" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H17" t="s">
+        <v>118</v>
+      </c>
+      <c r="S17" t="s">
         <v>120</v>
-      </c>
-      <c r="S17" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="18" spans="2:19">
       <c r="S18" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" spans="2:19">
@@ -10808,31 +10956,31 @@
         <v>5.5</v>
       </c>
       <c r="C19" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E19" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="2:19">
       <c r="E20" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="S20" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="2:19">
       <c r="D22" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" spans="2:19">
       <c r="D24" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" spans="2:19">
@@ -10840,60 +10988,60 @@
         <v>6</v>
       </c>
       <c r="C26" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="2:19">
       <c r="C27" t="s">
+        <v>96</v>
+      </c>
+      <c r="D27" t="s">
+        <v>97</v>
+      </c>
+      <c r="E27" t="s">
         <v>98</v>
-      </c>
-      <c r="D27" t="s">
-        <v>99</v>
-      </c>
-      <c r="E27" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="29" spans="2:19">
       <c r="C29" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D29" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="2:19">
       <c r="D30" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32" spans="2:19">
       <c r="C32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D32" t="s">
         <v>103</v>
-      </c>
-      <c r="D32" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="C34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D34" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="C36" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D36" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="D37" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="39" spans="2:4">
@@ -10901,7 +11049,7 @@
         <v>7</v>
       </c>
       <c r="C39" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="41" spans="2:4">
@@ -10909,10 +11057,10 @@
         <v>8</v>
       </c>
       <c r="C41" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D41" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="43" spans="2:4">
@@ -10920,7 +11068,7 @@
         <v>9</v>
       </c>
       <c r="C43" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="45" spans="2:4">
@@ -10928,12 +11076,12 @@
         <v>10</v>
       </c>
       <c r="C45" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="47" spans="2:4">
       <c r="C47" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -10954,30 +11102,30 @@
   <sheetData>
     <row r="1" spans="1:18" ht="33.75">
       <c r="A1" s="117" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="27" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B3" s="50" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C3" s="51"/>
       <c r="D3" s="19" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E3" s="52" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F3" s="52"/>
       <c r="G3" s="50" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="H3" s="51"/>
       <c r="I3" s="52" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J3" s="52"/>
       <c r="K3" s="52"/>
@@ -11019,18 +11167,18 @@
       </c>
       <c r="C5" s="113"/>
       <c r="D5" s="115" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E5" s="114" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="F5" s="113"/>
       <c r="G5" s="118" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H5" s="111"/>
       <c r="I5" s="120" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="J5" s="121"/>
       <c r="K5" s="121"/>
@@ -11052,18 +11200,18 @@
       </c>
       <c r="C6" s="113"/>
       <c r="D6" s="115" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E6" s="114" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="F6" s="113"/>
       <c r="G6" s="118" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H6" s="111"/>
       <c r="I6" s="120" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="J6" s="121"/>
       <c r="K6" s="121"/>
@@ -11085,18 +11233,18 @@
       </c>
       <c r="C7" s="113"/>
       <c r="D7" s="115" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E7" s="114" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F7" s="113"/>
       <c r="G7" s="112" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H7" s="111"/>
       <c r="I7" s="120" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J7" s="121"/>
       <c r="K7" s="121"/>
@@ -11258,12 +11406,12 @@
   <sheetData>
     <row r="1" spans="1:7" ht="26.25">
       <c r="A1" s="47" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="B3" s="8" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -11335,7 +11483,7 @@
         <v>14</v>
       </c>
       <c r="F7" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -11458,7 +11606,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E17" s="13"/>
     </row>
@@ -11767,10 +11915,10 @@
       <c r="D2" s="9"/>
       <c r="E2" s="12"/>
       <c r="K2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="27" thickBot="1">
@@ -11799,7 +11947,7 @@
     </row>
     <row r="5" spans="1:21">
       <c r="B5" t="s">
-        <v>47</v>
+        <v>423</v>
       </c>
       <c r="K5" s="3"/>
       <c r="O5" s="4"/>
@@ -11817,13 +11965,13 @@
         <v>7</v>
       </c>
       <c r="C7" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="E7" s="16" t="s">
         <v>50</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>51</v>
       </c>
       <c r="K7" s="3"/>
       <c r="O7" s="4"/>
@@ -11835,10 +11983,10 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" t="s">
         <v>52</v>
-      </c>
-      <c r="D8" t="s">
-        <v>53</v>
       </c>
       <c r="K8" s="3"/>
       <c r="O8" s="4"/>
@@ -11850,10 +11998,10 @@
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>54</v>
+        <v>424</v>
       </c>
       <c r="E9" s="17"/>
       <c r="K9" s="3"/>
@@ -11875,7 +12023,7 @@
     </row>
     <row r="12" spans="1:21">
       <c r="B12" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E12" s="11"/>
       <c r="K12" s="3"/>
@@ -11948,14 +12096,14 @@
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E16" s="13"/>
       <c r="F16" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="K16" s="3"/>
       <c r="O16" s="4"/>
@@ -11971,7 +12119,7 @@
         <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="K17" s="3"/>
       <c r="O17" s="4"/>
@@ -12000,7 +12148,7 @@
         <v>6</v>
       </c>
       <c r="C19" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E19" s="11" t="s">
         <v>29</v>
@@ -12018,7 +12166,7 @@
     </row>
     <row r="21" spans="2:21">
       <c r="B21" s="8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K21" s="3"/>
       <c r="O21" s="4"/>
@@ -12052,13 +12200,13 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D23" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F23" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="K23" s="3"/>
       <c r="O23" s="4"/>
@@ -12071,10 +12219,10 @@
         <v>2</v>
       </c>
       <c r="C24" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F24" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K24" s="3"/>
       <c r="O24" s="4"/>
@@ -12087,7 +12235,7 @@
         <v>3</v>
       </c>
       <c r="C25" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K25" s="3"/>
       <c r="O25" s="4"/>
@@ -12100,7 +12248,7 @@
         <v>4</v>
       </c>
       <c r="C26" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="K26" s="3"/>
       <c r="O26" s="4"/>
@@ -12113,7 +12261,7 @@
         <v>5</v>
       </c>
       <c r="C27" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K27" s="5"/>
       <c r="L27" s="6"/>
@@ -12128,7 +12276,7 @@
     </row>
     <row r="30" spans="2:21" ht="26.25">
       <c r="B30" s="39" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="31" spans="2:21">
@@ -12141,7 +12289,7 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="33" spans="2:3">
@@ -12149,7 +12297,7 @@
         <v>2</v>
       </c>
       <c r="C33" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="34" spans="2:3">
@@ -12157,7 +12305,7 @@
         <v>3</v>
       </c>
       <c r="C34" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="35" spans="2:3">
@@ -12165,7 +12313,7 @@
         <v>4</v>
       </c>
       <c r="C35" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -12176,6 +12324,114 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87B44DE2-AF19-4BD2-BC99-24E49A2EB044}">
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="4.125" customWidth="1"/>
+    <col min="2" max="2" width="4.25" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="26.25">
+      <c r="A1" s="47" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="B3" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="B4" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="B6" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="C7" t="s">
+        <v>429</v>
+      </c>
+      <c r="D7" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="C9" t="s">
+        <v>431</v>
+      </c>
+      <c r="D9" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="C11" t="s">
+        <v>384</v>
+      </c>
+      <c r="D11" t="s">
+        <v>433</v>
+      </c>
+      <c r="E11" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>437</v>
+      </c>
+      <c r="E12" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13" t="s">
+        <v>436</v>
+      </c>
+      <c r="E13" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="C14">
+        <v>3</v>
+      </c>
+      <c r="D14" t="s">
+        <v>439</v>
+      </c>
+      <c r="E14" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="C15">
+        <v>4</v>
+      </c>
+      <c r="D15" t="s">
+        <v>442</v>
+      </c>
+      <c r="E15" t="s">
+        <v>441</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5B6D67C-9882-4C75-80BA-1B180D5DF46B}">
   <dimension ref="A1:X55"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
@@ -12186,7 +12442,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="26.25">
       <c r="A1" s="47" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B1" s="8"/>
     </row>
@@ -12197,14 +12453,14 @@
     <row r="3" spans="1:17" ht="16.5" customHeight="1">
       <c r="A3" s="47"/>
       <c r="B3" s="8" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="16.5" customHeight="1">
       <c r="A4" s="47"/>
       <c r="B4" s="8"/>
       <c r="C4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="16.5" customHeight="1">
@@ -12213,13 +12469,13 @@
     </row>
     <row r="6" spans="1:17" ht="16.5" customHeight="1">
       <c r="B6" s="8" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="16.5" customHeight="1">
       <c r="B7" s="8"/>
       <c r="C7" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="16.5" customHeight="1">
@@ -12227,16 +12483,16 @@
     </row>
     <row r="9" spans="1:17" ht="16.5" customHeight="1">
       <c r="B9" s="8" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="16.5" customHeight="1">
       <c r="B10" s="8"/>
       <c r="C10" s="74" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="L10" s="50" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="M10" s="52"/>
       <c r="N10" s="52"/>
@@ -12247,7 +12503,7 @@
     <row r="11" spans="1:17" ht="16.5" customHeight="1">
       <c r="B11" s="8"/>
       <c r="D11" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="L11" s="64"/>
       <c r="M11" s="65"/>
@@ -12268,7 +12524,7 @@
     <row r="13" spans="1:17" ht="16.5" customHeight="1">
       <c r="B13" s="8"/>
       <c r="D13" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="L13" s="58"/>
       <c r="M13" s="59"/>
@@ -12280,7 +12536,7 @@
     <row r="14" spans="1:17" ht="16.5" customHeight="1">
       <c r="B14" s="8"/>
       <c r="D14" s="69" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="L14" s="58"/>
       <c r="M14" s="59"/>
@@ -12301,7 +12557,7 @@
     <row r="16" spans="1:17" ht="16.5" customHeight="1">
       <c r="B16" s="8"/>
       <c r="D16" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="L16" s="58"/>
       <c r="M16" s="59"/>
@@ -12313,7 +12569,7 @@
     <row r="17" spans="2:17" ht="16.5" customHeight="1">
       <c r="B17" s="8"/>
       <c r="D17" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="L17" s="58"/>
       <c r="M17" s="59"/>
@@ -12334,7 +12590,7 @@
     <row r="19" spans="2:17" ht="16.5" customHeight="1">
       <c r="B19" s="8"/>
       <c r="C19" s="74" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="L19" s="58"/>
       <c r="M19" s="59"/>
@@ -12346,7 +12602,7 @@
     <row r="20" spans="2:17" ht="16.5" customHeight="1">
       <c r="B20" s="8"/>
       <c r="D20" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="L20" s="58"/>
       <c r="M20" s="59"/>
@@ -12358,7 +12614,7 @@
     <row r="21" spans="2:17" ht="16.5" customHeight="1">
       <c r="B21" s="8"/>
       <c r="D21" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="L21" s="58"/>
       <c r="M21" s="59"/>
@@ -12379,7 +12635,7 @@
     <row r="23" spans="2:17" ht="16.5" customHeight="1">
       <c r="B23" s="8"/>
       <c r="D23" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="L23" s="58"/>
       <c r="M23" s="59"/>
@@ -12400,10 +12656,10 @@
     <row r="25" spans="2:17" ht="16.5" customHeight="1">
       <c r="B25" s="8"/>
       <c r="D25" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E25" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="L25" s="58"/>
       <c r="M25" s="59"/>
@@ -12415,10 +12671,10 @@
     <row r="26" spans="2:17" ht="16.5" customHeight="1">
       <c r="B26" s="8"/>
       <c r="D26" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E26" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="L26" s="58"/>
       <c r="M26" s="59"/>
@@ -12468,13 +12724,13 @@
     </row>
     <row r="34" spans="2:24">
       <c r="B34" s="8" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="35" spans="2:24">
       <c r="B35" s="8"/>
       <c r="C35" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="36" spans="2:24" ht="17.25" thickBot="1">
@@ -12483,138 +12739,138 @@
     <row r="37" spans="2:24">
       <c r="B37" s="8"/>
       <c r="D37" s="27" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E37" s="67" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F37" s="89"/>
       <c r="G37" s="52" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H37" s="52"/>
       <c r="I37" s="67" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="J37" s="89"/>
       <c r="K37" s="51" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="L37" s="51"/>
       <c r="M37" s="49" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="N37" s="51"/>
       <c r="O37" s="49" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="P37" s="51"/>
       <c r="Q37" s="49" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="R37" s="52"/>
       <c r="S37" s="75" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="T37" s="76"/>
       <c r="U37" s="75" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="V37" s="76"/>
       <c r="W37" s="75" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="X37" s="77"/>
     </row>
     <row r="38" spans="2:24">
       <c r="B38" s="8"/>
       <c r="D38" s="27" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E38" s="86" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F38" s="90"/>
       <c r="G38" s="52" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="H38" s="52"/>
       <c r="I38" s="86" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="J38" s="90"/>
       <c r="K38" s="51" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="L38" s="51"/>
       <c r="M38" s="49" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="N38" s="51"/>
       <c r="O38" s="49" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="P38" s="51"/>
       <c r="Q38" s="49" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="R38" s="52"/>
       <c r="S38" s="75" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="T38" s="76"/>
       <c r="U38" s="75" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="V38" s="76"/>
       <c r="W38" s="75" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="X38" s="77"/>
     </row>
     <row r="39" spans="2:24" ht="17.25" thickBot="1">
       <c r="B39" s="8"/>
       <c r="D39" s="27" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E39" s="68" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F39" s="91"/>
       <c r="G39" s="88" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H39" s="52"/>
       <c r="I39" s="68" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="J39" s="91"/>
       <c r="K39" s="51" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L39" s="51"/>
       <c r="M39" s="49" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="N39" s="51"/>
       <c r="O39" s="49" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="P39" s="51"/>
       <c r="Q39" s="49" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="R39" s="52"/>
       <c r="S39" s="78" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="T39" s="76"/>
       <c r="U39" s="78" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="V39" s="76"/>
       <c r="W39" s="78" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="X39" s="77"/>
     </row>
@@ -12629,15 +12885,15 @@
       </c>
       <c r="F40" s="70"/>
       <c r="G40" s="70" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="H40" s="70"/>
       <c r="I40" s="70" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="J40" s="70"/>
       <c r="K40" s="70" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L40" s="70"/>
       <c r="M40" s="70">
@@ -12653,7 +12909,7 @@
       </c>
       <c r="R40" s="70"/>
       <c r="S40" s="93" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="T40" s="93"/>
       <c r="U40" s="93">
@@ -12672,19 +12928,19 @@
         <v>2</v>
       </c>
       <c r="E41" s="70" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F41" s="70"/>
       <c r="G41" s="70" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="H41" s="70"/>
       <c r="I41" s="70" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="J41" s="70"/>
       <c r="K41" s="70" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="L41" s="70"/>
       <c r="M41" s="11"/>
@@ -12704,19 +12960,19 @@
         <v>3</v>
       </c>
       <c r="E42" s="70" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F42" s="70"/>
       <c r="G42" s="70" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="H42" s="70"/>
       <c r="I42" s="70" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="J42" s="70"/>
       <c r="K42" s="70" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="L42" s="70"/>
       <c r="M42" s="11"/>
@@ -12736,19 +12992,19 @@
         <v>4</v>
       </c>
       <c r="E43" s="55" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F43" s="55"/>
       <c r="G43" s="55" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="H43" s="55"/>
       <c r="I43" s="55" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="J43" s="55"/>
       <c r="K43" s="56" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="L43" s="56"/>
       <c r="M43" s="56"/>
@@ -12770,66 +13026,66 @@
     <row r="45" spans="2:24">
       <c r="B45" s="8"/>
       <c r="D45" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G45" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="46" spans="2:24">
       <c r="B46" s="8"/>
       <c r="D46" s="8" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="47" spans="2:24">
       <c r="B47" s="8"/>
       <c r="D47" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="G47" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="48" spans="2:24">
       <c r="B48" s="8"/>
       <c r="D48" s="8" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="49" spans="2:9">
       <c r="B49" s="8"/>
       <c r="D49" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G49" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="2:9">
       <c r="B50" s="8"/>
       <c r="D50" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G50" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="51" spans="2:9">
       <c r="B51" s="8"/>
       <c r="D51" s="18" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E51" s="18"/>
       <c r="F51" s="18"/>
       <c r="G51" s="18" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H51" s="18"/>
       <c r="I51" s="18"/>
@@ -12837,12 +13093,12 @@
     <row r="52" spans="2:9">
       <c r="B52" s="8"/>
       <c r="D52" s="18" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E52" s="18"/>
       <c r="F52" s="18"/>
       <c r="G52" s="18" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="H52" s="18"/>
       <c r="I52" s="18"/>
@@ -12850,32 +13106,32 @@
     <row r="53" spans="2:9">
       <c r="B53" s="8"/>
       <c r="D53" s="18" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E53" s="18"/>
       <c r="F53" s="18"/>
       <c r="G53" s="18" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="54" spans="2:9">
       <c r="D54" s="18" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E54" s="18"/>
       <c r="F54" s="18"/>
       <c r="G54" s="18" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="55" spans="2:9">
       <c r="D55" s="18" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E55" s="18"/>
       <c r="F55" s="18"/>
       <c r="G55" s="18" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -12885,7 +13141,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90669897-7B19-41C3-ACE9-893F9F9C4143}">
   <dimension ref="A1:X54"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
@@ -12900,7 +13156,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="26.25">
       <c r="A1" s="47" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1">
@@ -12909,19 +13165,19 @@
     <row r="3" spans="1:4" ht="15.75" customHeight="1">
       <c r="A3" s="47"/>
       <c r="B3" s="8" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1">
       <c r="A4" s="47"/>
       <c r="C4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1">
       <c r="A5" s="47"/>
       <c r="C5" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1">
@@ -12929,42 +13185,42 @@
     </row>
     <row r="7" spans="1:4">
       <c r="B7" s="8" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="C8" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="B10" s="8" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="C11" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="C13" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="D14" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="D15" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="17" spans="2:9">
       <c r="C17" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="18" spans="2:9">
@@ -13005,7 +13261,7 @@
     </row>
     <row r="22" spans="2:9">
       <c r="C22" s="18" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
@@ -13016,7 +13272,7 @@
     <row r="23" spans="2:9">
       <c r="C23" s="18"/>
       <c r="D23" s="18" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E23" s="8"/>
       <c r="F23" s="8"/>
@@ -13025,7 +13281,7 @@
     </row>
     <row r="25" spans="2:9">
       <c r="B25" s="8" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="26" spans="2:9">
@@ -13033,11 +13289,11 @@
         <v>7</v>
       </c>
       <c r="D26" s="48" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E26" s="48"/>
       <c r="F26" s="48" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="27" spans="2:9">
@@ -13046,10 +13302,10 @@
         <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F27" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="28" spans="2:9">
@@ -13058,10 +13314,10 @@
         <v>2</v>
       </c>
       <c r="D28" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F28" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="29" spans="2:9">
@@ -13070,10 +13326,10 @@
         <v>3</v>
       </c>
       <c r="D29" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F29" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="30" spans="2:9">
@@ -13082,10 +13338,10 @@
         <v>4</v>
       </c>
       <c r="D30" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F30" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="31" spans="2:9">
@@ -13094,155 +13350,155 @@
         <v>5</v>
       </c>
       <c r="D31" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F31" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="33" spans="2:24">
       <c r="B33" s="8" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="34" spans="2:24">
       <c r="C34" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="35" spans="2:24" ht="17.25" thickBot="1"/>
     <row r="36" spans="2:24">
       <c r="D36" s="79" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E36" s="75" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F36" s="76"/>
       <c r="G36" s="75" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H36" s="76"/>
       <c r="I36" s="85" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="J36" s="85"/>
       <c r="K36" s="67" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="L36" s="73"/>
       <c r="M36" s="73" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="N36" s="73"/>
       <c r="O36" s="73" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="P36" s="73"/>
       <c r="Q36" s="73" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="R36" s="89"/>
       <c r="S36" s="75" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="T36" s="76"/>
       <c r="U36" s="75" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="V36" s="76"/>
       <c r="W36" s="75" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="X36" s="77"/>
     </row>
     <row r="37" spans="2:24">
       <c r="D37" s="79" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E37" s="75" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F37" s="76"/>
       <c r="G37" s="75" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="H37" s="76"/>
       <c r="I37" s="85" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="J37" s="85"/>
       <c r="K37" s="86" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="L37" s="71"/>
       <c r="M37" s="71" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="N37" s="71"/>
       <c r="O37" s="71" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="P37" s="71"/>
       <c r="Q37" s="71" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="R37" s="90"/>
       <c r="S37" s="75" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="T37" s="76"/>
       <c r="U37" s="75" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="V37" s="76"/>
       <c r="W37" s="75" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="X37" s="77"/>
     </row>
     <row r="38" spans="2:24" ht="17.25" thickBot="1">
       <c r="D38" s="79" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E38" s="78" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F38" s="76"/>
       <c r="G38" s="78" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H38" s="76"/>
       <c r="I38" s="85" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="J38" s="85"/>
       <c r="K38" s="68" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L38" s="87"/>
       <c r="M38" s="87" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="N38" s="87"/>
       <c r="O38" s="87" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="P38" s="87"/>
       <c r="Q38" s="87" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="R38" s="91"/>
       <c r="S38" s="78" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="T38" s="76"/>
       <c r="U38" s="78" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="V38" s="76"/>
       <c r="W38" s="78" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="X38" s="77"/>
     </row>
@@ -13256,15 +13512,15 @@
       </c>
       <c r="F39" s="93"/>
       <c r="G39" s="93" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="H39" s="93"/>
       <c r="I39" s="93" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="J39" s="93"/>
       <c r="K39" s="93" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L39" s="93"/>
       <c r="M39" s="93">
@@ -13280,7 +13536,7 @@
       </c>
       <c r="R39" s="93"/>
       <c r="S39" s="93" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="T39" s="93"/>
       <c r="U39" s="93">
@@ -13298,19 +13554,19 @@
         <v>2</v>
       </c>
       <c r="E40" s="93" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F40" s="93"/>
       <c r="G40" s="93" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="H40" s="93"/>
       <c r="I40" s="93" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="J40" s="93"/>
       <c r="K40" s="93" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="L40" s="93"/>
       <c r="M40" s="94"/>
@@ -13332,19 +13588,19 @@
         <v>3</v>
       </c>
       <c r="E41" s="93" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F41" s="93"/>
       <c r="G41" s="93" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="H41" s="93"/>
       <c r="I41" s="93" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="J41" s="93"/>
       <c r="K41" s="93" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="L41" s="93"/>
       <c r="M41" s="94"/>
@@ -13366,19 +13622,19 @@
         <v>4</v>
       </c>
       <c r="E42" s="83" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F42" s="83"/>
       <c r="G42" s="83" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="H42" s="83"/>
       <c r="I42" s="83" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="J42" s="83"/>
       <c r="K42" s="84" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="L42" s="84"/>
       <c r="M42" s="84"/>
@@ -13396,71 +13652,71 @@
     </row>
     <row r="44" spans="2:24">
       <c r="D44" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G44" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="45" spans="2:24">
       <c r="D45" s="18" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="G45" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="46" spans="2:24">
       <c r="D46" s="18" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="G46" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="47" spans="2:24">
       <c r="D47" s="18" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G47" s="18" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="48" spans="2:24">
       <c r="D48" s="8" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="4:22">
       <c r="D49" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="50" spans="4:22">
       <c r="D50" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E50" s="18"/>
       <c r="F50" s="18"/>
       <c r="G50" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H50" s="18"/>
     </row>
     <row r="51" spans="4:22">
       <c r="D51" s="8" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E51" s="18"/>
       <c r="F51" s="18"/>
       <c r="G51" s="8" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="H51" s="18"/>
       <c r="Q51" s="18"/>
@@ -13472,32 +13728,32 @@
     </row>
     <row r="52" spans="4:22">
       <c r="D52" s="18" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E52" s="18"/>
       <c r="F52" s="18"/>
       <c r="G52" s="18" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="53" spans="4:22">
       <c r="D53" s="18" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E53" s="18"/>
       <c r="F53" s="18"/>
       <c r="G53" s="18" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="54" spans="4:22">
       <c r="D54" s="18" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E54" s="18"/>
       <c r="F54" s="18"/>
       <c r="G54" s="18" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -13508,7 +13764,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96B3948A-F2EB-4210-816C-FE29D536AFF8}">
   <dimension ref="A1:Y69"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
@@ -13522,7 +13778,7 @@
   <sheetData>
     <row r="1" spans="1:25" ht="26.25">
       <c r="A1" s="47" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B1" s="8"/>
     </row>
@@ -13533,14 +13789,14 @@
     <row r="3" spans="1:25" ht="15.75" customHeight="1">
       <c r="A3" s="47"/>
       <c r="B3" s="8" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4" spans="1:25" ht="15.75" customHeight="1">
       <c r="A4" s="47"/>
       <c r="B4" s="8"/>
       <c r="C4" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:25" ht="15.75" customHeight="1">
@@ -13551,14 +13807,14 @@
       <c r="A6" s="47"/>
       <c r="B6" s="8"/>
       <c r="C6" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="7" spans="1:25" ht="15.75" customHeight="1">
       <c r="A7" s="47"/>
       <c r="B7" s="8"/>
       <c r="C7" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="8" spans="1:25" ht="15.75" customHeight="1">
@@ -13567,13 +13823,13 @@
     </row>
     <row r="9" spans="1:25" ht="15.75" customHeight="1">
       <c r="B9" s="8" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="15.75" customHeight="1">
       <c r="B10" s="8"/>
       <c r="C10" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="15.75" customHeight="1">
@@ -13581,7 +13837,7 @@
     </row>
     <row r="12" spans="1:25">
       <c r="B12" s="8" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -13592,32 +13848,32 @@
         <v>7</v>
       </c>
       <c r="D14" s="119" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E14" s="50" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="F14" s="51"/>
       <c r="G14" s="50" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="H14" s="52"/>
       <c r="I14" s="52"/>
       <c r="J14" s="51"/>
       <c r="K14" s="50" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="L14" s="52"/>
       <c r="M14" s="51"/>
       <c r="N14" s="50" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="O14" s="52"/>
       <c r="P14" s="52"/>
       <c r="Q14" s="52"/>
       <c r="R14" s="51"/>
       <c r="T14" s="50" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="U14" s="52"/>
       <c r="V14" s="52"/>
@@ -13631,21 +13887,21 @@
         <v>1</v>
       </c>
       <c r="D15" t="s">
+        <v>399</v>
+      </c>
+      <c r="E15" t="s">
         <v>401</v>
       </c>
-      <c r="E15" t="s">
-        <v>403</v>
-      </c>
       <c r="G15" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="K15" s="70" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="L15" s="70"/>
       <c r="M15" s="70"/>
       <c r="N15" s="13" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="O15" s="70"/>
       <c r="P15" s="70"/>
@@ -13662,19 +13918,19 @@
         <v>2</v>
       </c>
       <c r="D16" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E16" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G16" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="K16" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="N16" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="T16" s="58"/>
       <c r="U16" s="59"/>
@@ -13689,10 +13945,10 @@
         <v>3</v>
       </c>
       <c r="E17" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="G17" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="T17" s="58"/>
       <c r="U17" s="59"/>
@@ -13707,13 +13963,13 @@
         <v>4</v>
       </c>
       <c r="D18" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E18" t="s">
+        <v>408</v>
+      </c>
+      <c r="G18" t="s">
         <v>410</v>
-      </c>
-      <c r="G18" t="s">
-        <v>412</v>
       </c>
       <c r="T18" s="58"/>
       <c r="U18" s="59"/>
@@ -13728,10 +13984,10 @@
         <v>5</v>
       </c>
       <c r="E19" t="s">
+        <v>409</v>
+      </c>
+      <c r="G19" t="s">
         <v>411</v>
-      </c>
-      <c r="G19" t="s">
-        <v>413</v>
       </c>
       <c r="T19" s="58"/>
       <c r="U19" s="59"/>
@@ -13758,7 +14014,7 @@
         <v>7</v>
       </c>
       <c r="D21" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="T21" s="58"/>
       <c r="U21" s="59"/>
@@ -13787,22 +14043,22 @@
     </row>
     <row r="24" spans="2:25">
       <c r="D24" s="48" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E24" s="48"/>
       <c r="F24" s="48" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="G24" s="48"/>
       <c r="H24" s="48"/>
       <c r="I24" s="48"/>
       <c r="J24" s="48" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="K24" s="48"/>
       <c r="L24" s="48"/>
       <c r="M24" s="48" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="N24" s="48"/>
       <c r="O24" s="48"/>
@@ -13815,10 +14071,10 @@
     </row>
     <row r="25" spans="2:25">
       <c r="D25" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="G25" s="70"/>
       <c r="H25" s="70"/>
@@ -13832,21 +14088,21 @@
     </row>
     <row r="26" spans="2:25">
       <c r="D26" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="G26" s="70"/>
       <c r="H26" s="70"/>
       <c r="I26" s="70"/>
       <c r="J26" s="70" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="K26" s="70"/>
       <c r="L26" s="70"/>
       <c r="M26" s="70" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="N26" s="70"/>
       <c r="O26" s="70"/>
@@ -13859,21 +14115,21 @@
     </row>
     <row r="27" spans="2:25">
       <c r="D27" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="G27" s="70"/>
       <c r="H27" s="70"/>
       <c r="I27" s="70"/>
       <c r="J27" s="70" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="K27" s="70"/>
       <c r="L27" s="70"/>
       <c r="M27" s="70" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="N27" s="70"/>
       <c r="O27" s="70"/>
@@ -13886,21 +14142,21 @@
     </row>
     <row r="28" spans="2:25">
       <c r="D28" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="G28" s="70"/>
       <c r="H28" s="70"/>
       <c r="I28" s="70"/>
       <c r="J28" s="70" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K28" s="70"/>
       <c r="L28" s="70"/>
       <c r="M28" s="70" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="N28" s="70"/>
       <c r="O28" s="70"/>
@@ -13939,10 +14195,10 @@
     </row>
     <row r="31" spans="2:25">
       <c r="D31" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="T31" s="58"/>
       <c r="U31" s="59"/>
@@ -13962,7 +14218,7 @@
     </row>
     <row r="33" spans="2:25">
       <c r="G33" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="T33" s="58"/>
       <c r="U33" s="59"/>
@@ -13981,77 +14237,77 @@
     </row>
     <row r="36" spans="2:25">
       <c r="B36" t="s">
-        <v>84</v>
-      </c>
-      <c r="D36" s="130" t="s">
-        <v>419</v>
-      </c>
-      <c r="E36" s="130"/>
+        <v>82</v>
+      </c>
+      <c r="D36" s="123" t="s">
+        <v>417</v>
+      </c>
+      <c r="E36" s="123"/>
       <c r="H36" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="37" spans="2:25">
       <c r="D37" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E37" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="38" spans="2:25">
       <c r="D38" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E38" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="H38" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="40" spans="2:25">
-      <c r="D40" s="130" t="s">
-        <v>418</v>
-      </c>
-      <c r="E40" s="130"/>
+      <c r="D40" s="123" t="s">
+        <v>416</v>
+      </c>
+      <c r="E40" s="123"/>
       <c r="H40" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="41" spans="2:25">
       <c r="D41" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E41" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="42" spans="2:25">
       <c r="D42" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E42" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="H42" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="44" spans="2:25">
       <c r="H44" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="48" spans="2:25">
       <c r="B48" s="8" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="49" spans="2:24">
       <c r="B49" s="8"/>
       <c r="C49" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="50" spans="2:24" ht="17.25" thickBot="1">
@@ -14060,138 +14316,138 @@
     <row r="51" spans="2:24">
       <c r="B51" s="8"/>
       <c r="D51" s="79" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E51" s="75" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F51" s="76"/>
       <c r="G51" s="75" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H51" s="76"/>
       <c r="I51" s="85" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="J51" s="85"/>
       <c r="K51" s="75" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="L51" s="76"/>
       <c r="M51" s="75" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="N51" s="76"/>
       <c r="O51" s="75" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="P51" s="76"/>
       <c r="Q51" s="75" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="R51" s="76"/>
       <c r="S51" s="67" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="T51" s="73"/>
       <c r="U51" s="102" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="V51" s="102"/>
       <c r="W51" s="103" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="X51" s="104"/>
     </row>
     <row r="52" spans="2:24">
       <c r="B52" s="8"/>
       <c r="D52" s="79" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E52" s="75" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F52" s="76"/>
       <c r="G52" s="75" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="H52" s="76"/>
       <c r="I52" s="85" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="J52" s="85"/>
       <c r="K52" s="75" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="L52" s="76"/>
       <c r="M52" s="75" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="N52" s="76"/>
       <c r="O52" s="75" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="P52" s="76"/>
       <c r="Q52" s="75" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="R52" s="76"/>
       <c r="S52" s="86" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="T52" s="71"/>
       <c r="U52" s="105" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="V52" s="105"/>
       <c r="W52" s="106" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="X52" s="107"/>
     </row>
     <row r="53" spans="2:24">
       <c r="B53" s="8"/>
       <c r="D53" s="79" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E53" s="78" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F53" s="76"/>
       <c r="G53" s="78" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H53" s="76"/>
       <c r="I53" s="85" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="J53" s="85"/>
       <c r="K53" s="78" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L53" s="76"/>
       <c r="M53" s="78" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="N53" s="76"/>
       <c r="O53" s="78" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="P53" s="76"/>
       <c r="Q53" s="78" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="R53" s="76"/>
       <c r="S53" s="86" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="T53" s="71"/>
       <c r="U53" s="108" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="V53" s="105"/>
       <c r="W53" s="109" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="X53" s="107"/>
     </row>
@@ -14206,15 +14462,15 @@
       </c>
       <c r="F54" s="93"/>
       <c r="G54" s="93" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="H54" s="93"/>
       <c r="I54" s="93" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="J54" s="93"/>
       <c r="K54" s="93" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L54" s="93"/>
       <c r="M54" s="93">
@@ -14230,7 +14486,7 @@
       </c>
       <c r="R54" s="93"/>
       <c r="S54" s="95" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="T54" s="93"/>
       <c r="U54" s="92">
@@ -14249,19 +14505,19 @@
         <v>2</v>
       </c>
       <c r="E55" s="93" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F55" s="93"/>
       <c r="G55" s="93" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="H55" s="93"/>
       <c r="I55" s="93" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="J55" s="93"/>
       <c r="K55" s="93" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="L55" s="93"/>
       <c r="M55" s="94"/>
@@ -14284,19 +14540,19 @@
         <v>3</v>
       </c>
       <c r="E56" s="93" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F56" s="93"/>
       <c r="G56" s="93" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="H56" s="93"/>
       <c r="I56" s="93" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="J56" s="93"/>
       <c r="K56" s="93" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="L56" s="93"/>
       <c r="M56" s="94"/>
@@ -14319,19 +14575,19 @@
         <v>4</v>
       </c>
       <c r="E57" s="83" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F57" s="83"/>
       <c r="G57" s="83" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="H57" s="83"/>
       <c r="I57" s="83" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="J57" s="83"/>
       <c r="K57" s="84" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="L57" s="84"/>
       <c r="M57" s="84"/>
@@ -14353,78 +14609,78 @@
     <row r="59" spans="2:24">
       <c r="B59" s="8"/>
       <c r="D59" s="18" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G59" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="60" spans="2:24">
       <c r="B60" s="8"/>
       <c r="D60" s="18" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="G60" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="61" spans="2:24">
       <c r="B61" s="8"/>
       <c r="D61" s="18" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="G61" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="62" spans="2:24">
       <c r="B62" s="8"/>
       <c r="D62" s="18" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G62" s="18" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="63" spans="2:24">
       <c r="B63" s="8"/>
       <c r="D63" s="18" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G63" s="18" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="64" spans="2:24">
       <c r="B64" s="8"/>
       <c r="D64" s="18" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G64" s="18" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="65" spans="2:23">
       <c r="B65" s="8"/>
       <c r="D65" s="18" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E65" s="18"/>
       <c r="F65" s="18"/>
       <c r="G65" s="18" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H65" s="18"/>
     </row>
     <row r="66" spans="2:23">
       <c r="B66" s="8"/>
       <c r="D66" s="18" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E66" s="18"/>
       <c r="F66" s="18"/>
       <c r="G66" s="18" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="H66" s="18"/>
       <c r="S66" s="18"/>
@@ -14435,26 +14691,26 @@
     </row>
     <row r="67" spans="2:23">
       <c r="D67" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="68" spans="2:23">
       <c r="D68" s="8" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="69" spans="2:23">
       <c r="D69" s="8" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -14469,7 +14725,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3FA637D-A4E4-43F5-99C7-0DE64168A271}">
   <dimension ref="A1:L46"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
@@ -14490,410 +14746,410 @@
   <sheetData>
     <row r="1" spans="1:12" ht="31.5">
       <c r="A1" s="31" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="32" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B3" s="33"/>
       <c r="C3" s="33"/>
     </row>
     <row r="5" spans="1:12">
-      <c r="B5" s="126" t="s">
-        <v>129</v>
-      </c>
-      <c r="C5" s="126"/>
-      <c r="D5" s="123"/>
-      <c r="E5" s="123" t="s">
-        <v>126</v>
-      </c>
-      <c r="F5" s="125"/>
-      <c r="G5" s="124"/>
-      <c r="H5" s="123" t="s">
-        <v>136</v>
-      </c>
-      <c r="I5" s="124"/>
-      <c r="J5" s="123" t="s">
-        <v>141</v>
-      </c>
-      <c r="K5" s="124"/>
+      <c r="B5" s="129" t="s">
+        <v>127</v>
+      </c>
+      <c r="C5" s="129"/>
+      <c r="D5" s="124"/>
+      <c r="E5" s="124" t="s">
+        <v>124</v>
+      </c>
+      <c r="F5" s="130"/>
+      <c r="G5" s="125"/>
+      <c r="H5" s="124" t="s">
+        <v>134</v>
+      </c>
+      <c r="I5" s="125"/>
+      <c r="J5" s="124" t="s">
+        <v>139</v>
+      </c>
+      <c r="K5" s="125"/>
     </row>
     <row r="6" spans="1:12">
       <c r="B6" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="D6" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="F6" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="G6" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="E6" s="29" t="s">
-        <v>148</v>
-      </c>
-      <c r="F6" s="30" t="s">
-        <v>132</v>
-      </c>
-      <c r="G6" s="24" t="s">
-        <v>133</v>
-      </c>
       <c r="H6" s="19" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="I6" s="20" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J6" s="25" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="K6" s="24" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="19" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B7" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="B9" s="124" t="s">
+        <v>149</v>
+      </c>
+      <c r="C9" s="125"/>
+      <c r="D9" s="124" t="s">
+        <v>151</v>
+      </c>
+      <c r="E9" s="130"/>
+      <c r="F9" s="125"/>
+      <c r="G9" s="124" t="s">
         <v>134</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="K7" s="11" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="B9" s="123" t="s">
-        <v>151</v>
-      </c>
-      <c r="C9" s="124"/>
-      <c r="D9" s="123" t="s">
-        <v>153</v>
-      </c>
-      <c r="E9" s="125"/>
-      <c r="F9" s="124"/>
-      <c r="G9" s="123" t="s">
-        <v>136</v>
-      </c>
-      <c r="H9" s="124"/>
-      <c r="I9" s="123" t="s">
-        <v>141</v>
-      </c>
-      <c r="J9" s="124"/>
-      <c r="K9" s="123" t="s">
-        <v>178</v>
-      </c>
-      <c r="L9" s="124"/>
+      <c r="H9" s="125"/>
+      <c r="I9" s="124" t="s">
+        <v>139</v>
+      </c>
+      <c r="J9" s="125"/>
+      <c r="K9" s="124" t="s">
+        <v>176</v>
+      </c>
+      <c r="L9" s="125"/>
     </row>
     <row r="10" spans="1:12">
       <c r="B10" s="25" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D10" s="29" t="s">
+        <v>165</v>
+      </c>
+      <c r="E10" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="E10" s="30" t="s">
-        <v>169</v>
-      </c>
       <c r="F10" s="24" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G10" s="19" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H10" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="I10" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="J10" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="I10" s="25" t="s">
-        <v>176</v>
-      </c>
-      <c r="J10" s="24" t="s">
-        <v>175</v>
-      </c>
       <c r="K10" s="19" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="L10" s="19" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="19" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C11" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="126" t="s">
+        <v>153</v>
+      </c>
+      <c r="D14" s="27" t="s">
         <v>154</v>
       </c>
-      <c r="D11" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="K11" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="L11" s="11" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14" s="127" t="s">
+      <c r="E14" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="F14" s="129" t="s">
+        <v>163</v>
+      </c>
+      <c r="G14" s="129"/>
+      <c r="H14" s="129"/>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="127"/>
+      <c r="D15" s="34" t="s">
         <v>155</v>
       </c>
-      <c r="D14" s="27" t="s">
+      <c r="E15" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="127"/>
+      <c r="D16" s="35" t="s">
         <v>156</v>
       </c>
-      <c r="E14" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="F14" s="126" t="s">
-        <v>165</v>
-      </c>
-      <c r="G14" s="126"/>
-      <c r="H14" s="126"/>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" s="128"/>
-      <c r="D15" s="34" t="s">
+      <c r="E16" s="13" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="127"/>
+      <c r="D17" s="23" t="s">
         <v>157</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E17" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" s="128"/>
-      <c r="D16" s="35" t="s">
-        <v>158</v>
-      </c>
-      <c r="E16" s="13" t="s">
+      <c r="F17" s="13" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="127"/>
+      <c r="D18" s="13" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="128"/>
-      <c r="D17" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="E17" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="128"/>
-      <c r="D18" s="13" t="s">
-        <v>163</v>
-      </c>
-    </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="128"/>
+      <c r="A19" s="127"/>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="128"/>
+      <c r="A20" s="127"/>
       <c r="E20" s="36" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="127"/>
+      <c r="E21" s="13" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="127"/>
+      <c r="E22" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="128"/>
-      <c r="E21" s="13" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="128"/>
-      <c r="E22" t="s">
-        <v>197</v>
-      </c>
-    </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="128"/>
+      <c r="A23" s="127"/>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="128"/>
+      <c r="A24" s="127"/>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="128"/>
+      <c r="A25" s="127"/>
       <c r="E25" s="11" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="128"/>
+      <c r="A26" s="127"/>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="128"/>
+      <c r="A27" s="127"/>
       <c r="E27" s="13" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="127"/>
+      <c r="E28" s="13" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="127"/>
+      <c r="E29" s="11" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="128"/>
-      <c r="E28" s="13" t="s">
+    <row r="30" spans="1:6">
+      <c r="A30" s="127"/>
+      <c r="E30" s="13" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="128"/>
-      <c r="E29" s="11" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="128"/>
-      <c r="E30" s="13" t="s">
-        <v>228</v>
-      </c>
-    </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="129"/>
+      <c r="A31" s="128"/>
     </row>
     <row r="33" spans="1:7">
       <c r="B33" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="C33" s="27" t="s">
         <v>151</v>
       </c>
-      <c r="C33" s="27" t="s">
-        <v>153</v>
-      </c>
-      <c r="D33" s="123" t="s">
-        <v>189</v>
-      </c>
-      <c r="E33" s="124"/>
-      <c r="F33" s="123" t="s">
-        <v>178</v>
-      </c>
-      <c r="G33" s="124"/>
+      <c r="D33" s="124" t="s">
+        <v>187</v>
+      </c>
+      <c r="E33" s="125"/>
+      <c r="F33" s="124" t="s">
+        <v>176</v>
+      </c>
+      <c r="G33" s="125"/>
     </row>
     <row r="34" spans="1:7">
       <c r="B34" s="26" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C34" s="29" t="s">
+        <v>183</v>
+      </c>
+      <c r="D34" s="19" t="s">
         <v>185</v>
       </c>
-      <c r="D34" s="19" t="s">
-        <v>187</v>
-      </c>
       <c r="E34" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="F34" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="F34" s="19" t="s">
+      <c r="G34" s="19" t="s">
         <v>192</v>
-      </c>
-      <c r="G34" s="19" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="19" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B35" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="C35" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="C35" s="11" t="s">
+      <c r="D35" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="D35" s="11" t="s">
-        <v>188</v>
-      </c>
       <c r="E35" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="F35" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="F35" s="11" t="s">
-        <v>193</v>
-      </c>
       <c r="G35" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="B38" s="19" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D38" s="19" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E38" s="19" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="19" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B39" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C39" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="C39" s="11" t="s">
+      <c r="D39" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="E39" s="13" t="s">
         <v>220</v>
-      </c>
-      <c r="D39" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="33">
       <c r="E40" s="38" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -14934,11 +15190,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="A14:A31"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="B9:C9"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="G9:H9"/>
     <mergeCell ref="K9:L9"/>
@@ -14947,247 +15198,14 @@
     <mergeCell ref="E5:G5"/>
     <mergeCell ref="J5:K5"/>
     <mergeCell ref="H5:I5"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="A14:A31"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="B9:C9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{511B7746-4A5E-454B-8602-7B4B353E7BEF}">
-  <dimension ref="A1:Y24"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
-  <cols>
-    <col min="1" max="1" width="4.625" customWidth="1"/>
-    <col min="2" max="2" width="8.5" customWidth="1"/>
-    <col min="3" max="3" width="5.125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:25" ht="26.25">
-      <c r="A1" s="39" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25">
-      <c r="B3" t="s">
-        <v>201</v>
-      </c>
-      <c r="N3" s="40" t="s">
-        <v>245</v>
-      </c>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="40"/>
-      <c r="R3" s="40"/>
-      <c r="S3" s="40"/>
-      <c r="T3" s="40"/>
-      <c r="U3" s="40"/>
-      <c r="V3" s="40"/>
-      <c r="W3" s="40"/>
-    </row>
-    <row r="4" spans="1:25">
-      <c r="B4" t="s">
-        <v>202</v>
-      </c>
-      <c r="C4" t="s">
-        <v>233</v>
-      </c>
-      <c r="N4" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="O4" s="40"/>
-      <c r="P4" s="40"/>
-      <c r="Q4" s="40"/>
-      <c r="R4" s="40"/>
-      <c r="S4" s="40"/>
-      <c r="T4" s="40"/>
-      <c r="U4" s="40"/>
-      <c r="V4" s="40"/>
-      <c r="W4" s="40"/>
-    </row>
-    <row r="5" spans="1:25">
-      <c r="B5" t="s">
-        <v>203</v>
-      </c>
-      <c r="C5" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" ht="21.75">
-      <c r="B6" t="s">
-        <v>204</v>
-      </c>
-      <c r="C6" t="s">
-        <v>250</v>
-      </c>
-      <c r="N6" s="42" t="s">
-        <v>237</v>
-      </c>
-      <c r="O6" s="43"/>
-      <c r="P6" s="43"/>
-      <c r="Q6" s="43"/>
-      <c r="R6" s="43"/>
-      <c r="S6" s="43"/>
-      <c r="T6" s="43"/>
-      <c r="U6" s="43"/>
-      <c r="V6" s="43"/>
-      <c r="W6" s="43"/>
-      <c r="X6" s="43"/>
-      <c r="Y6" s="43"/>
-    </row>
-    <row r="7" spans="1:25">
-      <c r="N7" s="43"/>
-      <c r="O7" s="43"/>
-      <c r="P7" s="43"/>
-      <c r="Q7" s="43"/>
-      <c r="R7" s="43"/>
-      <c r="S7" s="43"/>
-      <c r="T7" s="43"/>
-      <c r="U7" s="43"/>
-      <c r="V7" s="43"/>
-      <c r="W7" s="43"/>
-      <c r="X7" s="43"/>
-      <c r="Y7" s="43"/>
-    </row>
-    <row r="8" spans="1:25">
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8" t="s">
-        <v>241</v>
-      </c>
-      <c r="N8" s="43" t="s">
-        <v>238</v>
-      </c>
-      <c r="O8" s="43"/>
-      <c r="P8" s="43"/>
-      <c r="Q8" s="43"/>
-      <c r="R8" s="43"/>
-      <c r="S8" s="43"/>
-      <c r="T8" s="43"/>
-      <c r="U8" s="43"/>
-      <c r="V8" s="43"/>
-      <c r="W8" s="43"/>
-      <c r="X8" s="43"/>
-      <c r="Y8" s="43"/>
-    </row>
-    <row r="9" spans="1:25">
-      <c r="C9" t="s">
-        <v>234</v>
-      </c>
-      <c r="N9" s="44"/>
-      <c r="O9" s="43"/>
-      <c r="P9" s="43"/>
-      <c r="Q9" s="43"/>
-      <c r="R9" s="43"/>
-      <c r="S9" s="43"/>
-      <c r="T9" s="43"/>
-      <c r="U9" s="43"/>
-      <c r="V9" s="43"/>
-      <c r="W9" s="43"/>
-      <c r="X9" s="43"/>
-      <c r="Y9" s="43"/>
-    </row>
-    <row r="10" spans="1:25">
-      <c r="N10" s="45" t="s">
-        <v>248</v>
-      </c>
-      <c r="O10" s="43"/>
-      <c r="P10" s="43"/>
-      <c r="Q10" s="43"/>
-      <c r="R10" s="43"/>
-      <c r="S10" s="43"/>
-      <c r="T10" s="43"/>
-      <c r="U10" s="43"/>
-      <c r="V10" s="43"/>
-      <c r="W10" s="43"/>
-      <c r="X10" s="43"/>
-      <c r="Y10" s="43"/>
-    </row>
-    <row r="11" spans="1:25">
-      <c r="B11">
-        <v>2</v>
-      </c>
-      <c r="C11" t="s">
-        <v>239</v>
-      </c>
-      <c r="N11" s="45" t="s">
-        <v>249</v>
-      </c>
-      <c r="O11" s="43"/>
-      <c r="P11" s="43"/>
-      <c r="Q11" s="43"/>
-      <c r="R11" s="43"/>
-      <c r="S11" s="43"/>
-      <c r="T11" s="43"/>
-      <c r="U11" s="43"/>
-      <c r="V11" s="43"/>
-      <c r="W11" s="43"/>
-      <c r="X11" s="43"/>
-      <c r="Y11" s="43"/>
-    </row>
-    <row r="12" spans="1:25">
-      <c r="C12" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25">
-      <c r="B14">
-        <v>3</v>
-      </c>
-      <c r="C14" t="s">
-        <v>242</v>
-      </c>
-      <c r="N14" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25">
-      <c r="C15" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25">
-      <c r="C16" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5">
-      <c r="B18">
-        <v>4</v>
-      </c>
-      <c r="C18" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5">
-      <c r="B20" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5">
-      <c r="B22" t="s">
-        <v>320</v>
-      </c>
-      <c r="D22" t="s">
-        <v>395</v>
-      </c>
-      <c r="E22" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5">
-      <c r="B24" s="57">
-        <f>1920/3</f>
-        <v>640</v>
-      </c>
-      <c r="C24" t="s">
-        <v>319</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>